--- a/regulatory-compliance/cloud-foundation/9.1/nist-ai-600-1/vcf-91-companion-nist-ai-600-1.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/nist-ai-600-1/vcf-91-companion-nist-ai-600-1.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -1076,18 +1091,9 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to asset inventory processes by maintaining a detailed, real-time inventory of technology assets across compute, storage, and networking layers.
-VMware vCenter maintains the authoritative inventory of all managed objects in the environment. The vSphere inventory organizes objects in a hierarchical structure beginning at the root folder and extending through datacenters, clusters, hosts, virtual machines, networks, and datastores. Each object carries metadata including configuration details, resource allocations, and operational state. Administrators can extend this metadata by defining custom attributes, which store organization-specific fields against any inventory object in vCenter. Custom attribute values are held centrally by vCenter rather than within the individual objects, allowing teams to annotate VMs, hosts, datastores, and other inventory items with organization-defined information such as ownership, classification, or business justification details. This inventory reflects the live state of the environment as objects are created, modified, or removed. Multiple vCenter instances can be linked for centralized inventory management across workload domains.
-Programmatic access to the full inventory is available through the vSphere Web Services API. The Property Collector service uses Property Filter Specifications to identify inventory elements either directly or through object property traversal. The RetrievePropertiesEx method collects properties from inventory objects, allowing external systems and automation scripts to enumerate assets, gather configuration details, and build reports at whatever level of granularity is needed. The SimpleClient sample application demonstrates how to connect to a vCenter instance and obtain a listing of top-level inventory entities along with their properties and references.
-VCF Operations extends inventory visibility by retrieving inventory details from each vCenter, including associated clusters, VMware ESX hosts, datastores, and virtual machines. Discovered objects are grouped logically in detailed inventory lists, and the inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group. ResourceAttribute elements define the metrics that appear in the monitoring interface, each identified by a Metric Key, providing continuous visibility into asset utilization, capacity, and health. The vSphere Compute Inventory Dashboard provides interactive views of clusters, hosts, and virtual machines associated with any selected object.
-For application-level visibility, the VCF Operations Service Discovery adapter discovers running applications and services along with their CPU and memory metrics. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be grouped by object type and selected attributes through Application Definition criteria, and the results can be exported in CSV format for use in external asset tracking systems.
-VCF Automation adds a consumption-oriented layer to asset tracking. Projects link users, catalog items, and infrastructure resources where deployments are provisioned. The Overview tab displays infrastructure and consumption metrics across the organization. Resources visible in inventory views are scoped by the rights and project roles assigned to each user, providing role-appropriate visibility for audit and review. When catalog items are deployed, they are provisioned against the infrastructure available to the selected project, creating a traceable relationship between the request, the deployment, and the underlying resources. Provider accounts can create and track assets including virtual machines, catalogs, templates, and media. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources. Tags within VCF Automation express capabilities and constraints that define deployments, and cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-For integration with external asset registries, VCF provides multiple paths. The Management Pack for ServiceNow in VCF Operations discovers and synchronizes asset details including CPU count, CPU speed, CPU type, disk space, RAM, serial number, manufacturer, model ID, OS version, IP address, and vCenter reference through the ServiceNow Table API and CMDB Meta API. These properties are marked as required discovery fields, keeping the external CMDB aligned with the actual virtual infrastructure. VCF Operations for Networks supports adding ServiceNow as a CMDB data source to fetch configuration items and their relationships. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-Software asset tracking is supported through vSphere Lifecycle Manager, where software depots contain both the payloads and metadata for software updates. VCF Lifecycle Management tracks different versions of software components to help maintain compatibility across the infrastructure. The VCF Operations API includes methods to register associated products with their product name, version, and deployment details, contributing to a software-level view of the environment.
-The Consumption layer of VCF extends asset inventory to containerized workloads running on VMware Kubernetes Service (VKS) and vSphere Supervisor. The Kubernetes API server maintains a live registry of every object within a cluster or Supervisor namespace, covering pods, deployments, services, ConfigMaps, Secrets, PersistentVolumeClaims, CustomResourceDefinitions, and other resource types. Every resource carries standard metadata including name, namespace, labels, annotations, creation timestamp, and owning references that administrators can query or export at any level of granularity. Labels and annotations allow teams to attach arbitrary metadata to any Kubernetes resource, such as application name, business unit, or data classification, and these fields are queryable via label selectors, supporting filtered inventory exports by category. Supervisor namespaces map to vCenter namespaces, associating Kubernetes workloads with the organizational units defined during provisioning, and resource quotas and limit ranges attached to each namespace record the allocated capacity and support tracking of resource consumption by application or team.
-For workloads that consume specialized hardware such as accelerators or dedicated network devices, the Kubernetes Device Plugin framework provides hardware-level asset visibility within VKS clusters. Administrators or device owners use DeviceClasses to define sets of devices available in the cluster, and workloads claim specific hardware resources by creating ResourceClaims that filter for device parameters declared in a DeviceClass. Monitoring agents for device plugin resources discover which devices are in use on each node and collect metadata that associates each device allocation with the specific container consuming it, extending hardware asset tracking to the workload level.
-The Harbor Registry Supervisor Service provides an inventory mechanism for container images and artifacts. Harbor organizes images in a Projects structure by team or application and secures them with policies and role-based access control, allowing administrators to track which container images are authorized for use within the environment. Container images deployed through VCF consumption paths should be scanned, signed, and approved according to organizational software supply chain policies before use; digital certificates and validation mechanisms support supply chain assurance of images and artifacts. Where GitOps practices are in use, the Argo CD Supervisor Service extends this inventory capability by recording application synchronization events with timestamps, capturing the resource group, kind, namespace, name, sync status, and health status of each synchronized resource. Git repositories serve as the single source of truth for desired application and infrastructure state in a GitOps workflow, and infrastructure as code stored in version control creates a durable audit log of every authorized change to that state.
-These capabilities give VCF a strong technical foundation for tracking virtual infrastructure assets with accurate, real-time data at multiple levels of granularity. However, the broader requirements of this control, including business justification tracking, organization-defined accountability information, and formal review and audit processes for the full scope of technology assets, applications, services, and data, require organizational policies and processes that operate alongside the platform's inventory capabilities.</t>
+          <t>VMware Private AI Services (PAIS) provides a centralized inventory of AI models through the Model Gallery in Harbor Registry. Each model gallery has a unique name and is organized within Harbor projects with configured user access controls. Model revisions are stored as OCI artifacts with immutable manifests, and each revision is assigned a unique digest, giving a verifiable record of every model version in the inventory.
+OCI metadata describes model contents and dependencies, supporting identification of compatible platforms and giving visibility into what each model requires. The vcf pais models list command retrieves and displays all models available in a model gallery, giving operators a direct inventory view. Model Runtime tracks which models are actively deployed to inference endpoints, distinguishing between stored and deployed models.
+For third-party AI components, PAIS validates running AI workloads based on NVIDIA GPU Cloud (NGC) containers, a curated catalog of GPU-optimized, pre-tested containers. In disconnected environments, a Harbor registry stores container images from the NGC catalog, acting as a controlled intermediary that makes third-party AI components visible and trackable within the organization's infrastructure.</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -2102,19 +2108,17 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides infrastructure that supports AI Test, Evaluation, Validation and Verification (TEVV) activities throughout the model lifecycle. Deep learning VMs provisioned from PAIS images provide dedicated testing environments for AI prototyping, fine-tuning, validation, and inference workloads. These DL VMs run on the same GPU-accelerated workload domains, vGPU profiles, and VM classes used in production, so TEVV activities occur in conditions comparable to the deployment environment.
-The validate-then-publish workflow creates a formal gate for AI deployment. MLOps engineers validate models for inference functionality using the Triton Inference Server and evaluate performance and safety against business use cases, including examination of inference requests for malicious behavior and functional testing. Models must pass this validation before being uploaded to the Model Gallery for production use. Model integrity is verified through hash code validation, and each revision is assigned a unique digest stored as an OCI artifact with an immutable manifest, giving cryptographic verification that the tested model is the same artifact that gets deployed.
-The platform also supports TEVV through its monitoring stack. VCF Operations monitors GPU consumption at cluster, host system, and host properties levels. Each DL VM includes a pre-installed DCGM Exporter with Prometheus collection at 5-second scrape intervals and Grafana visualization, supplying performance telemetry during testing and evaluation. The software stack for running AI applications on top of NVIDIA GPUs is validated in advance, and NVIDIA NGC containers are pre-tested and ready to run, reducing variables during TEVV by providing a known-good baseline.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -2613,20 +2617,17 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides explicit data source identification and tracking for AI workloads. The Data Indexing and Retrieval service offers a Knowledge Bases interface where users create and manage knowledge bases, and a knowledge base can be linked to up to ten data sources. Each data source is created with a name, description, type, and the required properties for retrieving content from its original location, and a single data source can be linked to multiple knowledge bases. The data source type is fixed at creation. Supported data source types include Microsoft SharePoint sites, Amazon S3 compatible stores, and other enterprise content management systems. Each data source stores the credentials required for retrieval, such as service account key file information when applicable, which creates a documented connection between the AI system and its data origins.
-During knowledge base indexing, PAIS tracks document-level detail including crawled documents, new documents found, deleted documents, existing unmodified documents, existing modified documents requiring embedding updates, and skipped documents. It captures size metrics including total megabytes downloaded, new chunks indexed corresponding to inference server invocations for embeddings, and final index size after removal of deleted documents. It records timing metrics for download, embedding generation, and the overall index operation. Document counts returned by retrieval queries are tracked, and counts of documents per media type such as PDF and PPTX are maintained for each knowledge base. Automatic collection and indexing of updates from linked data sources over time keeps these records current.
-For runtime visibility, PAIS supports LLM trace collection through an OpenTelemetry Collector by configuring the spec.observability.llmTraces section of the PAISConfiguration custom resource, with traces transmitted over HTTP/protobuf or gRPC. PAIS metrics, including knowledge base activity, can be visualized in third-party observability platforms such as Grafana. The Data Indexing and Retrieval component also implements a Model Context Protocol (MCP) server that exports a set of search tools for each knowledge base, which gives downstream AI applications a documented programmatic surface tied back to specific data sources. PAIS AI catalog items, including AI Workstation, DSM Database, Triton Inferencing Server, and AI Kubernetes Cluster, are added to the VCF Automation catalog by running the PAIS Quickstart, with required images uploaded in advance to a Harbor registry in disconnected environments.
-Organizational decisions about which data sources are approved for AI use, how data lineage is documented outside the platform, and how training data provenance is governed remain the responsibility of the organization. PAIS supplies the technical registration and tracking infrastructure that the organization configures and operates.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -2770,9 +2771,14 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides infrastructure that supports AI Test, Evaluation, Validation and Verification (TEVV) activities throughout the model lifecycle. Deep learning VMs provisioned from PAIS images provide dedicated testing environments for AI prototyping, fine-tuning, validation, and inference workloads. These DL VMs run on the same GPU-accelerated workload domains, vGPU profiles, and VM classes used in production, so TEVV activities occur in conditions comparable to the deployment environment.
-The validate-then-publish workflow creates a formal gate for AI deployment. MLOps engineers validate models for inference functionality using the Triton Inference Server and evaluate performance and safety against business use cases, including examination of inference requests for malicious behavior and functional testing. Models must pass this validation before being uploaded to the Model Gallery for production use. Model integrity is verified through hash code validation, and each revision is assigned a unique digest stored as an OCI artifact with an immutable manifest, giving cryptographic verification that the tested model is the same artifact that gets deployed.
-The platform also supports TEVV through its monitoring stack. VCF Operations monitors GPU consumption at cluster, host system, and host properties levels. Each DL VM includes a pre-installed DCGM Exporter with Prometheus collection at 5-second scrape intervals and Grafana visualization, supplying performance telemetry during testing and evaluation. The software stack for running AI applications on top of NVIDIA GPUs is validated in advance, and NVIDIA NGC containers are pre-tested and ready to run, reducing variables during TEVV by providing a known-good baseline.</t>
+          <t>VCF provides configurable data retention controls within VCF Operations that allow administrators to align operational data retention periods with organizational requirements. These controls do not address the full scope of media and data retention governance, but they give administrators granular tuning over how long different categories of platform-generated data are kept.
+VCF Operations exposes data retention settings through Administration &gt; Global Settings &gt; Data Retention. Administrators can configure retention periods independently for several data categories. Metrics data supports a retention window between 1 month and 13 months. Entities and configuration data can be retained for a minimum of 1 month and a maximum of 3 months. Organization reports support a maximum data retention period of 1,440 days. At the normal retention tier, VCF Operations retains data at 5-minute granularity for 6 months, then rolls up the seventh month into 1-hour aggregations. A real-time retention tier provides 5-minute granularity, a standard tier retains data for 1 month, and a long-term tier retains data for 13 months. Different data retention policies can be configured and controlled for each category according to organizational requirements. Log data is governed separately through VCF Log Management, where administrators define log partitions that each carry their own retention period in days, with logs removed from disk automatically once a partition's period elapses and the option to archive partitions to external NFS or S3 storage for longer-term preservation.
+VCF Operations for Networks provides additional granular retention controls. The default data retention period is 1 month in the advanced license edition. Flow data retention is fixed at a 1-month window within the platform. For organizations that need to retain flow data beyond one month, the Streaming Databus provides a mechanism to export flows to an external subscriber via HTTPS/HTTP for extended retention. Miscellaneous data retention can be configured with up to 100 GB of additional disk space.
+VCF Operations also provides backup capabilities that support regulatory and operational retention needs. Administrators can take regular backups of both custom and out-of-the-box content. When reducing an entity metrics retention period in VCF Operations for Networks, the recommendation is to back up log files first to prevent data loss, which supports the principle of preserving data before modifying retention windows.
+The Consumption layer of VCF, comprising VMware Kubernetes Service (VKS), vSphere Supervisor, and vSphere namespaces, adds Kubernetes-native persistent storage lifecycle controls relevant to data retention for containerized workloads. Persistent volumes in Supervisor namespaces store application data outside the lifecycle of individual pods and workloads, so data remains available when workloads restart or scale. The central mechanism governing retention behavior is the PersistentVolume reclaim policy, which controls what happens to the underlying storage and its data when the associated PersistentVolumeClaim is deleted. The Retain policy preserves the volume and its data in a Released state for manual administrator reclamation, leaving the data intact for inspection, archival, or transfer before final disposal. The Delete policy causes the storage asset to be removed when the claim is released. Retain is the default for manually provisioned PersistentVolumes. StorageClass definitions carry a ReclaimPolicy field that sets the default behavior for all dynamically provisioned volumes within a given storage class, allowing cluster administrators to enforce organization-wide retention defaults at the storage class level rather than per-volume. For StatefulSet workloads, Kubernetes provides a persistentVolumeClaimRetentionPolicy setting with a whenDeleted field that controls whether PVCs and their backing volumes are retained or deleted when the StatefulSet is removed; scaling a StatefulSet down does not delete the associated volumes by default. Organizations subject to retention obligations should configure StorageClasses with the Retain policy so that workload termination does not destroy data that must be kept for a defined period.
+Storage Policy Based Management (SPBM) provides a unified control plane across VKS storage, enabling storage policies to be associated with persistent volumes that capture the storage characteristics required by a given workload or retention regime. VKS clusters surface a storage compliance status per volume: a Compliant status indicates that the datastore backing the volume satisfies the requirements of the associated policy; an Out of Date status indicates the policy has been updated but the new requirements have not yet been communicated to the datastore, requiring the policy to be reapplied to bring the volume back into compliance. This policy-driven model allows administrators to codify storage requirements and verify adherence continuously.
+For Harbor Registry deployments on VKS clusters, administrators should note that configuring a StorageClass or PersistentVolume with a Delete reclaim policy results in all Harbor data being deleted when the Harbor package is removed. Image artifact retention requirements should drive reclaim policy selection for Harbor-backing storage. Platform teams should also manage data protection storage locations in VCF Automation to align with company-specific data residency and infrastructure standards.
+These retention controls apply to the operational, monitoring, and configuration data that VCF Operations collects and manages, and to the persistent volume lifecycle for containerized workloads on VKS. They do not extend to application data stored within virtual machines outside the Kubernetes layer, user-generated content on datastores not managed by Kubernetes, or media outside the VCF platform. Organizations must establish broader data retention policies, classification schemes, and lifecycle management processes that address all media and data types subject to statutory, regulatory, and contractual obligations. VCF's retention settings are one component of a larger retention program that requires organizational governance, legal review of applicable obligations, and potentially additional tools for archival and disposition of data beyond what VCF Operations and VKS storage lifecycle controls manage.</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -2857,18 +2863,9 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to asset inventory processes by maintaining a detailed, real-time inventory of technology assets across compute, storage, and networking layers.
-VMware vCenter maintains the authoritative inventory of all managed objects in the environment. The vSphere inventory organizes objects in a hierarchical structure beginning at the root folder and extending through datacenters, clusters, hosts, virtual machines, networks, and datastores. Each object carries metadata including configuration details, resource allocations, and operational state. Administrators can extend this metadata by defining custom attributes, which store organization-specific fields against any inventory object in vCenter. Custom attribute values are held centrally by vCenter rather than within the individual objects, allowing teams to annotate VMs, hosts, datastores, and other inventory items with organization-defined information such as ownership, classification, or business justification details. This inventory reflects the live state of the environment as objects are created, modified, or removed. Multiple vCenter instances can be linked for centralized inventory management across workload domains.
-Programmatic access to the full inventory is available through the vSphere Web Services API. The Property Collector service uses Property Filter Specifications to identify inventory elements either directly or through object property traversal. The RetrievePropertiesEx method collects properties from inventory objects, allowing external systems and automation scripts to enumerate assets, gather configuration details, and build reports at whatever level of granularity is needed. The SimpleClient sample application demonstrates how to connect to a vCenter instance and obtain a listing of top-level inventory entities along with their properties and references.
-VCF Operations extends inventory visibility by retrieving inventory details from each vCenter, including associated clusters, VMware ESX hosts, datastores, and virtual machines. Discovered objects are grouped logically in detailed inventory lists, and the inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group. ResourceAttribute elements define the metrics that appear in the monitoring interface, each identified by a Metric Key, providing continuous visibility into asset utilization, capacity, and health. The vSphere Compute Inventory Dashboard provides interactive views of clusters, hosts, and virtual machines associated with any selected object.
-For application-level visibility, the VCF Operations Service Discovery adapter discovers running applications and services along with their CPU and memory metrics. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be grouped by object type and selected attributes through Application Definition criteria, and the results can be exported in CSV format for use in external asset tracking systems.
-VCF Automation adds a consumption-oriented layer to asset tracking. Projects link users, catalog items, and infrastructure resources where deployments are provisioned. The Overview tab displays infrastructure and consumption metrics across the organization. Resources visible in inventory views are scoped by the rights and project roles assigned to each user, providing role-appropriate visibility for audit and review. When catalog items are deployed, they are provisioned against the infrastructure available to the selected project, creating a traceable relationship between the request, the deployment, and the underlying resources. Provider accounts can create and track assets including virtual machines, catalogs, templates, and media. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources. Tags within VCF Automation express capabilities and constraints that define deployments, and cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-For integration with external asset registries, VCF provides multiple paths. The Management Pack for ServiceNow in VCF Operations discovers and synchronizes asset details including CPU count, CPU speed, CPU type, disk space, RAM, serial number, manufacturer, model ID, OS version, IP address, and vCenter reference through the ServiceNow Table API and CMDB Meta API. These properties are marked as required discovery fields, keeping the external CMDB aligned with the actual virtual infrastructure. VCF Operations for Networks supports adding ServiceNow as a CMDB data source to fetch configuration items and their relationships. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-Software asset tracking is supported through vSphere Lifecycle Manager, where software depots contain both the payloads and metadata for software updates. VCF Lifecycle Management tracks different versions of software components to help maintain compatibility across the infrastructure. The VCF Operations API includes methods to register associated products with their product name, version, and deployment details, contributing to a software-level view of the environment.
-The Consumption layer of VCF extends asset inventory to containerized workloads running on VMware Kubernetes Service (VKS) and vSphere Supervisor. The Kubernetes API server maintains a live registry of every object within a cluster or Supervisor namespace, covering pods, deployments, services, ConfigMaps, Secrets, PersistentVolumeClaims, CustomResourceDefinitions, and other resource types. Every resource carries standard metadata including name, namespace, labels, annotations, creation timestamp, and owning references that administrators can query or export at any level of granularity. Labels and annotations allow teams to attach arbitrary metadata to any Kubernetes resource, such as application name, business unit, or data classification, and these fields are queryable via label selectors, supporting filtered inventory exports by category. Supervisor namespaces map to vCenter namespaces, associating Kubernetes workloads with the organizational units defined during provisioning, and resource quotas and limit ranges attached to each namespace record the allocated capacity and support tracking of resource consumption by application or team.
-For workloads that consume specialized hardware such as accelerators or dedicated network devices, the Kubernetes Device Plugin framework provides hardware-level asset visibility within VKS clusters. Administrators or device owners use DeviceClasses to define sets of devices available in the cluster, and workloads claim specific hardware resources by creating ResourceClaims that filter for device parameters declared in a DeviceClass. Monitoring agents for device plugin resources discover which devices are in use on each node and collect metadata that associates each device allocation with the specific container consuming it, extending hardware asset tracking to the workload level.
-The Harbor Registry Supervisor Service provides an inventory mechanism for container images and artifacts. Harbor organizes images in a Projects structure by team or application and secures them with policies and role-based access control, allowing administrators to track which container images are authorized for use within the environment. Container images deployed through VCF consumption paths should be scanned, signed, and approved according to organizational software supply chain policies before use; digital certificates and validation mechanisms support supply chain assurance of images and artifacts. Where GitOps practices are in use, the Argo CD Supervisor Service extends this inventory capability by recording application synchronization events with timestamps, capturing the resource group, kind, namespace, name, sync status, and health status of each synchronized resource. Git repositories serve as the single source of truth for desired application and infrastructure state in a GitOps workflow, and infrastructure as code stored in version control creates a durable audit log of every authorized change to that state.
-These capabilities give VCF a strong technical foundation for tracking virtual infrastructure assets with accurate, real-time data at multiple levels of granularity. However, the broader requirements of this control, including business justification tracking, organization-defined accountability information, and formal review and audit processes for the full scope of technology assets, applications, services, and data, require organizational policies and processes that operate alongside the platform's inventory capabilities.</t>
+          <t>VMware Private AI Services (PAIS) provides a centralized inventory of AI models through the Model Gallery in Harbor Registry. Each model gallery has a unique name and is organized within Harbor projects with configured user access controls. Model revisions are stored as OCI artifacts with immutable manifests, and each revision is assigned a unique digest, giving a verifiable record of every model version in the inventory.
+OCI metadata describes model contents and dependencies, supporting identification of compatible platforms and giving visibility into what each model requires. The vcf pais models list command retrieves and displays all models available in a model gallery, giving operators a direct inventory view. Model Runtime tracks which models are actively deployed to inference endpoints, distinguishing between stored and deployed models.
+For third-party AI components, PAIS validates running AI workloads based on NVIDIA GPU Cloud (NGC) containers, a curated catalog of GPU-optimized, pre-tested containers. In disconnected environments, a Harbor registry stores container images from the NGC catalog, acting as a controlled intermediary that makes third-party AI components visible and trackable within the organization's infrastructure.</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -2939,42 +2936,27 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to asset inventory processes by maintaining a detailed, real-time inventory of technology assets across compute, storage, and networking layers.
-VMware vCenter maintains the authoritative inventory of all managed objects in the environment. The vSphere inventory organizes objects in a hierarchical structure beginning at the root folder and extending through datacenters, clusters, hosts, virtual machines, networks, and datastores. Each object carries metadata including configuration details, resource allocations, and operational state. Administrators can extend this metadata by defining custom attributes, which store organization-specific fields against any inventory object in vCenter. Custom attribute values are held centrally by vCenter rather than within the individual objects, allowing teams to annotate VMs, hosts, datastores, and other inventory items with organization-defined information such as ownership, classification, or business justification details. This inventory reflects the live state of the environment as objects are created, modified, or removed. Multiple vCenter instances can be linked for centralized inventory management across workload domains.
-Programmatic access to the full inventory is available through the vSphere Web Services API. The Property Collector service uses Property Filter Specifications to identify inventory elements either directly or through object property traversal. The RetrievePropertiesEx method collects properties from inventory objects, allowing external systems and automation scripts to enumerate assets, gather configuration details, and build reports at whatever level of granularity is needed. The SimpleClient sample application demonstrates how to connect to a vCenter instance and obtain a listing of top-level inventory entities along with their properties and references.
-VCF Operations extends inventory visibility by retrieving inventory details from each vCenter, including associated clusters, VMware ESX hosts, datastores, and virtual machines. Discovered objects are grouped logically in detailed inventory lists, and the inventory management interface supports sorting, searching, and object tagging to organize assets at scale. Custom object groups are containers that collect data from included objects and report on the data collected, allowing administrators to create dashboards and widgets that display resource information for grouped assets. VCF Operations also applies policies to newly discovered objects, such as objects added to an object group. ResourceAttribute elements define the metrics that appear in the monitoring interface, each identified by a Metric Key, providing continuous visibility into asset utilization, capacity, and health. The vSphere Compute Inventory Dashboard provides interactive views of clusters, hosts, and virtual machines associated with any selected object.
-For application-level visibility, the VCF Operations Service Discovery adapter discovers running applications and services along with their CPU and memory metrics. Discovery rules can be defined using object types including metrics, relationships, properties, object names, and tag-based criteria. Discovered applications can be grouped by object type and selected attributes through Application Definition criteria, and the results can be exported in CSV format for use in external asset tracking systems.
-VCF Automation adds a consumption-oriented layer to asset tracking. Projects link users, catalog items, and infrastructure resources where deployments are provisioned. The Overview tab displays infrastructure and consumption metrics across the organization. Resources visible in inventory views are scoped by the rights and project roles assigned to each user, providing role-appropriate visibility for audit and review. When catalog items are deployed, they are provisioned against the infrastructure available to the selected project, creating a traceable relationship between the request, the deployment, and the underlying resources. Provider accounts can create and track assets including virtual machines, catalogs, templates, and media. Organizations in VCF Automation support policy-based governance on resource usage, allowing IT teams to monitor resource consumption, control permissions, and provide managed services with network isolation. Each organization maintains a secure boundary from other organizations. Resource quota policies can be defined through the Policies API to limit resources consumed by each user, project, or organization. Day 2 Action policies restrict which users have access to specific lifecycle operations on deployed resources. Tags within VCF Automation express capabilities and constraints that define deployments, and cloud administrators can place constraint tags on projects to exercise governance over resource provisioning, supporting asset classification and controlled placement of workloads across the infrastructure.
-For integration with external asset registries, VCF provides multiple paths. The Management Pack for ServiceNow in VCF Operations discovers and synchronizes asset details including CPU count, CPU speed, CPU type, disk space, RAM, serial number, manufacturer, model ID, OS version, IP address, and vCenter reference through the ServiceNow Table API and CMDB Meta API. These properties are marked as required discovery fields, keeping the external CMDB aligned with the actual virtual infrastructure. VCF Operations for Networks supports adding ServiceNow as a CMDB data source to fetch configuration items and their relationships. VCF Automation also integrates with ServiceNow for ITSM and CMDB synchronization, configurable through extensibility action scripts or through VCF Operations Orchestrator Client hosted workflows. The ServiceNow ITSM Plug-in for VCF Automation captures extensive asset metadata, including resource name, operational status, project assignment, storage details, account and region information, endpoint type, zone, environment, and custom properties. The plug-in stores machine resource records in custom ServiceNow CMDB tables that track creation timestamps, deployment IDs, machine IDs, entitled users, and network schema. Deployment records similarly capture blueprint version, project ID, catalog ID, organization ID, operational status, owner, requester, and expiration tracking. The plug-in supports day-2 resource lifecycle actions such as Add Disk, Resize, Power On/Off, Create Snapshot, and Delete, and maintains CMDB accuracy through reconciliation.
-Software asset tracking is supported through vSphere Lifecycle Manager, where software depots contain both the payloads and metadata for software updates. VCF Lifecycle Management tracks different versions of software components to help maintain compatibility across the infrastructure. The VCF Operations API includes methods to register associated products with their product name, version, and deployment details, contributing to a software-level view of the environment.
-The Consumption layer of VCF extends asset inventory to containerized workloads running on VMware Kubernetes Service (VKS) and vSphere Supervisor. The Kubernetes API server maintains a live registry of every object within a cluster or Supervisor namespace, covering pods, deployments, services, ConfigMaps, Secrets, PersistentVolumeClaims, CustomResourceDefinitions, and other resource types. Every resource carries standard metadata including name, namespace, labels, annotations, creation timestamp, and owning references that administrators can query or export at any level of granularity. Labels and annotations allow teams to attach arbitrary metadata to any Kubernetes resource, such as application name, business unit, or data classification, and these fields are queryable via label selectors, supporting filtered inventory exports by category. Supervisor namespaces map to vCenter namespaces, associating Kubernetes workloads with the organizational units defined during provisioning, and resource quotas and limit ranges attached to each namespace record the allocated capacity and support tracking of resource consumption by application or team.
-For workloads that consume specialized hardware such as accelerators or dedicated network devices, the Kubernetes Device Plugin framework provides hardware-level asset visibility within VKS clusters. Administrators or device owners use DeviceClasses to define sets of devices available in the cluster, and workloads claim specific hardware resources by creating ResourceClaims that filter for device parameters declared in a DeviceClass. Monitoring agents for device plugin resources discover which devices are in use on each node and collect metadata that associates each device allocation with the specific container consuming it, extending hardware asset tracking to the workload level.
-The Harbor Registry Supervisor Service provides an inventory mechanism for container images and artifacts. Harbor organizes images in a Projects structure by team or application and secures them with policies and role-based access control, allowing administrators to track which container images are authorized for use within the environment. Container images deployed through VCF consumption paths should be scanned, signed, and approved according to organizational software supply chain policies before use; digital certificates and validation mechanisms support supply chain assurance of images and artifacts. Where GitOps practices are in use, the Argo CD Supervisor Service extends this inventory capability by recording application synchronization events with timestamps, capturing the resource group, kind, namespace, name, sync status, and health status of each synchronized resource. Git repositories serve as the single source of truth for desired application and infrastructure state in a GitOps workflow, and infrastructure as code stored in version control creates a durable audit log of every authorized change to that state.
-These capabilities give VCF a strong technical foundation for tracking virtual infrastructure assets with accurate, real-time data at multiple levels of granularity. However, the broader requirements of this control, including business justification tracking, organization-defined accountability information, and formal review and audit processes for the full scope of technology assets, applications, services, and data, require organizational policies and processes that operate alongside the platform's inventory capabilities.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Services Platform (SSP) maintains an inventory of network-visible workloads organized into a hierarchical asset collection spanning regions, zones, environments, applications, and application tiers. The Publish Inventory Assets tab in SSP displays infrastructure asset details including asset names, asset types, IP addresses, and total VM counts for assets sourced from imported CSV files, discovered services, or published infrastructure assets, providing accurate, granular records of network-visible assets.
-Platform Inventory monitoring supports ongoing inventory accuracy through several mechanisms. Administrators can filter infrastructure assets by Name and Status, identifying assets that are timed out or out of sync. The inventory hierarchy view shows regions, zones, and VMs so administrators can verify correct definition. SSP Inventory displays assigned tags for each infrastructure asset, and environment rows can be expanded to view tag assignments and confirm hierarchy accuracy. The platform also collects and displays VM tags with their respective scopes, supporting classification and tracking. Published applications and their application types are verifiable in the Inventory &gt; Applications interface.
-SSP identifies and publishes application assets, classifying them as either critical or regular applications. Application Asset Collections represent groups of workloads delivering enterprise software functions. Security Intelligence within SSP displays application associations for compute entities, indicating the tiers within each application to which a given compute entity belongs. Administering compute entity classifications in Security Intelligence requires appropriate privileges, supporting access control over classification changes. Consistent naming conventions are recommended when preparing inventory data for import, and the Asset Prefix setting enables standardized naming during segmentation planning and monitoring.
-In disconnected mode, usage files include an asset_id field providing a unique asset identifier, supporting asset tracking in environments without continuous connectivity.
-vDefend's inventory scope is limited to network-visible workloads and does not replace enterprise-wide TAASD inventory tools, authorized software catalogs with business justification records, or data asset registries required for full AST-02 compliance.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -2989,17 +2971,12 @@
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to asset inventory requirements by providing built-in visibility into the database instances, infrastructure resources, and users it manages. This visibility supports tracking and accountability for the subset of technology assets that DSM governs. Organization-wide TAASD inventory across all asset categories requires organizational processes and additional tooling beyond DSM itself.
-DSM tracks the association between deployed databases and the infrastructure policies under which they were provisioned. Administrators can review databases and their configuration details through the Databases tab in the Infrastructure Policies view of the DSM Administrator UI, which displays each policy alongside the databases bound to it. Because infrastructure policies define the compute, storage, and networking resources allocated to databases, including allowed VM classes, this view gives administrators a structured picture of how platform resources are being consumed. The About the DSM UI Views section confirms the Infrastructure Policies view lists all policies available in the environment and the databases associated with each.
-DSM administrators can define and configure data service policies for the data services DSM manages, supporting compliance with organizational standards across tenants. Each policy can be tailored to specific requirements and assigned to one or more organizations to enforce consistent configurations. For tenant-facing self-service, the DSM Consumption Operator creates infrastructure policies as cluster-scoped resources in the consumption cluster and requires an allowedInfrastructurePolicies list that defines which policies a tenant cluster may use, giving administrators a clear inventory of the policies in scope per cluster. Tenant users create and consume databases under a Supervisor namespace through the VCF Automation Cloud Consumption Interface (CCI), and the DSM portal exposes a Consumption Operator endpoint that provides access to deployment artifacts.
-For database-level visibility, the Database Health view in the DSM UI collects metric data for each database instance and cross-references alerts with resolution paths. DSM deploys a Telegraf agent on the Provider Appliance and a local Telegraf agent on each workload cluster to gather VM-level metrics such as CPU, memory, and disk usage, plus engine-specific metrics. DSM can forward metrics to an external Metrics target server, supporting integration with external monitoring or inventory aggregation systems.
-For auditors, DSM's inventory-relevant information is accessible through the Administrator UI and is available to personnel with the Admin role. The Databases tab, Infrastructure Policies view, Database Health view, and Consumption Operator policy inventory collectively provide the granularity needed to account for DSM-managed database assets and the policies governing them. The documented DSM user roles (vSphere administrator, VCF Automation organization administrator, VCF Automation project user) clarify which personnel have visibility into which inventory views.
-DSM provides resource tracking and visibility within its own management scope. DSM does not perform organization-wide asset discovery and does not inventory physical infrastructure, non-database applications, or data assets outside its management domain. A TAASD inventory program spanning all asset categories requires a CMDB or dedicated asset management solution that can aggregate DSM resource data alongside information from other platform components.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
@@ -4183,92 +4160,57 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>VCF provides enterprise-wide monitoring through integrated tools that span infrastructure health, performance metrics, compliance assessment, log analysis, and alerting.
-VCF Operations continuously monitors the operational state of all VCF components to detect conditions that may affect availability or compliance. It collects metrics across compute, storage, and networking resources, and correlates them over time to identify trends that may lead to potential failures. VCF Health, a component of VCF Operations, continuously monitors the operational state of VCF components to verify they are functioning as expected, giving platform operators a single view of operational status. Platform operators can configure alerts, perform log analysis, run infrastructure diagnostics, and review VCF health from a unified interface.
-VCF Operations provides continuous compliance management by monitoring infrastructure against industry-standard benchmarks and custom policies. Administrators can create custom compliance benchmarks that monitor selected alert definitions and policies, tailoring the monitoring posture to organizational requirements. The platform assesses objects based on selected compliance policies and activates alert definitions associated with the current scorecard, providing ongoing visibility into compliance status. Compliance-related alerts are triggered on objects and displayed through a dedicated compliance alert subtype.
-The alerting subsystem in VCF Operations supports the full lifecycle of alert management. Administrators can configure and manage alert definitions to monitor infrastructure events and conditions, including performance metrics, log events, and custom conditions configured through the Management Pack Builder. The Platform Health Alerts page provides a centralized view of all alerts related to overall system health, including alerts from data sources and infrastructure nodes. Health alerts are generated for conditions that affect the health of the environment and require immediate attention. Administrators can create policies to govern how alert definitions are evaluated, including which objects to monitor and what thresholds to apply, and can apply consistent practices to optimize alert behavior across monitored objects.
-VCF Operations supports flexible grouping and scheduling to align monitoring with operational realities. Custom groups can be configured with automatic membership criteria to support monitoring strategies and achieve a high level of automation. Maintenance schedules can be assigned to objects undergoing planned downtime to keep monitoring data accurate and avoid false alerts when an object is offline for scheduled maintenance.
-VCF Log Management provides centralized log collection and analysis. It ingests logs from VMware vCenter, VMware ESX hosts, NSX, vSAN, VCF Automation, VCF Operations, VCF Identity Broker, VCF Operations for Networks, and VCF Operations HCX. VCF Operations and VCF Log Management must be integrated to implement the centralized log collection architecture. The platform provides dashboards and analytics for troubleshooting and security investigation. Log-based alert definitions allow administrators to trigger notifications when specific log patterns appear across monitored systems. Log forwarding to external SIEM or syslog targets is configurable, with support for TLS encryption to protect log data in transit. The vCenter syslog forwarding API supports TCP, UDP, TLS, and RELP protocols. NSX Manager syslog supports TLS and requires port 6514 for encrypted log transmission.
-At the vSphere layer, the alarm infrastructure integrates with events and performance counters to provide real-time alerting. The MetricAlarmExpression data object allows administrators to set alarms on specific performance metrics with configurable monitoring intervals and aggregation functions for processing data points. The vSphere Client provides direct visibility into tasks and events for change tracking and troubleshooting. VCF ships with preconfigured vSphere alarms that are active by default and monitor specific components including the Identity Management Service, Message Bus Configuration Service, ESX Agent Manager, VMware Service Control Agent, vSphere HA host status, and host connection and power state. The vCenter Management Interface provides appliance-level health visibility through an Overall Health badge that reflects one of five states (Good, Warning, Alert, Critical, or Unknown) across all vCenter components, and notifies administrators of available security patches through Critical or Alert badge indicators when automatic patch checks are enabled.
-When VCF Automation is integrated with VCF Operations, the Insights dashboard and Alerts tab provide real-time capacity awareness and alert information for VCF Automation objects, giving IT teams visibility into resource usage across both provisioned workloads and the underlying infrastructure. The VCF Automation Monitor tab surfaces deployment health information sourced from VCF Operations, and deployment cards display Last Request Status information that tracks the most recent operation on each deployment (Create, Update, or Delete) and its outcome (Successful, In Progress, or Failed). The Management Pack Builder allows administrators to set up event definitions for integrated systems, monitoring specific conditions or thresholds and configuring alerts for proactive management. Management Packs extend monitoring to network devices, including sensor monitoring for devices such as switches and routers. Adapters can be installed on VCF Operations nodes to extend monitoring to additional systems and data sources beyond the core VCF components.
-The VMware Kubernetes Service (VKS) layer of VCF extends enterprise monitoring to container workloads and Kubernetes infrastructure. VKS clusters support MachineHealthCheck objects for both control plane nodes and worker node deployments; administrators manage these through the VCF CLI vcf cluster machinehealthcheck command, which supports configuration of unhealthy-condition definitions, maximum unhealthy thresholds (expressed as an absolute number or a percentage), and label selectors to target specific machines. The VCF CLI vcf cluster machinehealthcheck node get and vcf cluster machinehealthcheck control-plane get commands retrieve node and control plane health status on demand. VKS cluster health conditions, including the Ready and ControlPlaneReady status indicators, reflect the operational state of each cluster and are accessible via kubectl and the VCF CLI. The VCF Automation Provider Management UI includes a Services overview interface that exposes VKS cluster management functions and the health status of all cluster elements, giving platform operators a centralized view of the VKS tier. The Kubernetes API server within VKS clusters exposes diagnostic and health check endpoints (/healthz, /livez, /readyz, /statusz, and /metrics) that external monitoring systems can scrape to track API server availability and readiness; the kube-apiserver also emits the kubernetes_healthchecks_total counter and kubernetes_healthcheck gauge metric, which report structured health check status for components including etcd and autoregister-completion. Access to these monitoring endpoints is governed by the built-in Kubernetes system:monitoring RBAC group, which grants read access to liveness, readiness, and metrics endpoints while restricting broader cluster access. The Kubernetes Watch API allows monitoring tools to track changes to any API object as a live stream, supporting event-driven monitoring without continuous polling. The Node Problem Detector monitors node health and surfaces node-level problems as Kubernetes events and node conditions that external monitoring systems can consume via the event stream.
-For workload-level monitoring within VKS clusters, Prometheus Operator is available as a standard package and defines custom resource definitions to deploy and manage Prometheus and Alertmanager StatefulSets, enabling high-availability alerting configurations. The Prometheus Alertmanager custom resource definition configures alert grouping, inhibition, and routing to external notification systems. The Istio service mesh, also available as a standard package on VKS clusters, provides service-level monitoring alongside its traffic management capabilities. The Dynatrace Operator can be deployed on VKS clusters to automate the deployment, scaling, and maintenance of the Dynatrace monitoring stack. Historical analysis, dashboarding, and alerting on cluster-level metrics require a dedicated monitoring solution configured to scrape the VKS metrics endpoints and subscribe to the Kubernetes event stream. The vcf cluster support-bundler create command gathers diagnostic information from Supervisor and VKS clusters when troubleshooting is needed.
-At the network layer, NSX provides monitored indicators including node uptime status, deployment status, management and controller connections, tunnel status, PNIC status, and uptime duration. NSX time series APIs allow viewing data such as VPN statistics, including metadata about the number of tunnels configured and how many are up or down at a given time.
-VCF Operations also supports self-monitoring through the VCF Operations adapter, which collects internal metrics such as activity success counts. This allows administrators to verify that the monitoring platform itself is functioning correctly. The VCF Operations policy engine monitors conditions and generates events to react to changing states in the orchestrator server or connected technologies. The Adapter Instance monitoring interval is configurable, with intervals as granular as five minutes.
-VMware Private AI Services (PAIS) includes a built-in observability stack that supplies monitoring data for AI infrastructure and AI workloads. PAIS Controller metrics are exposed at a Prometheus metrics endpoint on the pais-controller-manager service, allowing collection by monitoring systems and visualization in observability platforms such as Grafana. Observability is activated by updating the PAISConfiguration custom resource with optional sections for Prometheus metrics collection and LLM trace forwarding. The Prometheus runtime can be configured with a specified storage class policy and a configurable metrics retention period, giving administrators control over how long monitoring data is stored. A Prometheus server pod must be in a ready and running state for observability to function.
-LLM trace data from PAIS can be forwarded to an OpenTelemetry Collector endpoint over http/protobuf or gRPC, providing distributed tracing for AI model inference activity. The observability.llmTraces configuration governs trace forwarding and works alongside the Prometheus metrics pipeline to produce two signals: metrics for health and performance, and traces for inference-level behavior. PAIS Controller metrics include the Model Endpoint Controller and PAIS Configuration Controller, giving monitoring platforms component-level visibility into PAIS operations.
-In 9.1, PAIS adds direct integration with VCF Operations. The controller-pod-metrics-streaming setting activates streaming of PAIS controller pod metrics from the Supervisor cluster to VCF Operations, allowing administrators to view PAIS metrics alongside other VCF infrastructure metrics. A Telegraf deployment in the vmware-system-monitoring namespace uses a telegraf-user-config ConfigMap to manage user-configured monitoring endpoints for PAIS. The VCF Consumption CLI connects to the Supervisor endpoint and enables VI administrators to stream metrics from the PAIS controller pod. DevOps engineers can visualize health and performance metrics for PAIS components running in a VCF Automation namespace using Grafana, and MLOps engineers and application developers can monitor the health, quality, and behavior of AI applications and the models used in agents through the same observability platforms.
-PAIS supplies the technical monitoring mechanisms this control requires. Enterprise-wide orchestration of monitoring controls, including alert threshold definition, escalation procedures, and integration with a centralized monitoring or log management platform, remain organizational responsibilities.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) supports network security monitoring through multiple integrated capabilities that contribute to enterprise-wide monitoring frameworks.
-Security Intelligence, hosted on the Security Services Platform (SSP), provides continuous visibility into network traffic flows across protected workloads. It monitors flows between application pairs, updates the Policy Protection Status for each application to indicate that flows are being monitored, and continuously detects new flows between environment pairs, alerting administrators to unauthorized or unexpected traffic. The Monitor &amp; Plan Overview page presents a consolidated view of pending actions, data collection activity status, network security posture, flow trends, and a summary of suspicious traffic. The Security Intelligence Recommendations monitoring capability checks for changes in the scope of monitored entities every hour when the Monitoring toggle is enabled, allowing administrators to keep policy recommendations current as environments evolve. Segmentation Monitoring provides dedicated views of application and infrastructure flows with configurable time ranges spanning from the last hour to the last month, and displays flows related to detected infrastructure servers in a specified time interval.
-The Network Detection and Response (NDR) Sensor checks the status of activated detection features every 15 minutes and updates its configuration accordingly, supporting sustained threat detection coverage. NDR Sensor health status monitoring tracks whether key components, including network traffic capture, file analysis, and data transmission, are operating properly. The NDR Sensor also sends alerts notifying administrators of conditions such as services being down, high CPU, memory, or disk usage, packet drops, or missed heartbeats. NDR provides role-based access control covering triage operations such as viewing detections and campaigns, as well as SIEM configuration management.
-The Security Services Platform monitors its own health, with Yellow or Red health status indicators displayed when issues occur in subcomponents. SSP monitoring tracks the status of the flow clustering job that runs every hour and reports suspicious traffic detector execution status after each run, with values such as SUCCESS, NOT_ENOUGH_BASELINE, and FAILURE.
-The Security dashboard provides a consolidated view for monitoring and configuring security features across network workloads. In federated deployments, the Global Manager provides centralized event management and monitoring for malicious IP blocking activity across all Local Managers.
-vDefend generates Unified Security Logs that VCF Log Management can collect and analyze. These logs cover Distributed Firewall, Gateway Firewall, Identity Firewall, FQDN Analysis, TLS Inspection, Intrusion Detection/Prevention System (IDPS), and URL Filtering activity. Broader log aggregation and SIEM correlation for enterprise-wide monitoring remain the responsibility of the SIEM and logging infrastructure deployed alongside vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides monitoring capabilities specific to the disaster recovery domain and integrates with the broader VCF monitoring ecosystem through dedicated Protection and Recovery dashboards in VCF Operations. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, presenting this through an overview dashboard that displays all site pairs, configurations, health scores, and protection and recoverability status for sites and virtual machines. PNR provides default health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites through VCF Operations, and the dashboards surface alerts informing administrators about configurations and deployments that require attention. Separate dashboard views cover vSAN Snapshots and Replication monitoring, and an Inventory view provides health status, metrics, alerts, and network topology for all monitored objects.
-Within its own domain, PNR provides event logging and configurable alarms for replication and recovery operations. Administrators can create alarms that trigger on specified event conditions, with support for email notifications, SNMP traps, or script execution in response. PNR monitors connections between sites by sending periodic ping requests, logs connection check events, and generates alarms when broken connections are detected. The alarm system generates warning-level alerts for expired snapshot schedules, replication errors such as missing VMs, and connectivity issues with protected and target sites. PNR also monitors resource consumption on the Protection and Recovery Server host and raises alarms when configurable resource thresholds are reached.
-PNR includes a health monitoring service that checks each health finding every five minutes and records a timestamp at each check. Health findings are tracked with status history that can be reviewed over configurable time periods, defaulting to a 24-hour window. The Protection and Recovery Appliance supports syslog forwarding to a remote syslog server for log analysis and centralized monitoring, allowing appliance-level events to flow into existing log management infrastructure.
-The Clean Room Orchestrator, part of PNR's Cyber Recovery capabilities, supports monitoring of clean room events, tasks, and alarms for recovery operations. Clean Room Orchestrator can forward events to VCF Operations, Microsoft Sentinel, or Splunk Cloud for centralized monitoring, supporting organizations that require DR event data to flow into enterprise SIEM and log management platforms as part of a broader monitoring strategy. The Clean Room Orchestrator integrates with endpoint detection and response tools, including CrowdStrike and Carbon Black sensor appliances, for threat detection within isolated recovery environments.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to enterprise-wide monitoring controls through a layered set of observability capabilities covering database health, infrastructure compliance, and event-driven alerting.
-DSM provides a built-in monitoring framework that tracks database instance health across multiple dimensions. From the Monitoring tab in the DSM UI or the vSphere Client, administrators and authorized users can view real-time and historical metrics for database VMs, including CPU Health, Data Disk Health, System Disk Health, Max Connections, Active Connections, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage, and InnoDB Reads and Writes. The Monitoring page defaults to the last three hours of aggregated metric data, with the time range adjustable through the Time Range Last dropdown. This visibility supports detection of resource contention, performance degradation, and connectivity anomalies at the database layer.
-DSM's alert framework provides configurable thresholds for warning and critical conditions on key health indicators. Administrators and users can set separate warning and critical thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections parameters. When thresholds are exceeded, DSM generates typed alerts such as Database Engine Health, Custom Config Health, and Backup Storage Health alerts. DSM monitors database replication status and raises an alert when a secondary database is not replicating data from the primary. DSM also raises an alert when metrics are no longer being received from a cluster, supporting detection of monitoring gaps. Alerts can be activated or deactivated per data service through the "Enable Alerts for DB Alert" setting, providing granular control over which databases are subject to active alerting. For each alert, DSM provides mitigation suggestions to help administrators resolve issues without disrupting database services.
-In addition to database-level alerts, DSM generates global infrastructure alerts that surface vCenter integration and infrastructure policy issues. These include INFRASTRUCTURE_POLICY_VC_ALARMS, raised when vCenter resource alarms are active; INFRASTRUCTURE_POLICY_CLUSTER_COMPLIANT and INVALID_SUPERVISOR_INFRASTRUCTURE_POLICY_STATUS, which reflect cluster compliance state; VCENTER_CONNECTIVITY, raised when vCenter connectivity fails and triggering troubleshooting steps that include verifying connectivity and checking authentication logs; and LicensingNotUpdated and vCenterBinding API status alerts that surface license and API integration conditions. A Global Alerts page in the DSM UI provides a centralized view of these alerts during and after installation and ongoing operation.
-In 9.1, DSM integrates with VCF Operations to extend observability beyond the DSM UI. When configured, VCF Operations automatically discovers and monitors PostgreSQL and MySQL clusters in the Ready state and displays a Data Services View dashboard showing active alerts and inventory items. VCF Operations presents performance data across three levels: cluster-level for overall health, node-level for infrastructure resource use, and database-level for KPIs including Active Connections, Commits, Rollbacks, and Deadlocks. This integration requires configuring the connection between DSM and VCF Operations before use.
-DSM also adds SQL Server as a supported database type, with dedicated monitoring through an integrated InfluxDB instance and Telegraf agents deployed across the provider appliance and SQL Server workload clusters. The monitoring framework supports metrics-based and status-condition-based alerts for SQL Server, covering database engine degradation, non-operational status, and automated or transaction log backup failure conditions.
-DSM supports event notification to external systems through a webhook integration. Webhooks transmit alert notifications containing the triggered date, triggered time, triggered user email, task status, previous status, and task type. This allows DSM alerts to feed into centralized monitoring or incident management platforms maintained by the organization. DSM generates plug-in registration logs that administrators can review for vCenter connectivity errors, and DSM's troubleshooting guidance directs administrators to review active vCenter infrastructure alarms and resolve underlying issues identified through the alert system.
-Enterprise-wide monitoring requires organizational decisions about monitoring architecture, log aggregation platforms, alerting policies, and operational response procedures that lie outside DSM's scope. DSM provides the data and integration points; the organization must determine how those signals are collected, correlated, and acted upon across the broader environment.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to enterprise-wide monitoring through application-delivery-layer mechanisms built into the Avi Controller and Service Engines.
-The Avi Controller monitors Service Engine metrics and sends alarms and notifications to administrators when resource utilization data exceeds defined thresholds. Administrators configure custom thresholds on Service Engine groups through the Resource Events tab in the Avi UI. The Alert feature processes system events and metrics against user-defined rules and generates alerts that trigger configured actions, including sending an email, a syslog message, or an SNMP trap. Alert notifications can be forwarded to remote syslog servers for integration with centralized log management and monitoring platforms.
-ControlScripts extend this event-response capability: a ControlScript can alter Avi configuration or communicate to external systems, including through webhook integrations with external monitoring tools, in response to defined system events. This supports dynamic responses including resource scaling or automated notifications based on health scores from monitoring data.
-The Avi Controller and Service Engines track health score changes and SSL certificate expiration events. Avi integrates with external monitoring tools such as Prometheus for metrics collection and analysis. User-Defined Metrics allow administrators to define and extract customized telemetry data for specific compliance or reporting needs through the API. Real-time metrics are available via API but deactivate by default after 30 minutes to conserve resources and must be reactivated when sustained real-time visibility is required.
-At the data plane, Avi health monitors track the status of backend servers and Service Engines continuously. Service Engine health monitoring records detailed server operational status, including health monitor name, type, last transition timestamps, rise count, fall count, total checks, and total failed checks. Each health monitor can be assigned its own threshold and timeout period for server health validation. Monitors support HTTP, HTTPS, TCP, and UDP health-check protocols with configurable success and failure thresholds, send intervals, and receive timeouts.
-In Kubernetes environments managed by the Avi Kubernetes Operator (AKO), the HealthMonitor custom resource definition (CRD) allows users to define custom health monitoring configurations for backend services with fine-grained control over health check parameters. The Avi Multi-Cluster Kubernetes Operator (AMKO) GlobalDeploymentPolicy supports health monitor references for consistent monitoring across multi-cluster deployments. Within VCF Automation, a HealthMonitor custom resource can create monitors for tracking backend pool member status using TCP, PING, and HTTP check types.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -4650,20 +4592,17 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides explicit data source identification and tracking for AI workloads. The Data Indexing and Retrieval service offers a Knowledge Bases interface where users create and manage knowledge bases, and a knowledge base can be linked to up to ten data sources. Each data source is created with a name, description, type, and the required properties for retrieving content from its original location, and a single data source can be linked to multiple knowledge bases. The data source type is fixed at creation. Supported data source types include Microsoft SharePoint sites, Amazon S3 compatible stores, and other enterprise content management systems. Each data source stores the credentials required for retrieval, such as service account key file information when applicable, which creates a documented connection between the AI system and its data origins.
-During knowledge base indexing, PAIS tracks document-level detail including crawled documents, new documents found, deleted documents, existing unmodified documents, existing modified documents requiring embedding updates, and skipped documents. It captures size metrics including total megabytes downloaded, new chunks indexed corresponding to inference server invocations for embeddings, and final index size after removal of deleted documents. It records timing metrics for download, embedding generation, and the overall index operation. Document counts returned by retrieval queries are tracked, and counts of documents per media type such as PDF and PPTX are maintained for each knowledge base. Automatic collection and indexing of updates from linked data sources over time keeps these records current.
-For runtime visibility, PAIS supports LLM trace collection through an OpenTelemetry Collector by configuring the spec.observability.llmTraces section of the PAISConfiguration custom resource, with traces transmitted over HTTP/protobuf or gRPC. PAIS metrics, including knowledge base activity, can be visualized in third-party observability platforms such as Grafana. The Data Indexing and Retrieval component also implements a Model Context Protocol (MCP) server that exports a set of search tools for each knowledge base, which gives downstream AI applications a documented programmatic surface tied back to specific data sources. PAIS AI catalog items, including AI Workstation, DSM Database, Triton Inferencing Server, and AI Kubernetes Cluster, are added to the VCF Automation catalog by running the PAIS Quickstart, with required images uploaded in advance to a Harbor registry in disconnected environments.
-Organizational decisions about which data sources are approved for AI use, how data lineage is documented outside the platform, and how training data provenance is governed remain the responsibility of the organization. PAIS supplies the technical registration and tracking infrastructure that the organization configures and operates.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -4725,34 +4664,27 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides explicit data source identification and tracking for AI workloads. The Data Indexing and Retrieval service offers a Knowledge Bases interface where users create and manage knowledge bases, and a knowledge base can be linked to up to ten data sources. Each data source is created with a name, description, type, and the required properties for retrieving content from its original location, and a single data source can be linked to multiple knowledge bases. The data source type is fixed at creation. Supported data source types include Microsoft SharePoint sites, Amazon S3 compatible stores, and other enterprise content management systems. Each data source stores the credentials required for retrieval, such as service account key file information when applicable, which creates a documented connection between the AI system and its data origins.
-During knowledge base indexing, PAIS tracks document-level detail including crawled documents, new documents found, deleted documents, existing unmodified documents, existing modified documents requiring embedding updates, and skipped documents. It captures size metrics including total megabytes downloaded, new chunks indexed corresponding to inference server invocations for embeddings, and final index size after removal of deleted documents. It records timing metrics for download, embedding generation, and the overall index operation. Document counts returned by retrieval queries are tracked, and counts of documents per media type such as PDF and PPTX are maintained for each knowledge base. Automatic collection and indexing of updates from linked data sources over time keeps these records current.
-For runtime visibility, PAIS supports LLM trace collection through an OpenTelemetry Collector by configuring the spec.observability.llmTraces section of the PAISConfiguration custom resource, with traces transmitted over HTTP/protobuf or gRPC. PAIS metrics, including knowledge base activity, can be visualized in third-party observability platforms such as Grafana. The Data Indexing and Retrieval component also implements a Model Context Protocol (MCP) server that exports a set of search tools for each knowledge base, which gives downstream AI applications a documented programmatic surface tied back to specific data sources. PAIS AI catalog items, including AI Workstation, DSM Database, Triton Inferencing Server, and AI Kubernetes Cluster, are added to the VCF Automation catalog by running the PAIS Quickstart, with required images uploaded in advance to a Harbor registry in disconnected environments.
-Organizational decisions about which data sources are approved for AI use, how data lineage is documented outside the platform, and how training data provenance is governed remain the responsibility of the organization. PAIS supplies the technical registration and tracking infrastructure that the organization configures and operates.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to protecting sensitive and regulated data in support of contracts by enabling microsegmentation through the Distributed Firewall (DFW), which enforces least-privilege network access controls around workloads that collect, process, transmit, or store contract data. In 9.1, privileged labels provide a tamper-proof mechanism for anchoring firewall rules to immutable labels, preventing virtual machines from leaking out of security groups and maintaining the integrity of network isolation boundaries around protected workloads.
-DFW packet logs capture rule set, rule ID, direction, protocol, and source and destination addresses and ports, providing an audit trail for traffic flows around workloads handling contract data. The Gateway Firewall extends this protection to north-south traffic flows.
-Security Services Platform (SSP) supports a structured approach to coverage: the Application Inventory prioritizes securing critical applications before regular ones, and Security Policies gives operators visibility into protected and unprotected network flows with drill-down into individual flow details. The Security Segmentation report breaks down unique traffic flows by protection status and workload type, allowing operators to verify that workloads handling contract data are fully covered by policy.
-VMware vDefend can identify and control risky application protocols that transport data in clear text, including HTTP, Telnet, FTP, TFTP, LDAP, POP3, and IMAP, supporting detection and restriction of unencrypted data paths. Network Detection and Response (NDR) anonymizes sensitive customer information when sharing telemetry data to the cloud, and SSP stores collected data using encryption at rest.
-Data governance obligations, including contractual data handling requirements, access agreements, and regulatory compliance documentation, remain organizational responsibilities outside vDefend's scope.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -4777,18 +4709,12 @@
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N56" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides application-layer mechanisms relevant to protecting sensitive and regulated data in transit at the application delivery tier.
-For data in transit, each virtual service that handles encrypted connections is configured with an SSL/TLS profile that specifies the accepted cipher suites and protocol versions. These profiles are configurable per virtual service, allowing organizations to enforce strong cryptographic standards on connections carrying sensitive or regulated data. The System-Secure-HTTP application profile provides an additional layer of protection by enforcing HTTPS, protecting cookies, managing client IP handling, and controlling protocol behavior for HTTP virtual services.
-TLS session persistence state is stored in encrypted form at the Service Engine so that session data is not exposed when a client reconnects to a different Service Engine. Communication between Avi Controllers and Service Engines uses encrypted channels.
-Avi's Analytics Profile includes a sensitive log profile capability that controls how sensitive data appearing in client requests is handled in application logs. Operators configure this setting to suppress or mask fields that may contain regulated information, reducing the risk of sensitive data being written to log storage in cleartext.
-In Kubernetes environments, the Avi Kubernetes Operator (AKO) supports PKIProfile resources that enable certificate-based authentication and encryption for communication with backend services. The RouteBackendExtension custom resource definition provides backend TLS configuration capability, supporting encryption of traffic between Service Engines and backend servers. The System-Standard SSL Profile can be applied through AKO to enable SSL/TLS re-encryption for backend traffic using modern cipher suites.
-The Avi Cloud Console Application Rules service allows organizations to protect applications from known vulnerabilities by enabling managed application security rules on their Avi Controllers.
-Fully satisfying this control also requires an organizational data classification program that identifies which data is sensitive or regulated under applicable contracts, maps that data to the application flows handled by Avi virtual services, and verifies that Avi's encryption and logging controls are applied to those flows. Avi provides the technical mechanisms; the organizational program determines how and where they are applied.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -5465,92 +5391,57 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>VCF provides enterprise-wide monitoring through integrated tools that span infrastructure health, performance metrics, compliance assessment, log analysis, and alerting.
-VCF Operations continuously monitors the operational state of all VCF components to detect conditions that may affect availability or compliance. It collects metrics across compute, storage, and networking resources, and correlates them over time to identify trends that may lead to potential failures. VCF Health, a component of VCF Operations, continuously monitors the operational state of VCF components to verify they are functioning as expected, giving platform operators a single view of operational status. Platform operators can configure alerts, perform log analysis, run infrastructure diagnostics, and review VCF health from a unified interface.
-VCF Operations provides continuous compliance management by monitoring infrastructure against industry-standard benchmarks and custom policies. Administrators can create custom compliance benchmarks that monitor selected alert definitions and policies, tailoring the monitoring posture to organizational requirements. The platform assesses objects based on selected compliance policies and activates alert definitions associated with the current scorecard, providing ongoing visibility into compliance status. Compliance-related alerts are triggered on objects and displayed through a dedicated compliance alert subtype.
-The alerting subsystem in VCF Operations supports the full lifecycle of alert management. Administrators can configure and manage alert definitions to monitor infrastructure events and conditions, including performance metrics, log events, and custom conditions configured through the Management Pack Builder. The Platform Health Alerts page provides a centralized view of all alerts related to overall system health, including alerts from data sources and infrastructure nodes. Health alerts are generated for conditions that affect the health of the environment and require immediate attention. Administrators can create policies to govern how alert definitions are evaluated, including which objects to monitor and what thresholds to apply, and can apply consistent practices to optimize alert behavior across monitored objects.
-VCF Operations supports flexible grouping and scheduling to align monitoring with operational realities. Custom groups can be configured with automatic membership criteria to support monitoring strategies and achieve a high level of automation. Maintenance schedules can be assigned to objects undergoing planned downtime to keep monitoring data accurate and avoid false alerts when an object is offline for scheduled maintenance.
-VCF Log Management provides centralized log collection and analysis. It ingests logs from VMware vCenter, VMware ESX hosts, NSX, vSAN, VCF Automation, VCF Operations, VCF Identity Broker, VCF Operations for Networks, and VCF Operations HCX. VCF Operations and VCF Log Management must be integrated to implement the centralized log collection architecture. The platform provides dashboards and analytics for troubleshooting and security investigation. Log-based alert definitions allow administrators to trigger notifications when specific log patterns appear across monitored systems. Log forwarding to external SIEM or syslog targets is configurable, with support for TLS encryption to protect log data in transit. The vCenter syslog forwarding API supports TCP, UDP, TLS, and RELP protocols. NSX Manager syslog supports TLS and requires port 6514 for encrypted log transmission.
-At the vSphere layer, the alarm infrastructure integrates with events and performance counters to provide real-time alerting. The MetricAlarmExpression data object allows administrators to set alarms on specific performance metrics with configurable monitoring intervals and aggregation functions for processing data points. The vSphere Client provides direct visibility into tasks and events for change tracking and troubleshooting. VCF ships with preconfigured vSphere alarms that are active by default and monitor specific components including the Identity Management Service, Message Bus Configuration Service, ESX Agent Manager, VMware Service Control Agent, vSphere HA host status, and host connection and power state. The vCenter Management Interface provides appliance-level health visibility through an Overall Health badge that reflects one of five states (Good, Warning, Alert, Critical, or Unknown) across all vCenter components, and notifies administrators of available security patches through Critical or Alert badge indicators when automatic patch checks are enabled.
-When VCF Automation is integrated with VCF Operations, the Insights dashboard and Alerts tab provide real-time capacity awareness and alert information for VCF Automation objects, giving IT teams visibility into resource usage across both provisioned workloads and the underlying infrastructure. The VCF Automation Monitor tab surfaces deployment health information sourced from VCF Operations, and deployment cards display Last Request Status information that tracks the most recent operation on each deployment (Create, Update, or Delete) and its outcome (Successful, In Progress, or Failed). The Management Pack Builder allows administrators to set up event definitions for integrated systems, monitoring specific conditions or thresholds and configuring alerts for proactive management. Management Packs extend monitoring to network devices, including sensor monitoring for devices such as switches and routers. Adapters can be installed on VCF Operations nodes to extend monitoring to additional systems and data sources beyond the core VCF components.
-The VMware Kubernetes Service (VKS) layer of VCF extends enterprise monitoring to container workloads and Kubernetes infrastructure. VKS clusters support MachineHealthCheck objects for both control plane nodes and worker node deployments; administrators manage these through the VCF CLI vcf cluster machinehealthcheck command, which supports configuration of unhealthy-condition definitions, maximum unhealthy thresholds (expressed as an absolute number or a percentage), and label selectors to target specific machines. The VCF CLI vcf cluster machinehealthcheck node get and vcf cluster machinehealthcheck control-plane get commands retrieve node and control plane health status on demand. VKS cluster health conditions, including the Ready and ControlPlaneReady status indicators, reflect the operational state of each cluster and are accessible via kubectl and the VCF CLI. The VCF Automation Provider Management UI includes a Services overview interface that exposes VKS cluster management functions and the health status of all cluster elements, giving platform operators a centralized view of the VKS tier. The Kubernetes API server within VKS clusters exposes diagnostic and health check endpoints (/healthz, /livez, /readyz, /statusz, and /metrics) that external monitoring systems can scrape to track API server availability and readiness; the kube-apiserver also emits the kubernetes_healthchecks_total counter and kubernetes_healthcheck gauge metric, which report structured health check status for components including etcd and autoregister-completion. Access to these monitoring endpoints is governed by the built-in Kubernetes system:monitoring RBAC group, which grants read access to liveness, readiness, and metrics endpoints while restricting broader cluster access. The Kubernetes Watch API allows monitoring tools to track changes to any API object as a live stream, supporting event-driven monitoring without continuous polling. The Node Problem Detector monitors node health and surfaces node-level problems as Kubernetes events and node conditions that external monitoring systems can consume via the event stream.
-For workload-level monitoring within VKS clusters, Prometheus Operator is available as a standard package and defines custom resource definitions to deploy and manage Prometheus and Alertmanager StatefulSets, enabling high-availability alerting configurations. The Prometheus Alertmanager custom resource definition configures alert grouping, inhibition, and routing to external notification systems. The Istio service mesh, also available as a standard package on VKS clusters, provides service-level monitoring alongside its traffic management capabilities. The Dynatrace Operator can be deployed on VKS clusters to automate the deployment, scaling, and maintenance of the Dynatrace monitoring stack. Historical analysis, dashboarding, and alerting on cluster-level metrics require a dedicated monitoring solution configured to scrape the VKS metrics endpoints and subscribe to the Kubernetes event stream. The vcf cluster support-bundler create command gathers diagnostic information from Supervisor and VKS clusters when troubleshooting is needed.
-At the network layer, NSX provides monitored indicators including node uptime status, deployment status, management and controller connections, tunnel status, PNIC status, and uptime duration. NSX time series APIs allow viewing data such as VPN statistics, including metadata about the number of tunnels configured and how many are up or down at a given time.
-VCF Operations also supports self-monitoring through the VCF Operations adapter, which collects internal metrics such as activity success counts. This allows administrators to verify that the monitoring platform itself is functioning correctly. The VCF Operations policy engine monitors conditions and generates events to react to changing states in the orchestrator server or connected technologies. The Adapter Instance monitoring interval is configurable, with intervals as granular as five minutes.
-VMware Private AI Services (PAIS) includes a built-in observability stack that supplies monitoring data for AI infrastructure and AI workloads. PAIS Controller metrics are exposed at a Prometheus metrics endpoint on the pais-controller-manager service, allowing collection by monitoring systems and visualization in observability platforms such as Grafana. Observability is activated by updating the PAISConfiguration custom resource with optional sections for Prometheus metrics collection and LLM trace forwarding. The Prometheus runtime can be configured with a specified storage class policy and a configurable metrics retention period, giving administrators control over how long monitoring data is stored. A Prometheus server pod must be in a ready and running state for observability to function.
-LLM trace data from PAIS can be forwarded to an OpenTelemetry Collector endpoint over http/protobuf or gRPC, providing distributed tracing for AI model inference activity. The observability.llmTraces configuration governs trace forwarding and works alongside the Prometheus metrics pipeline to produce two signals: metrics for health and performance, and traces for inference-level behavior. PAIS Controller metrics include the Model Endpoint Controller and PAIS Configuration Controller, giving monitoring platforms component-level visibility into PAIS operations.
-In 9.1, PAIS adds direct integration with VCF Operations. The controller-pod-metrics-streaming setting activates streaming of PAIS controller pod metrics from the Supervisor cluster to VCF Operations, allowing administrators to view PAIS metrics alongside other VCF infrastructure metrics. A Telegraf deployment in the vmware-system-monitoring namespace uses a telegraf-user-config ConfigMap to manage user-configured monitoring endpoints for PAIS. The VCF Consumption CLI connects to the Supervisor endpoint and enables VI administrators to stream metrics from the PAIS controller pod. DevOps engineers can visualize health and performance metrics for PAIS components running in a VCF Automation namespace using Grafana, and MLOps engineers and application developers can monitor the health, quality, and behavior of AI applications and the models used in agents through the same observability platforms.
-PAIS supplies the technical monitoring mechanisms this control requires. Enterprise-wide orchestration of monitoring controls, including alert threshold definition, escalation procedures, and integration with a centralized monitoring or log management platform, remain organizational responsibilities.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) supports network security monitoring through multiple integrated capabilities that contribute to enterprise-wide monitoring frameworks.
-Security Intelligence, hosted on the Security Services Platform (SSP), provides continuous visibility into network traffic flows across protected workloads. It monitors flows between application pairs, updates the Policy Protection Status for each application to indicate that flows are being monitored, and continuously detects new flows between environment pairs, alerting administrators to unauthorized or unexpected traffic. The Monitor &amp; Plan Overview page presents a consolidated view of pending actions, data collection activity status, network security posture, flow trends, and a summary of suspicious traffic. The Security Intelligence Recommendations monitoring capability checks for changes in the scope of monitored entities every hour when the Monitoring toggle is enabled, allowing administrators to keep policy recommendations current as environments evolve. Segmentation Monitoring provides dedicated views of application and infrastructure flows with configurable time ranges spanning from the last hour to the last month, and displays flows related to detected infrastructure servers in a specified time interval.
-The Network Detection and Response (NDR) Sensor checks the status of activated detection features every 15 minutes and updates its configuration accordingly, supporting sustained threat detection coverage. NDR Sensor health status monitoring tracks whether key components, including network traffic capture, file analysis, and data transmission, are operating properly. The NDR Sensor also sends alerts notifying administrators of conditions such as services being down, high CPU, memory, or disk usage, packet drops, or missed heartbeats. NDR provides role-based access control covering triage operations such as viewing detections and campaigns, as well as SIEM configuration management.
-The Security Services Platform monitors its own health, with Yellow or Red health status indicators displayed when issues occur in subcomponents. SSP monitoring tracks the status of the flow clustering job that runs every hour and reports suspicious traffic detector execution status after each run, with values such as SUCCESS, NOT_ENOUGH_BASELINE, and FAILURE.
-The Security dashboard provides a consolidated view for monitoring and configuring security features across network workloads. In federated deployments, the Global Manager provides centralized event management and monitoring for malicious IP blocking activity across all Local Managers.
-vDefend generates Unified Security Logs that VCF Log Management can collect and analyze. These logs cover Distributed Firewall, Gateway Firewall, Identity Firewall, FQDN Analysis, TLS Inspection, Intrusion Detection/Prevention System (IDPS), and URL Filtering activity. Broader log aggregation and SIEM correlation for enterprise-wide monitoring remain the responsibility of the SIEM and logging infrastructure deployed alongside vDefend.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides monitoring capabilities specific to the disaster recovery domain and integrates with the broader VCF monitoring ecosystem through dedicated Protection and Recovery dashboards in VCF Operations. VCF Operations collects configuration, component health, and usage information from protection and recovery servers and site pairs, presenting this through an overview dashboard that displays all site pairs, configurations, health scores, and protection and recoverability status for sites and virtual machines. PNR provides default health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites through VCF Operations, and the dashboards surface alerts informing administrators about configurations and deployments that require attention. Separate dashboard views cover vSAN Snapshots and Replication monitoring, and an Inventory view provides health status, metrics, alerts, and network topology for all monitored objects.
-Within its own domain, PNR provides event logging and configurable alarms for replication and recovery operations. Administrators can create alarms that trigger on specified event conditions, with support for email notifications, SNMP traps, or script execution in response. PNR monitors connections between sites by sending periodic ping requests, logs connection check events, and generates alarms when broken connections are detected. The alarm system generates warning-level alerts for expired snapshot schedules, replication errors such as missing VMs, and connectivity issues with protected and target sites. PNR also monitors resource consumption on the Protection and Recovery Server host and raises alarms when configurable resource thresholds are reached.
-PNR includes a health monitoring service that checks each health finding every five minutes and records a timestamp at each check. Health findings are tracked with status history that can be reviewed over configurable time periods, defaulting to a 24-hour window. The Protection and Recovery Appliance supports syslog forwarding to a remote syslog server for log analysis and centralized monitoring, allowing appliance-level events to flow into existing log management infrastructure.
-The Clean Room Orchestrator, part of PNR's Cyber Recovery capabilities, supports monitoring of clean room events, tasks, and alarms for recovery operations. Clean Room Orchestrator can forward events to VCF Operations, Microsoft Sentinel, or Splunk Cloud for centralized monitoring, supporting organizations that require DR event data to flow into enterprise SIEM and log management platforms as part of a broader monitoring strategy. The Clean Room Orchestrator integrates with endpoint detection and response tools, including CrowdStrike and Carbon Black sensor appliances, for threat detection within isolated recovery environments.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L66" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to enterprise-wide monitoring controls through a layered set of observability capabilities covering database health, infrastructure compliance, and event-driven alerting.
-DSM provides a built-in monitoring framework that tracks database instance health across multiple dimensions. From the Monitoring tab in the DSM UI or the vSphere Client, administrators and authorized users can view real-time and historical metrics for database VMs, including CPU Health, Data Disk Health, System Disk Health, Max Connections, Active Connections, Write Throughput, Read Throughput, Thread Resource Utilization, Slow Queries per Second, InnoDB Buffer Usage, and InnoDB Reads and Writes. The Monitoring page defaults to the last three hours of aggregated metric data, with the time range adjustable through the Time Range Last dropdown. This visibility supports detection of resource contention, performance degradation, and connectivity anomalies at the database layer.
-DSM's alert framework provides configurable thresholds for warning and critical conditions on key health indicators. Administrators and users can set separate warning and critical thresholds for CPU Health, Data Disk Health, System Disk Health, and Max Connections parameters. When thresholds are exceeded, DSM generates typed alerts such as Database Engine Health, Custom Config Health, and Backup Storage Health alerts. DSM monitors database replication status and raises an alert when a secondary database is not replicating data from the primary. DSM also raises an alert when metrics are no longer being received from a cluster, supporting detection of monitoring gaps. Alerts can be activated or deactivated per data service through the "Enable Alerts for DB Alert" setting, providing granular control over which databases are subject to active alerting. For each alert, DSM provides mitigation suggestions to help administrators resolve issues without disrupting database services.
-In addition to database-level alerts, DSM generates global infrastructure alerts that surface vCenter integration and infrastructure policy issues. These include INFRASTRUCTURE_POLICY_VC_ALARMS, raised when vCenter resource alarms are active; INFRASTRUCTURE_POLICY_CLUSTER_COMPLIANT and INVALID_SUPERVISOR_INFRASTRUCTURE_POLICY_STATUS, which reflect cluster compliance state; VCENTER_CONNECTIVITY, raised when vCenter connectivity fails and triggering troubleshooting steps that include verifying connectivity and checking authentication logs; and LicensingNotUpdated and vCenterBinding API status alerts that surface license and API integration conditions. A Global Alerts page in the DSM UI provides a centralized view of these alerts during and after installation and ongoing operation.
-In 9.1, DSM integrates with VCF Operations to extend observability beyond the DSM UI. When configured, VCF Operations automatically discovers and monitors PostgreSQL and MySQL clusters in the Ready state and displays a Data Services View dashboard showing active alerts and inventory items. VCF Operations presents performance data across three levels: cluster-level for overall health, node-level for infrastructure resource use, and database-level for KPIs including Active Connections, Commits, Rollbacks, and Deadlocks. This integration requires configuring the connection between DSM and VCF Operations before use.
-DSM also adds SQL Server as a supported database type, with dedicated monitoring through an integrated InfluxDB instance and Telegraf agents deployed across the provider appliance and SQL Server workload clusters. The monitoring framework supports metrics-based and status-condition-based alerts for SQL Server, covering database engine degradation, non-operational status, and automated or transaction log backup failure conditions.
-DSM supports event notification to external systems through a webhook integration. Webhooks transmit alert notifications containing the triggered date, triggered time, triggered user email, task status, previous status, and task type. This allows DSM alerts to feed into centralized monitoring or incident management platforms maintained by the organization. DSM generates plug-in registration logs that administrators can review for vCenter connectivity errors, and DSM's troubleshooting guidance directs administrators to review active vCenter infrastructure alarms and resolve underlying issues identified through the alert system.
-Enterprise-wide monitoring requires organizational decisions about monitoring architecture, log aggregation platforms, alerting policies, and operational response procedures that lie outside DSM's scope. DSM provides the data and integration points; the organization must determine how those signals are collected, correlated, and acted upon across the broader environment.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M66" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) contributes to enterprise-wide monitoring through application-delivery-layer mechanisms built into the Avi Controller and Service Engines.
-The Avi Controller monitors Service Engine metrics and sends alarms and notifications to administrators when resource utilization data exceeds defined thresholds. Administrators configure custom thresholds on Service Engine groups through the Resource Events tab in the Avi UI. The Alert feature processes system events and metrics against user-defined rules and generates alerts that trigger configured actions, including sending an email, a syslog message, or an SNMP trap. Alert notifications can be forwarded to remote syslog servers for integration with centralized log management and monitoring platforms.
-ControlScripts extend this event-response capability: a ControlScript can alter Avi configuration or communicate to external systems, including through webhook integrations with external monitoring tools, in response to defined system events. This supports dynamic responses including resource scaling or automated notifications based on health scores from monitoring data.
-The Avi Controller and Service Engines track health score changes and SSL certificate expiration events. Avi integrates with external monitoring tools such as Prometheus for metrics collection and analysis. User-Defined Metrics allow administrators to define and extract customized telemetry data for specific compliance or reporting needs through the API. Real-time metrics are available via API but deactivate by default after 30 minutes to conserve resources and must be reactivated when sustained real-time visibility is required.
-At the data plane, Avi health monitors track the status of backend servers and Service Engines continuously. Service Engine health monitoring records detailed server operational status, including health monitor name, type, last transition timestamps, rise count, fall count, total checks, and total failed checks. Each health monitor can be assigned its own threshold and timeout period for server health validation. Monitors support HTTP, HTTPS, TCP, and UDP health-check protocols with configurable success and failure thresholds, send intervals, and receive timeouts.
-In Kubernetes environments managed by the Avi Kubernetes Operator (AKO), the HealthMonitor custom resource definition (CRD) allows users to define custom health monitoring configurations for backend services with fine-grained control over health check parameters. The Avi Multi-Cluster Kubernetes Operator (AMKO) GlobalDeploymentPolicy supports health monitor references for consistent monitoring across multi-cluster deployments. Within VCF Automation, a HealthMonitor custom resource can create monitors for tracking backend pool member status using TCP, PING, and HTTP check types.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -6261,19 +6152,17 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides infrastructure for evaluating AI systems for trustworthy behavior, specifically addressing the security dimension of trustworthiness assessment. The validate-then-publish workflow requires MLOps engineers to validate ML models against the security, privacy, and technical requirements of the organization before uploading them to the Model Gallery. This validation includes evaluating models for inference functionality using the Triton Inference Server and examining inference requests for malicious behavior, directly addressing the security evaluation component of trustworthiness.
-Deep learning VMs provisioned from PAIS images are isolated evaluation environments where data scientists and MLOps engineers can assess model behavior before production deployment. These DL VMs run on the same GPU-accelerated workload domains, vGPU profiles, and VM classes used in production, so trustworthiness evaluation occurs under conditions comparable to the deployment environment. Model integrity is verified through hash code validation and unique content digests on each revision, stored as OCI artifacts with immutable manifests, providing cryptographic verification that the evaluated model is the same artifact that reaches production.
-PAIS does not address the anonymization or disaggregation aspects of this control. Data anonymization, de-identification, and disaggregation of captured and stored data are application-layer data governance activities that fall outside the scope of infrastructure-level platform controls.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -6848,19 +6737,17 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides infrastructure for evaluating AI systems for trustworthy behavior, specifically addressing the security dimension of trustworthiness assessment. The validate-then-publish workflow requires MLOps engineers to validate ML models against the security, privacy, and technical requirements of the organization before uploading them to the Model Gallery. This validation includes evaluating models for inference functionality using the Triton Inference Server and examining inference requests for malicious behavior, directly addressing the security evaluation component of trustworthiness.
-Deep learning VMs provisioned from PAIS images are isolated evaluation environments where data scientists and MLOps engineers can assess model behavior before production deployment. These DL VMs run on the same GPU-accelerated workload domains, vGPU profiles, and VM classes used in production, so trustworthiness evaluation occurs under conditions comparable to the deployment environment. Model integrity is verified through hash code validation and unique content digests on each revision, stored as OCI artifacts with immutable manifests, providing cryptographic verification that the evaluated model is the same artifact that reaches production.
-PAIS does not address the anonymization or disaggregation aspects of this control. Data anonymization, de-identification, and disaggregation of captured and stored data are application-layer data governance activities that fall outside the scope of infrastructure-level platform controls.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -8039,19 +7926,17 @@
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides infrastructure that supports AI Test, Evaluation, Validation and Verification (TEVV) activities throughout the model lifecycle. Deep learning VMs provisioned from PAIS images provide dedicated testing environments for AI prototyping, fine-tuning, validation, and inference workloads. These DL VMs run on the same GPU-accelerated workload domains, vGPU profiles, and VM classes used in production, so TEVV activities occur in conditions comparable to the deployment environment.
-The validate-then-publish workflow creates a formal gate for AI deployment. MLOps engineers validate models for inference functionality using the Triton Inference Server and evaluate performance and safety against business use cases, including examination of inference requests for malicious behavior and functional testing. Models must pass this validation before being uploaded to the Model Gallery for production use. Model integrity is verified through hash code validation, and each revision is assigned a unique digest stored as an OCI artifact with an immutable manifest, giving cryptographic verification that the tested model is the same artifact that gets deployed.
-The platform also supports TEVV through its monitoring stack. VCF Operations monitors GPU consumption at cluster, host system, and host properties levels. Each DL VM includes a pre-installed DCGM Exporter with Prometheus collection at 5-second scrape intervals and Grafana visualization, supplying performance telemetry during testing and evaluation. The software stack for running AI applications on top of NVIDIA GPUs is validated in advance, and NVIDIA NGC containers are pre-tested and ready to run, reducing variables during TEVV by providing a known-good baseline.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -10048,48 +9933,27 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>Meets</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>VCF provides integrated tools for near-real-time log analysis, event correlation, incident investigation, and alert escalation across the entire infrastructure stack. It also supports forwarding logs to external SIEM solutions through syslog integration on every major component.
-VCF Operations continuously monitors compute, storage, and networking resources, correlating metrics over time to identify trends and anomalies. Administrators can define alert policies that specify which objects to monitor and what thresholds to apply. Alert definitions can be based on performance metrics, log events, or custom conditions configured through the Management Pack Builder. Metric event symptoms can be configured based on reported violations of metric thresholds from monitored systems, and those symptoms can be incorporated into alert definitions that trigger when conditions are met. Intelligent Alerts group related alerts into clusters based on creation time and topology distance, reducing alert noise so administrators can focus on the most critical issues rather than sifting through thousands of alerts generated by multiple monitoring tools for the same problem. Each alert cluster includes a graphical timeline and an object-relationship chart to help trace root causes. When an alert is triggered, it generates an event that is posted to the event history database for tracking and escalation. VCF Operations can also send alert notifications via SNMP trap to up to four SNMP trap destinations.
-VCF Health, a component of VCF Operations, continuously monitors the operational state of VCF components to verify they are functioning as expected, giving platform operators a single view of operational status. The Platform Health Alerts page provides a centralized view of all alerts related to overall system health, including alerts from data sources and infrastructure nodes. Health alerts are generated for conditions that affect the health of the environment and require immediate attention.
-The Troubleshooting Incidents page in VCF Operations provides a summary of all incidents, including status, entity count for in-progress incidents, and count of top root causes. The interface highlights anomalies in metrics for quick detection and allows filtering metrics and alerts based on metric name, entity name, and other parameters. Correlated metric analysis is available through the incident interface to support root cause investigation. VCF Operations Diagnostics provides a Refresh Findings capability that performs real-time analysis using product logs in the environment where the problem has occurred.
-Event auditing within VCF Operations provides visibility into platform interaction changes across the VCF infrastructure, with insights into suspicious access events and policy violations. Each audit event includes a detailed view containing information that helps administrators analyze events in the virtual infrastructure for suspicious user actions or system issues.
-VCF Operations provides continuous compliance management by monitoring infrastructure against industry-standard benchmarks and custom policies. Administrators can create custom compliance benchmarks that monitor selected alert definitions and policies, tailoring the monitoring posture to organizational requirements. The platform assesses objects based on selected compliance policies and activates alert definitions associated with the current scorecard, providing ongoing visibility into compliance status.
-VCF Log Management provides centralized log aggregation, collecting logs from all VCF components including VMware vCenter, VMware ESX, NSX, vSAN, VCF Automation, VCF Identity Broker, VCF Operations for Networks, and VCF Operations HCX. The platform delivers real-time analytics that allow administrators to search and filter logs instantly for troubleshooting or auditing purposes. Pre-built dashboards, alerts, and queries are available through content packs for each VCF component. Log-based alert definitions allow administrators to trigger notifications when specific log patterns appear across monitored systems. Log analysis charts support aggregation functions and grouping types for investigating patterns across the environment. VCF Operations and VCF Log Management must be integrated to implement the centralized log collection architecture.
-VCF supports forwarding logs to external SIEM or syslog targets on every major component. vCenter syslog forwarding can be configured through both the UI and the vCenter Management API, supporting TCP, UDP, TLS, and RELP protocols. The API provides endpoints for setting the forwarding configuration, retrieving the current configuration, and testing the connection with remote syslog servers. The vCenter Appliance Management Interface supports up to three remote syslog destination hosts. ESX hosts can forward syslog messages to remote collectors through the VMware Host Client by configuring the Syslog.global.logHost setting, using the format protocol://hostname:port where protocol can be UDP, TCP, or SSL. NSX Manager can export syslog to a remote server with configurable protocol, port, and log level, and supports TLS on port 6514 for encrypted log transmission. The Foundation Load Balancer supports log forwarding to syslog servers. VCF Operations supports remote syslog host configuration through Host System Properties. VCF Operations HCX automatically forwards logs from both the manager and appliance virtual machines once configured. VCF Operations for Networks supports per-cluster syslog server configuration, with the option for individual collectors to use different syslog destinations. vSphere Supervisor forwards control plane logs to external syslog servers using Fluent Bit with RFC 5424 message format over TCP, with configurable host, port, and transport mode. Log forwarding supports TLS encryption for confidentiality in transit.
-At the vSphere layer, the alarm infrastructure integrates with events and performance counters for real-time alerting. The MetricAlarmExpression data object allows administrators to set alarms on specific performance metrics with configurable monitoring intervals and aggregation functions for processing data points. The alarm system supports automating actions and sending different types of notification in response to certain server conditions. The vSphere Client provides direct visibility into tasks and events for change tracking.
-The monitoring platform extends beyond VCF's core infrastructure. When VCF Automation is integrated with VCF Operations, the Insights dashboard and Alerts tab provide real-time capacity awareness and alert information for VCF Automation objects, giving IT teams visibility into resource usage across both provisioned workloads and the underlying infrastructure. The Management Pack Builder allows administrators to set up event definitions for integrated systems, monitoring specific conditions or thresholds and configuring alerts for proactive management. Adapters can be installed on VCF Operations nodes to extend monitoring to additional systems and data sources beyond the core VCF components.
-VCF Operations supports flexible grouping and scheduling to align monitoring with operational realities. Custom groups can be configured with automatic membership criteria to support monitoring strategies and achieve a high level of automation. Maintenance schedules can be assigned to objects undergoing planned downtime to keep monitoring data accurate and avoid false alerts when an object is offline for scheduled maintenance.
-At the network layer, NSX provides monitored indicators including node uptime status, deployment status, management and controller connections, tunnel status, PNIC status, and uptime duration. NSX time series APIs allow viewing data such as VPN statistics, including metadata about the number of tunnels configured and how many are up or down at a given time. NSX Live Traffic Analysis monitors live traffic at a source or between source and destination, with packet capture to identify packet drops and bad flows between endpoints. Starting with NSX 4.2, Live Traffic Analysis sessions can capture real-time debug statistics from data path kernel-level modules on ESX host transport nodes.
-VCF Operations also supports self-monitoring through the VCF Operations adapter, which collects internal metrics such as analytics operation counts, threshold check durations, and incoming observation sizes. This allows administrators to verify that the monitoring platform itself is functioning correctly. The VCF Operations policy engine monitors conditions and generates events to react to changing states in the orchestrator server or connected technologies. The Adapter Instance monitoring interval is configurable, with intervals as granular as five minutes.
-VMware Private AI Services (PAIS) provides observability infrastructure that supports near real-time monitoring of AI workload activity and emits the data streams that an external Security Incident Event Manager (SIEM) or analytics platform consumes for analysis and incident escalation.
-PAIS exposes a Prometheus runtime that is activated through the observability section of the PAISConfiguration custom resource, with a configurable storage class policy and a metrics retention period. The Prometheus metrics endpoint is reachable at the PAIS FQDN or IP address so that external monitoring systems can scrape operational data in near real time. PAIS metrics are visualized in observability platforms such as Grafana and VCF Operations, and a single Grafana instance can visualize metrics from multiple PAIS instances when they share the same OIDC provider. The Grafana dashboards expose operationally relevant signals including LLM completion API response times at the 95th percentile, inference engine tokens-per-second generation rate, and GPU compute and memory utilization. For the VCF Operations integration, PAIS Controller metrics are collected through Telegraf with namepass filters configured to capture controller_runtime_active_workers, controller_runtime_max_concurrent_reconciles, workqueue_depth, and workqueue_longest_running_processor. The PAIS Prometheus server authenticates clients using Forward OAuth identity.
-For AI inference traceability, PAIS supports forwarding LLM traces to an external OpenTelemetry Collector, configured by uncommenting the spec.observability.llmTraces section of the PAISConfiguration custom resource. Traces are transmitted over HTTP/Protobuf or gRPC. Authentication to the collector is configured through a Kubernetes Secret containing Authorization Bearer tokens and custom headers. When LLM trace collection is active, operators and security teams can analyze traces from agents and knowledge base indexing in the OpenTelemetry Collector, producing behavioral visibility that can feed into incident analysis workflows. The vLLM inference engine that runs completion models on GPU supports a configurable logging level through the VLLM_LOGGING_LEVEL environment variable for additional diagnostic detail.
-For Deep Learning VM workloads, PAIS deploys a DCGM Exporter virtual machine that integrates with NVIDIA DCGM, Prometheus, and Grafana to export vGPU performance metrics. Prometheus and Grafana are deployed as Docker services on a visualization VM to collect and visualize DCGM metrics from Deep Learning VMs running the DCGM exporter, supporting near real-time GPU performance monitoring.
-To support SIEM integration, administrators should activate the PAIS observability sections and direct the Prometheus and OpenTelemetry data streams to the SIEM, security analytics platform, or VCF Log Management deployment that performs the near real-time analysis and incident escalation. PAIS itself does not implement SIEM correlation or automated escalation; that capability is provided by the external platform that consumes these streams.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend does not function as a SIEM but contributes to near real-time analysis by generating structured security event data from multiple enforcement and detection engines, supporting forwarding of that data to external log management and SIEM platforms, and providing native dashboards that surface security events, intrusion trends, and anomalies.
-Security Services Platform (SSP) supports syslog forwarding to remote servers with TCP, UDP, or TLS-encrypted transport, configurable through the SSP UI under Server Configurations &gt; Add Platform Syslog Server or via REST API. The License Hub component within SSP can independently be configured to send logs to a remote syslog server by specifying a server FQDN or IP address, protocol, and port. Malware Prevention Service log forwarding supports UDP delivery with configurable log level and message ID filtering (SECURITY, MONITORING), and can be configured for TLS-encrypted delivery using client certificates and keys. IDS/IPS events support independent syslog forwarding, enabling security operations teams to route detection events to a centralized log management or SIEM platform.
-The Security Overview Dashboard's Threat Event Monitoring view provides near real-time visibility into security events: a timeline graph of intrusion events categorized by Intrusion Severity, a radar chart showing distribution by Attack Type, Attack Target, or Severity over a configurable window of 24 hours to 14 days, the top IPs and VMs subject to intrusion attempts filtered by Vulnerability Severity criteria, and counts of unique intrusion signatures detected per severity category. Firewall Insights provides time-series data visualizations for historical firewall activity trends. Security Intelligence categorizes detected suspicious traffic events by impact type (Critical, High, Medium, and Low) to help prioritize response actions, and detects and categorizes suspicious events using MITRE tactics and techniques over the selected time period.
-Through the Security Explorer interface, Security Intelligence detects intrusion events in real time with filtering by compute and IDS Signature ID, and provides a View Full Event History capability that displays all events associated with a signature ID and intrusion severity. Network Detection and Response (NDR) and IDS/IPS support date range filtering for event detail review, enabling temporal analysis of security events and intrusion attempts. Security teams can investigate individual threat events and correlated campaigns through the SSP interface to assess impact, identify root causes, and take appropriate mitigation actions. The Process Analysis Report for fileless and file-based malware provides a downloadable packet capture (PCAP) file for detailed process inspection analysis. The Metrics API provides programmatic access to firewall and network monitoring metrics, supporting Point-in-Time queries for current state, Top-N analysis, and time-interval aggregated queries over configurable windows.
-Organizations must deploy a dedicated SIEM or equivalent platform to fulfill the full requirements of this control, including cross-source event correlation, normalization, and automated incident escalation workflows.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -10114,15 +9978,12 @@
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N127" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides a native alerting framework that processes system events and metrics against user-defined rules and generates near real-time notifications through multiple channels. When audit record failures occur across the Events, Syslog, or Splunk subsystems, the Avi Controller and Service Engine log those failures and route them to configured notification destinations.
-The Avi Controller supports four alert notification channels: email, external syslog servers, SNMP trap receivers, and ControlScripts. These are configured in the Operations &gt; Notifications page of the Controller UI. The Controller cluster leader issues SNMP trap notifications based on system events, and multiple SNMP servers can be configured for redundancy. Both SNMPv2c and SNMPv3 protocols are supported for SNMP trap delivery. SNMP notifications can be configured with TLS encryption and strict certificate verification for secure transport to monitoring infrastructure.
-For syslog-based notification, Avi provides the Syslog-Audit-Persistence mechanism, which streams alert events to external syslog servers. Alert events can be delivered using the SYSLOG_RFC5425_ENHANCED format for structured notification delivery. Syslog notifications push alert events to syslog servers; virtual service logs must be separately retrieved from the Controller through the API or pushed to a remote destination using a ControlScript.
-The Avi Controller and Service Engine log audit record failures for trusted channel initiation, termination, and function failures to the Events, Syslog, and Splunk subsystems. Custom alert configurations allow administrators to map specific system events to specific notification actions. The Controller also executes ControlScripts when alert conditions are triggered, generating detailed execution logs including operation status and error conditions. Avi Event Logs provide an audit trail that records system activities and configuration changes with information about who made them and when.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -10360,19 +10221,17 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) supports domain expert validation through a structured role-based workflow built around a validated-model gallery, container-registry model storage, and approval gates for agent tooling. The platform separates responsibilities so that domain-appropriate experts review AI systems at each stage, with MLOps engineers acting as the designated domain expert for model quality and safety within the PAIS workflow.
-MLOps engineers validate ML models onboarded to PAIS against the security, privacy, and technical requirements of the organization before the models are made available for downstream use. Validated models are stored in a Harbor registry that acts as the model storage backend, with authentication and certificate-based trust for retrieval; OCI-compliant registries from other vendors are also supported, including in disconnected environments. A central model gallery is the recommended store for ML models, providing centralized management and consistency across deployment targets, which gives reviewers a single inventory to assess and approve before promotion.
-For agent-based AI applications, PAIS requires examination and approval of Model Context Protocol (MCP) server tools and capabilities before they are used in agents, and the Agent Builder maintains a list of approved tools for use when connecting to MCP servers. Deep learning VMs give domain experts hands-on environments to prototype, fine-tune, and validate model behavior before promotion. When deploying completion or embedding model endpoints, A/B testing is recommended so that reviewers can compare candidate models in real-world settings. Catalog items for AI applications provisioned through VCF Automation, together with PAIS observability surfaced in platforms such as Grafana, give reviewers the operational signals needed to validate that AI systems perform consistently after release.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr">
@@ -12006,41 +11865,27 @@
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to post-deployment monitoring of AI workloads through VCF Operations, which provides continuous health, performance, and capacity monitoring for the infrastructure hosting those workloads. VCF Operations dashboards surface CPU, memory, storage, and network metrics for VMs running AI workloads. VCF Log Management aggregates and analyzes log data from VMware vCenter, VMware ESX, and NSX components. vCenter alarms provide threshold-based alerting for infrastructure conditions that could affect AI workload availability.
-For AI workloads running as containerized applications on VMware Kubernetes Service (VKS) clusters, the platform extends infrastructure-level observability to the Kubernetes layer. VKS clusters provisioned with the automated-monitoring label automatically receive monitoring configuration on each new node, integrating cluster telemetry with VCF Operations. The Prometheus standard package, installable on VKS clusters through the Supervisor Management Proxy Service, deploys kube-state-metrics, node-exporter, pushgateway, Prometheus, and Alertmanager as components. The prometheus-kube-state-metrics component monitors node status and capacity, ReplicaSet compliance, pod status, job and CronJob status, and resource requests and limits, providing continuous metric collection that can be directed at AI inference services or training job pods. Telegraf is available as a standard package that deploys as a Deployment component to scrape metrics from kube-state-metrics and node-exporter and forward them to external observability backends. Monitoring and alerting for Kubernetes deployments is also available through the Argo CD Supervisor Service using Grafana Operator and Prometheus.
-Kubernetes-native health probes and status tracking support workload condition detection at the pod level. Liveness and readiness probes can be configured on AI workload containers to detect unresponsive or overloaded model serving instances; a readiness probe removes the pod from service routing when it cannot handle requests, and a liveness probe triggers a container restart when the application becomes unresponsive. The Kubernetes Deployment controller continuously monitors running application instances and automatically replaces instances when nodes fail or are removed from service, providing a self-healing mechanism that addresses machine failure or maintenance. Kubernetes DeploymentStatus exposes observedGeneration and conditions fields with type, status, lastTransitionTime, and reason values, allowing operators to detect rollout failures, stuck deployments, or configuration drift from the expected specification. VKS cluster management proactively monitors the cluster estate to verify that assigned policies are enforced correctly, and generates Policy Insights when configuration conflicts or environmental errors are detected.
-For organizations using Harness CI/CD on VKS, Dynatrace integration provides full-stack observability including application performance monitoring, infrastructure monitoring, and digital experience monitoring. The Dynatrace operator automates deployment, scaling, and maintenance of the monitoring stack within VKS clusters, and automatically correlates application deployment service metrics with underlying VKS infrastructure including nodes, pods, and the network. The Dynatrace AI engine detects anomalies, identifies root causes, and provides intelligent alerts. Harness SRM monitors deployed services post-deployment to calculate a real-time health score based on transaction success and latency.
-The VCF Automation Monitor tab provides deployment health information drawn from VCF Operations, and deployment cards in the self-service catalog surface deployment state, last request status, and operational history for workload deployments. AI-specific behavior monitoring (model accuracy drift, output quality) requires application-level tooling outside VCF's scope.
-VMware Private AI Services (PAIS) provides AI-specific monitoring mechanisms that support continuous post-deployment observation of AI workloads on VCF.
-At the PAIS layer, observability is activated by updating the PAISConfiguration custom resource with parameters that enable metrics collection and forward large language model traces to an OpenTelemetry Collector. PAIS deploys a Prometheus server pod for metrics collection that must be ready and running for observability to function, configured with a chosen storage class and a configurable metrics retention period. PAIS controller pod metrics are integrated into observability platforms through Telegraf configuration in the Supervisor instance, and the telegraf-user-config ConfigMap in the vmware-system-monitoring namespace manages user-configured monitoring endpoints for PAIS. The PAIS Supervisor Service exposes service-level metrics through pais.vmware.com that VI administrators access to monitor the health of the service.
-DevOps engineers visualize PAIS health and performance metrics in observability platforms such as Grafana, where dashboards report pod restart frequency, vGPU licensing status, and idle or underutilized GPU devices in passthrough mode. VI administrators visualize PAIS controller pod operation metrics in VCF Operations using the same metrics pipeline. MLOps engineers and application developers track the health, quality, and behavior of AI applications and the models used in agents through Grafana, supporting continuous observation of inference behavior. Model Endpoint deployment status can be verified using the kubectl get modelendpoints command, which returns the Ready status for each deployed endpoint, and the vcf cluster command-line interface provides cluster provisioning monitoring, registration, and kubeconfig retrieval for VKS clusters that host AI workloads. PAIS deployment leases can be configured to bound how long a deployment can exist, supporting lifecycle oversight of catalog-deployed AI workloads.
-Enabling these observability features, defining retention and alerting policy, and acting on monitoring signals are organizational process responsibilities. PAIS provides the monitoring infrastructure and integration points, but continuous post-deployment monitoring as a practice requires the organization to assign operational ownership, review observability data on an ongoing basis, and respond to anomalies in AI workload behavior.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to proactive and continuous monitoring of deployed AI workloads running on VCF through multiple layers of ongoing network-level security monitoring.
-Security Intelligence continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic, enabling ongoing policy adjustments as workloads evolve. It also monitors infrastructure services to detect newly deployed servers. A classification cron job runs automatically at 2:00 AM local time and repeats every 24 hours, evaluating traffic flows from the preceding 30 days to classify compute entities providing network infrastructure services. When the Recommendations Monitoring feature is enabled, Security Intelligence checks every hour for changes in the scope of monitored entities, allowing policy recommendations to remain current as AI workloads change. The Security Intelligence Flow Insights Dashboard supports detection and display of MITRE ATT&amp;CK framework tactics and techniques, showing counts of detected suspicious events per tactic and technique during a selected time period.
-Segmentation Monitoring provides dedicated views for environment-level traffic flows, accessible through the Monitor &amp; Plan interface. Administrators can monitor traffic between configured environment pairs, view flows related to detected infrastructure servers within specified time intervals, and export all unique flows to a CSV file for offline analysis or compliance evidence. The Environments monitoring window provides assessment of current security posture and enables improvement actions for environment pairs. When no protection policy is configured for an environment pair, Segmentation Monitoring offers a Run Recommendations option to generate policy recommendations, closing monitoring gaps around AI workloads.
-The Security Services Platform (SSP) collects metrics to monitor the readiness and performance of vDefend IDS/IPS in the environment. IDS/IPS engine statistics accessible per host include uptime, alert count, suppressed alerts, alert queue overflow status, engine ID, and last reload timestamp. IDS/IPS monitoring dashboards can be scoped to custom projects, displaying events triggered for that project only. For bare metal deployments, Bare Metal Agents stream metrics and detailed host-level telemetry to the SSP. The NDR Sensor periodically checks the status of activated features on the SSP every 15 minutes and updates its configuration accordingly.
-Intelligent Assist provides AI-assisted analysis within the NSX Manager UI and SSP UI, displaying on the IDS/IPS, Detections, and Campaigns pages to help administrators interpret monitoring data.
-Malware Prevention Service provides deployment status monitoring at the cluster level and per-node level, displaying deployment errors and individual transport node status. Network Detection and Response (NDR) applies behavioral analysis to detect suspicious activity targeting monitored workloads and correlates events into campaigns for investigation.
-Monitoring AI system functionality at the application layer, including model performance, output quality, and behavioral drift, is outside vDefend's domain.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
@@ -12600,20 +12445,17 @@
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) supports differentiated roles and responsibilities across the AI workload lifecycle through platform-level access controls layered on the VCF identity model. Platform administrators manage infrastructure setup: they deploy infrastructure, configure GPU-accelerated workload domains, and add the PAIS supervisor service to the supervisor before any AI workloads can be deployed. This role controls the foundational infrastructure on which AI operations depend.
-Organization administrators control namespace imports and grant permissions for AI catalog items. The organization administrator token is required for API calls that import namespaces into VCF Automation organizations, centralizing oversight of which AI capabilities are exposed. Organization administrators must grant permissions before users can request AI catalog items, providing a gatekeeping function over AI deployments.
-DevOps engineers are scoped to project and namespace membership for provisioning GPU-accelerated VMware Kubernetes Service (VKS) clusters and related infrastructure. Data scientists and MLOps engineers provision models and retrieval-augmented generation (RAG) applications through PAIS. The MLOps role carries specific validation responsibilities: MLOps engineers validate ML models against the security, privacy, and technical requirements of the organization before uploading them to the model gallery, including testing inference functionality and evaluating performance and safety against business use cases.
-Access to PAIS is authorized through OIDC groups specified in the authorizedGroups configuration, tying role enforcement to VCF SSO. Namespace-scoped permissions confine each role's actions to assigned boundaries within the platform.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G161" s="10" t="inlineStr">
@@ -12747,41 +12589,27 @@
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to post-deployment monitoring of AI workloads through VCF Operations, which provides continuous health, performance, and capacity monitoring for the infrastructure hosting those workloads. VCF Operations dashboards surface CPU, memory, storage, and network metrics for VMs running AI workloads. VCF Log Management aggregates and analyzes log data from VMware vCenter, VMware ESX, and NSX components. vCenter alarms provide threshold-based alerting for infrastructure conditions that could affect AI workload availability.
-For AI workloads running as containerized applications on VMware Kubernetes Service (VKS) clusters, the platform extends infrastructure-level observability to the Kubernetes layer. VKS clusters provisioned with the automated-monitoring label automatically receive monitoring configuration on each new node, integrating cluster telemetry with VCF Operations. The Prometheus standard package, installable on VKS clusters through the Supervisor Management Proxy Service, deploys kube-state-metrics, node-exporter, pushgateway, Prometheus, and Alertmanager as components. The prometheus-kube-state-metrics component monitors node status and capacity, ReplicaSet compliance, pod status, job and CronJob status, and resource requests and limits, providing continuous metric collection that can be directed at AI inference services or training job pods. Telegraf is available as a standard package that deploys as a Deployment component to scrape metrics from kube-state-metrics and node-exporter and forward them to external observability backends. Monitoring and alerting for Kubernetes deployments is also available through the Argo CD Supervisor Service using Grafana Operator and Prometheus.
-Kubernetes-native health probes and status tracking support workload condition detection at the pod level. Liveness and readiness probes can be configured on AI workload containers to detect unresponsive or overloaded model serving instances; a readiness probe removes the pod from service routing when it cannot handle requests, and a liveness probe triggers a container restart when the application becomes unresponsive. The Kubernetes Deployment controller continuously monitors running application instances and automatically replaces instances when nodes fail or are removed from service, providing a self-healing mechanism that addresses machine failure or maintenance. Kubernetes DeploymentStatus exposes observedGeneration and conditions fields with type, status, lastTransitionTime, and reason values, allowing operators to detect rollout failures, stuck deployments, or configuration drift from the expected specification. VKS cluster management proactively monitors the cluster estate to verify that assigned policies are enforced correctly, and generates Policy Insights when configuration conflicts or environmental errors are detected.
-For organizations using Harness CI/CD on VKS, Dynatrace integration provides full-stack observability including application performance monitoring, infrastructure monitoring, and digital experience monitoring. The Dynatrace operator automates deployment, scaling, and maintenance of the monitoring stack within VKS clusters, and automatically correlates application deployment service metrics with underlying VKS infrastructure including nodes, pods, and the network. The Dynatrace AI engine detects anomalies, identifies root causes, and provides intelligent alerts. Harness SRM monitors deployed services post-deployment to calculate a real-time health score based on transaction success and latency.
-The VCF Automation Monitor tab provides deployment health information drawn from VCF Operations, and deployment cards in the self-service catalog surface deployment state, last request status, and operational history for workload deployments. AI-specific behavior monitoring (model accuracy drift, output quality) requires application-level tooling outside VCF's scope.
-VMware Private AI Services (PAIS) provides AI-specific monitoring mechanisms that support continuous post-deployment observation of AI workloads on VCF.
-At the PAIS layer, observability is activated by updating the PAISConfiguration custom resource with parameters that enable metrics collection and forward large language model traces to an OpenTelemetry Collector. PAIS deploys a Prometheus server pod for metrics collection that must be ready and running for observability to function, configured with a chosen storage class and a configurable metrics retention period. PAIS controller pod metrics are integrated into observability platforms through Telegraf configuration in the Supervisor instance, and the telegraf-user-config ConfigMap in the vmware-system-monitoring namespace manages user-configured monitoring endpoints for PAIS. The PAIS Supervisor Service exposes service-level metrics through pais.vmware.com that VI administrators access to monitor the health of the service.
-DevOps engineers visualize PAIS health and performance metrics in observability platforms such as Grafana, where dashboards report pod restart frequency, vGPU licensing status, and idle or underutilized GPU devices in passthrough mode. VI administrators visualize PAIS controller pod operation metrics in VCF Operations using the same metrics pipeline. MLOps engineers and application developers track the health, quality, and behavior of AI applications and the models used in agents through Grafana, supporting continuous observation of inference behavior. Model Endpoint deployment status can be verified using the kubectl get modelendpoints command, which returns the Ready status for each deployed endpoint, and the vcf cluster command-line interface provides cluster provisioning monitoring, registration, and kubeconfig retrieval for VKS clusters that host AI workloads. PAIS deployment leases can be configured to bound how long a deployment can exist, supporting lifecycle oversight of catalog-deployed AI workloads.
-Enabling these observability features, defining retention and alerting policy, and acting on monitoring signals are organizational process responsibilities. PAIS provides the monitoring infrastructure and integration points, but continuous post-deployment monitoring as a practice requires the organization to assign operational ownership, review observability data on an ongoing basis, and respond to anomalies in AI workload behavior.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G163" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend (vDefend) contributes to proactive and continuous monitoring of deployed AI workloads running on VCF through multiple layers of ongoing network-level security monitoring.
-Security Intelligence continuously monitors for new flows between environments and alerts administrators to unauthorized or unexpected traffic, enabling ongoing policy adjustments as workloads evolve. It also monitors infrastructure services to detect newly deployed servers. A classification cron job runs automatically at 2:00 AM local time and repeats every 24 hours, evaluating traffic flows from the preceding 30 days to classify compute entities providing network infrastructure services. When the Recommendations Monitoring feature is enabled, Security Intelligence checks every hour for changes in the scope of monitored entities, allowing policy recommendations to remain current as AI workloads change. The Security Intelligence Flow Insights Dashboard supports detection and display of MITRE ATT&amp;CK framework tactics and techniques, showing counts of detected suspicious events per tactic and technique during a selected time period.
-Segmentation Monitoring provides dedicated views for environment-level traffic flows, accessible through the Monitor &amp; Plan interface. Administrators can monitor traffic between configured environment pairs, view flows related to detected infrastructure servers within specified time intervals, and export all unique flows to a CSV file for offline analysis or compliance evidence. The Environments monitoring window provides assessment of current security posture and enables improvement actions for environment pairs. When no protection policy is configured for an environment pair, Segmentation Monitoring offers a Run Recommendations option to generate policy recommendations, closing monitoring gaps around AI workloads.
-The Security Services Platform (SSP) collects metrics to monitor the readiness and performance of vDefend IDS/IPS in the environment. IDS/IPS engine statistics accessible per host include uptime, alert count, suppressed alerts, alert queue overflow status, engine ID, and last reload timestamp. IDS/IPS monitoring dashboards can be scoped to custom projects, displaying events triggered for that project only. For bare metal deployments, Bare Metal Agents stream metrics and detailed host-level telemetry to the SSP. The NDR Sensor periodically checks the status of activated features on the SSP every 15 minutes and updates its configuration accordingly.
-Intelligent Assist provides AI-assisted analysis within the NSX Manager UI and SSP UI, displaying on the IDS/IPS, Detections, and Campaigns pages to help administrators interpret monitoring data.
-Malware Prevention Service provides deployment status monitoring at the cluster level and per-node level, displaying deployment errors and individual transport node status. Network Detection and Response (NDR) applies behavioral analysis to detect suspicious activity targeting monitored workloads and correlates events into campaigns for investigation.
-Monitoring AI system functionality at the application layer, including model performance, output quality, and behavioral drift, is outside vDefend's domain.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
@@ -12806,16 +12634,12 @@
       </c>
       <c r="M163" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N163" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides application-layer logical security mechanisms that help protect traffic carrying personal data. At the transport layer, Avi supports SSL/TLS termination with certificate management, securing connections between clients and the application proxy and helping protect sensitive data from unauthorized interception or modification in transit (CLI Access Settings &gt; Certificates). For Kubernetes workloads, the Avi Kubernetes Operator (AKO) supports PKIProfile configuration, which enables secure communication with backend services through certificate-based authentication and encryption (Designing and Deploying AKO &gt; Setting up Routing Rules using CRDs &gt; PKIProfile).
-For application logging, the Avi Analytics Profile supports the creation of a sensitive log profile that governs how sensitive data is handled within client-side logs (Load Balancing &gt; Analytics Profile &gt; Client Log). Administrators can configure which fields are captured in client logs to limit inadvertent recording of personal data transmitted through applications. TLS persistence data, used to maintain session affinity across Service Engines, is stored in an encrypted format that a Service Engine can read if a client reconnects to a different Service Engine, reducing exposure of session-bound data throughout the persistence lifetime (Load Balancing &gt; Persistence &gt; TLS Persistence).
-Client access to applications can be controlled through authentication profiles. Avi supports LDAP Authentication Profiles configurable with LDAPS for encrypted directory connections, validating user identities against a directory service before granting access to application resources (User Authentication and Authorization &gt; Authentication Profile &gt; LDAP Authentication Profile). Avi also supports OAuth 2.0 and OpenID Connect (OIDC) for secure delegated client authentication, enabling identity providers to issue tokens to third-party applications without exposing user credentials directly (Security &gt; Client Authentication &gt; OAuth and OIDC).
-Multi-tenant data plane isolation depends on context configuration. When Tenant Context is used, Avi provides both control plane and data plane isolation, scoping application traffic to designated tenant resources and supporting multi-tenant deployments where each tenant's traffic remains separated. When Provider Context is used, only control plane isolation is provided; organizations requiring full data plane separation should configure Tenant Context accordingly (Tenant Settings &gt; Tenants Versus SE Group Isolation).
-Health monitor probes in secure environments should use encrypted credentials; Avi supports reconfiguring existing health monitors from plaintext credentials to encrypted form when encrypted authentication is required (Load Balancing &gt; Health Monitoring &gt; HTTP Health Monitor). For deployments with stringent cryptographic requirements, Avi supports FIPS 140-3 compliance, which requires stricter handling of keys, authentication data, and random number generation to help protect sensitive security parameters (FIPS Compliance in Avi Load Balancer &gt; FIPS 140-3 Compliance). For Avi Controller deployments automated via Ansible, Ansible Vault can be used to securely store sensitive variables such as passwords and API tokens, reducing the risk of credential exposure during automated provisioning (Automation Tools Overview &gt; Ansible).</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -12981,19 +12805,17 @@
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E166" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides mechanisms for validating the source and quality of pre-trained models before they enter the deployment pipeline. Models must be downloaded into a Deep Learning VM from trusted sources such as the NVIDIA NGC catalog, Hugging Face, or another model hub before validation. Inside the Deep Learning VM, the validation workflow performs integrity verification through hash code checking, malware scanning, serialization attack scanning, and inference testing with the Triton Inference Server. MLOps engineers validate onboarded models against the security, privacy, and technical requirements of the organization, and the documentation recommends distributing internally validated models from a central gallery rather than pulling models directly from the internet, which can carry malicious code or be tuned for malicious behavior.
-After validation, models are uploaded to the PAIS Model Gallery, which stores ML models that can be referenced by URL for deployment on CPU or GPU infrastructure. The Model Gallery sits behind a Harbor registry service running in the Supervisor and supports OCI-compliant registries from other vendors for connected and disconnected environments. Access to the Harbor registry requires authentication and certificate-based trust for model retrieval, which restricts access to the validated model store. The vcf pais commands support automated CI/CD upload of validated models for MLOps pipelines and provide a consistent mechanism for promoting models from validation to publication.
-PAIS Model Runtime serves validated models as Model Endpoints paired with inference engines such as vLLM, llama.cpp, or Infinity, and the endpoints are reachable through the PAIS REST API or through agents in Agent Builder in VCF Automation. The guidance recommends A/B testing between embedding models in real-world settings to compare performance, and MLOps engineers and application developers can perform monitoring and diagnostics through observability platforms such as Grafana to track the health, quality, and behavior of AI applications running on PAIS, supporting ongoing quality validation after a model has been admitted to production.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G166" s="10" t="inlineStr">
@@ -13590,20 +13412,17 @@
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides explicit data source identification and tracking for AI workloads. The Data Indexing and Retrieval service offers a Knowledge Bases interface where users create and manage knowledge bases, and a knowledge base can be linked to up to ten data sources. Each data source is created with a name, description, type, and the required properties for retrieving content from its original location, and a single data source can be linked to multiple knowledge bases. The data source type is fixed at creation. Supported data source types include Microsoft SharePoint sites, Amazon S3 compatible stores, and other enterprise content management systems. Each data source stores the credentials required for retrieval, such as service account key file information when applicable, which creates a documented connection between the AI system and its data origins.
-During knowledge base indexing, PAIS tracks document-level detail including crawled documents, new documents found, deleted documents, existing unmodified documents, existing modified documents requiring embedding updates, and skipped documents. It captures size metrics including total megabytes downloaded, new chunks indexed corresponding to inference server invocations for embeddings, and final index size after removal of deleted documents. It records timing metrics for download, embedding generation, and the overall index operation. Document counts returned by retrieval queries are tracked, and counts of documents per media type such as PDF and PPTX are maintained for each knowledge base. Automatic collection and indexing of updates from linked data sources over time keeps these records current.
-For runtime visibility, PAIS supports LLM trace collection through an OpenTelemetry Collector by configuring the spec.observability.llmTraces section of the PAISConfiguration custom resource, with traces transmitted over HTTP/protobuf or gRPC. PAIS metrics, including knowledge base activity, can be visualized in third-party observability platforms such as Grafana. The Data Indexing and Retrieval component also implements a Model Context Protocol (MCP) server that exports a set of search tools for each knowledge base, which gives downstream AI applications a documented programmatic surface tied back to specific data sources. PAIS AI catalog items, including AI Workstation, DSM Database, Triton Inferencing Server, and AI Kubernetes Cluster, are added to the VCF Automation catalog by running the PAIS Quickstart, with required images uploaded in advance to a Harbor registry in disconnected environments.
-Organizational decisions about which data sources are approved for AI use, how data lineage is documented outside the platform, and how training data provenance is governed remain the responsibility of the organization. PAIS supplies the technical registration and tracking infrastructure that the organization configures and operates.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G174" s="10" t="inlineStr">
@@ -14177,23 +13996,17 @@
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E182" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F182" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several capabilities that contribute to anomalous behavior detection and user activity monitoring, though it does not include a dedicated User &amp; Entity Behavior Analytics (UEBA) or User Activity Monitoring (UAM) solution.
-VCF Operations includes anomaly detection capabilities that use both dynamic and static thresholds to identify when metrics deviate from normal operating behavior. Dynamic thresholding is enabled by default and uses historical data analysis to establish baselines for each monitored object. The Smart Early Warning feature analyzes the number of applicable metrics that violate the dynamic threshold determining normal operating behavior, triggering alerts when the number of anomalies on an object exceeds a trending threshold. When an anomalous entity is detected, VCF Operations generates an outlier violation alert (vmwAnalyticsOutlierEvent, OID 37002), notifying administrators of unexpected behavior. A Critical threshold violation alert is also generated when anomalous entities are detected.
-The Anomalies widget displays detected anomalies for a resource over the past six hours at configurable time intervals, with color-coded criticality indicators. The Anomaly Breakdown widget shows likely root causes for symptoms on a selected resource, helping operators triage issues. The Troubleshooting Workbench includes an Anomalous Metrics card that surfaces metrics exhibiting drastic changes within a selected scope and time window, ranked by degree of change with the most recent anomaly given the highest weighting. Administrators can also examine outlier VMs detected by VCF Operations to identify unexpected behavior and take corrective actions. VCF Operations supports outbound SNMP trap notifications, enabling alert delivery to external SNMP management systems with up to four configurable trap destinations.
-For user activity monitoring, VCF Operations provides a User Activity Audit report that offers traceability of user actions including logging in, operations on clusters and nodes, changes to system passwords, certificate activation, and logging out. Each audit event has a detailed view containing information that supports analysis of events in the virtual infrastructure for suspicious user actions or system issues. Event auditing across the VCF platform provides visibility into platform interaction changes and surfaces suspicious access events and policy violations. Administrators should continuously monitor user security aspects to detect security risks early and respond to potential threats. VCF SSO maintains a dedicated audit log that captures user management events, including account creation, modification, deletion, and activation or deactivation, as well as changes to account credentials and profile information. The vSphere Client's Advanced Export feature allows administrators to export tasks performed by a specific user during a specified time range, providing targeted audit data for investigating suspicious activity.
-Audit logging extends across VCF components. NSX Manager generates audit log messages that record user operations with fields for UserName, ModuleName, Operation, and Operation status, along with detailed resource change information and timestamps. NSX Manager audit logs also record failed login attempts with username and timestamp information, enabling tracking of access patterns across the environment. VCF Operations for Networks captures audit logs of administrative actions, including CRUD operations and login/logout events.
-VCF Operations supports forwarding user activity audit logs to an external syslog server, enabling integration with dedicated SIEM or UEBA platforms for broader correlation and behavioral analysis. VCF Log Management includes content packs that offer pre-built dashboards, alerts, and queries for VCF components. These content packs support security monitoring use cases such as tracking failed login attempts and privilege escalations.
-VCF's built-in anomaly detection is primarily oriented toward infrastructure metrics and operational health rather than user behavior profiling. A dedicated UEBA or UAM solution consuming VCF's audit data would be needed to establish user behavior baselines, detect credential compromise through behavioral deviation, and provide the full scope of analytics this control requires. For organizations requiring deeper behavioral analysis, VMware vDefend extends VCF's monitoring foundation with IDS/IPS, network traffic inspection, and threat intelligence integration.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G182" s="10" t="inlineStr">
@@ -14228,16 +14041,12 @@
       </c>
       <c r="M182" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N182" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides application-layer anomaly detection mechanisms that contribute to meeting this control. The Anomalies Overlay feature, available in Virtual Service Analytics, Service Engine Analytics, and Pool Analytics, flags statistical deviations in traffic metrics as anomaly events when a specific metric deviates from the historical norm by more than four sigma during the anomaly period. Monitored metrics include CPU utilization, bandwidth, disk I/O, server response time, and connection rates. Each anomaly event is identified by entity name, entity type (Virtual Machine, Virtual Service, or Service Engine), and metric value, with a timestamp indicating when the deviation occurred. Anomaly detection operates against a moving-average baseline calculated from recent historical traffic. The Pool Anomalies Overlay also displays prediction interval upper and lower bounds alongside the anomalous value. Administrators can adjust detection granularity by changing the statistics time interval, and can configure alert filter sensitivity to tune the threshold for new alert generation. Note that anomaly recording is disabled when the statistics interval is set to Real Time; a non-real-time statistics interval is required for anomaly capture to function.
-The Bot Management module adds a behavioral detection layer focused on credential stuffing and web attack patterns at the application proxy boundary. Bot Management detects malicious bots responsible for online fraud and credential stuffing attacks. The IP Reputation service extends detection by maintaining a database of categorized IP addresses and identifying anomalous traffic patterns, including DoS and DDoS activity and anomalous SYN floods.
-For authentication-related anomalous behavior, Avi provides the AUDIT_COMPLIANCE_EVENT mechanism to log authentication failures for audit purposes, persisting them via the alerts infrastructure. The Web Application Firewall (WAF) App Log Analytics component captures events whenever a WAF application rule is triggered, recording the type of attack detected. Service Engines generate DOS_ATTACK alert events that include attack type, source IP addresses, virtual service UUID and name, and a report timestamp, supporting audit and forensic analysis of detected attacks. Avi also supports DataScripts for custom identification of suspicious traffic and execution of appropriate mitigation actions, enabling organizations to define custom behavioral detection logic beyond the built-in statistical baselines.
-Avi monitors over 500 real-time metrics to support DDoS detection and attack visibility. Alerts from any of these mechanisms can be forwarded proactively to email, syslog, SNMP, or custom APIs, enabling integration with a central SIEM or security operations platform. Avi integrates with Splunk via the Avi Load Balancer Splunk Add-on, generating events that serve as an audit trail for user logins, configuration changes, and runtime state changes.
-These capabilities operate at the application delivery and load balancing layer. An organization requires a dedicated UEBA or UAM platform to fulfill the full scope of this control, including identity-level behavioral baselines, user session correlation, and cross-system entity analytics that extend beyond application traffic visible to Avi.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -14259,21 +14068,17 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E183" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides specific, documentable tools for AI TEVV activities. Deep learning VMs are the primary validation environment, provisioned from PAIS images with pre-installed software stacks validated for running AI applications on NVIDIA GPUs. DL VMs support prototyping, fine-tuning, validation, and inference workloads in a single environment.
-The Triton Inference Server is the documented tool for model inference validation. Models are tested for inference functionality using Triton and evaluated for performance and safety against business use cases, including examination of inference requests for malicious behavior and functional testing. This provides a standardized, repeatable testing tool for model evaluation.
-For performance measurement, each DL VM includes a pre-installed NVIDIA DCGM Exporter that monitors GPU metrics and workload behavior. GPU metrics are collected by Prometheus at configurable scrape intervals (global scrape at 15 seconds, DCGM exporter scrape at 5 seconds) and visualized in Grafana dashboards. VCF Operations provides additional GPU metrics monitoring at the cluster, host system, and host properties levels. The vSphere Client provides GPU performance charts at both host and cluster levels.
-The vcf pais CLI provides model management tooling, including the vcf pais models list command for retrieving and displaying all models available in a model gallery. Harbor Registry provides the artifact management tooling for storing, versioning, and distributing model artifacts with integrity verification through hash codes and unique content digests.
-PAIS does not manage test datasets or test set documentation. The selection, curation, versioning, and documentation of test sets used during TEVV activities is an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G183" s="10" t="inlineStr">
@@ -14926,56 +14731,37 @@
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F192" s="10" t="inlineStr">
         <is>
-          <t>VCF provides granular role-based access control (RBAC) across its component products, giving organizations the technical foundation to implement and enforce separation of duties policies. While VCF does not define SoD policies on its own, it supplies the authorization mechanisms that make duty separation enforceable at the infrastructure layer.
-VMware vCenter implements fine-grained authorization through a permissions and roles model applied to the vSphere object hierarchy. Administrators can create custom roles with specific privilege assignments, controlling exactly which actions a user or group can perform on specific vSphere objects. Permission propagation allows these assignments to cascade through the object tree, so access boundaries can be drawn at any level of the infrastructure. When a role is assigned directly to an individual user, that assignment takes precedence over any role assigned to a group to which the user belongs, allowing administrators to grant more restrictive or more permissive access to specific individuals without modifying group-level assignments. vCenter ships with system-defined roles that cannot be modified or deleted, including a Read Only role limited to three system-defined privileges (System.Anonymous, System.View, and System.Read) and an administrator role that provides an intermediate authorization level for users who manage vCenter configuration and control functions. If a predefined role does not match operational requirements, administrators can define new roles containing only the minimum set of required privileges, supporting least-privilege assignment aligned with duty boundaries. PowerCLI cmdlets such as New-VIRole and Set-VIRole allow programmatic creation and modification of roles, enabling consistent and auditable role management across environments. The privilege checks recorder feature allows administrators to monitor and query the privileges checked during vCenter operations, which helps build least-privilege custom roles tailored to particular workflows.
-VCF Operations extends RBAC with its own set of predefined and assignable roles. Each user must have a unique account with one or more roles assigned, and administrators can assign roles to individual users or to user groups with a defined scope for each role. Predefined roles in VCF Operations include privileges for create, read, update, and delete actions on components such as dashboards, reports, administration, capacity, policies, problems, symptoms, alerts, user account management, and adapters. The ContentAdmin role can manage all content, including views, reports, dashboards, and custom groups. This separation of administrative functions allows organizations to restrict operational staff to monitoring and reporting while reserving configuration and policy changes for designated administrators. VCF Operations also integrates with vCenter by sending its roles as privileges within the vCenter Global privilege group, requiring a vCenter administrator to assign those roles to users, which creates a natural two-party authorization step for cross-product access.
-VCF Automation extends role-based access control with both organization-wide and project-level role assignments. Predefined roles include Organization Administrator, Organization User, Organization Auditor, Project Administrator, Project User, Project Advanced User, and Project Auditor. At the project level, users can be assigned as administrators, members, or viewers. Organization Administrators have broad management rights including certificate management, content libraries, and approval policies, while Organization Auditors have read-only access for review purposes. VCF Automation also supports approval policies that require designated approvers to hold specific role combinations, adding a workflow-level separation step for provisioning and deployment actions. The System Administrator role in VCF Automation provides granular permissions across dozens of functional areas including API tokens, approvals, audit, blueprints, catalog, cloud accounts, deployments, extensibility, and more.
-NSX supports creating custom roles with granular permission assignments based on operational requirements, allowing network administration duties to be separated from compute and storage administration. vSAN covers RBAC and permissions management through its Security Configuration Guide, supporting storage-specific duty boundaries. vSphere also supports configuring separate key providers for different departments or organizational units, supporting granular access control to encryption keys that aligns with duty separation requirements for cryptographic operations. VCF Operations Orchestrator supports group-based permission management where users without an assigned role can view only their own workflow runs.
-Together, these RBAC capabilities allow an organization to assign distinct roles for compute administration, network configuration, storage management, security policy, monitoring, and cloud automation across VCF's component products. By granting each team or individual only the privileges required for their function, organizations can enforce duty separation that requires collusion between multiple privileged accounts to perform unauthorized actions. The organization remains responsible for defining SoD policies, determining which duties must be segregated, and assigning personnel to the appropriate roles. VCF provides the technical enforcement layer that restricts users to their granted privileges.
-VMware Private AI Services (PAIS) provides several role-based access control mechanisms that support the implementation of Separation of Duties across the AI infrastructure stack.
-VCF Automation, which PAIS uses to deliver self-service provisioning of GPU-accelerated VMware Kubernetes Service (VKS) clusters and Deep Learning VMs, defines distinct project-level roles including Project Administrator, Project Advanced User, and Project Auditor with differentiated privilege levels. These roles allow organizations to separate the individuals who configure AI infrastructure from those who consume it and those who review activity. At the platform tier, VCF Automation separates provider-level operations, which require a PROVIDER_ADMIN_ACCESS_TOKEN, from organization administrator operations, which require a TENANT_ADMIN_ACCESS_TOKEN. This token distinction means that infrastructure-wide actions and organization-scoped actions must be performed under different credentials by different principals.
-PAIS enforces access control through OIDC group-based authorization. The authorizedGroups field in the PAISConfiguration custom resource specifies which OIDC groups can access the service, restricting access to designated personnel. PAIS can be configured with only one OIDC provider, so all group-based authorization decisions flow through a single auditable path. PAIS users are organized in groups, with a groups claim included in the Access Token and a groups scope created in the OIDC configuration, giving organizations a mechanism to map personnel categories to access levels. The PAISConfiguration custom resource is defined as a CRD YAML file with sections for storage policy, CA trust bundles, database connection, OIDC provider integration, and ingress, and access control uses OIDC provider groups with configurable claim names for group identification in the organization namespace.
-The observability layer carries its own role separation. Grafana for PAIS supports OIDC-driven role assignment using a configurable role attribute path expression: users whose OIDC groups match the configured access group receive the Admin role, while remaining authenticated users receive the Viewer role. This restricts who can modify dashboards and alert configurations from those who can only read metrics.
-For Deep Learning VM and PAIS deployment, a VI administrator must configure a GPU-accelerated workload domain and clusters with support for vSphere Supervisor and VCF Automation before PAIS is installed on a Supervisor for an organization. Separately, the organization administrator must assign the required user role before any user can provision Deep Learning VMs or upload to the model gallery. This two-step requirement separates the actor who manages platform prerequisites from the actor who grants provisioning access to individual users.
-The organization must define its SoD policy, decide which personnel occupy which roles, and configure the OIDC provider with appropriate group memberships to reflect those assignments. PAIS supplies the technical mechanisms; the design and maintenance of the SoD structure itself is an organizational responsibility.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G192" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend supports Separation of Duties within its management plane through differentiated role-based access control across Security Services Platform, Security Intelligence, Distributed Firewall policy management, and the VCF Automation firewall administration layer.
-Security Services Platform defines five distinct roles with non-overlapping permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector. Security Intelligence applies the same role structure within its management surface. Each role carries differentiated capabilities, preventing any single administrator from controlling all aspects of security operations without oversight.
-In 9.1, VCF Automation introduces a Firewall category under rights that governs access to Distributed Firewall, Tenant Gateway Firewall, VPC Gateway Firewall, and VPC Security Profile management. The Organization Administrator role requires all eight rights across these firewall categories, while custom roles can be configured to grant narrower combinations of manage and view rights per firewall tier. This allows organizations to assign separate personnel for firewall rule management versus read-only visibility, and to separate responsibility across north-south and east-west firewall functions. Administrative rights in VCF Automation 9.1 are primarily governed by predefined roles rather than granular custom project-level rights, keeping privilege delegation bounded.
-VMware vDefend implements a persona-based security rule model with three distinct administrative tiers: the Provider Admin manages global resources and high-precedence rules in the shared infrastructure space, the Project Admin orchestrates security policy within a project, and the Organization Admin manages tenant-level resources and groups. Tenant-level groups are owned and managed by the Organization Admin, while Project Admins focus on groups within their dedicated VPCs, providing structural administrative separation between provider-tier and tenant-tier firewall policy management.
-Access to Distributed Firewall monitoring features, including Firewall Insights, is restricted to Enterprise Admin, Security Admin, and Security Operator roles, limiting who can observe security telemetry to designated personnel.
-VMware vDefend's SoD controls apply within its own management plane. Organizational SoD enforcement spanning identity governance, staffing decisions, and cross-system access management is outside the scope of a network security product.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J192" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) supports separation of duties for replication and disaster recovery operations through role-based access control that augments vCenter roles with PNR-specific permissions. PNR adds several predefined roles to vCenter that are available in the role drop-down for assigning permissions to users and user groups. Each role includes a defined set of privileges that allows users to complete specific actions while restricting access to resources belonging to other users.
-By default, the vCenter administrator role inherits all PNR and vSphere Replication privileges upon installation. PNR also supports assigning protection and recovery roles to users or user groups that do not hold vCenter administrator rights, allowing those users to perform protection and recovery operations without granting full vCenter administration. When a user requires privileges for both PNR and vSphere Replication operations without holding vCenter administrator rights, the recommended approach is to add the user to two separate user groups, each assigned the appropriate role, so the combined privileges are explicit and auditable. Users granted the vCenter administrator role after PNR installation must have PNR roles manually assigned on PNR objects, so that elevated platform roles do not automatically convey replication-administration rights to those users.
-PNR enforces additional duty separation across the recovery workflow. Testing a recovery plan and running a recovery plan require separate privilege assignment to help prevent unintended changes that take significant time and effort to reverse. PNR administrators can assign SrmAdministrator or SrmProtectionGroupsAdministrator roles to automatic-protection users or groups, allowing protection responsibilities to be delegated independently of plan execution.
-The Clean Room Orchestrator component within PNR adds its own role model with Organization-level roles and service-specific roles. Access to the Clean Room Orchestrator is governed by Global Console Admin and Recovery Admin service roles, separating overall console administration from recovery operations within the isolated recovery environment. Service-specific roles can be assigned to users in addition to Organization-level roles, allowing organizations to delegate clean-room responsibilities without granting broader administrative scope. PNR also applies resource isolation on shared recovery sites to maintain separation between different organizations' virtual machines.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K192" s="10" t="inlineStr">
@@ -14990,19 +14776,12 @@
       </c>
       <c r="M192" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N192" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer provides a role-based access control (RBAC) system that organizations can use to implement Separation of Duties across the Avi control and data planes. The Avi for VCF guide identifies role-based separation of duties as a core design principle, enabling application teams to autonomously consume load-balancing services using resources assigned to their organization.
-The Avi Controller supports three privilege levels for each resource: Write (full create, read, modify, and delete access), Read (view-only access without modification capability), and No Access (which restricts the user from reading or listing the resource entirely). Administrators can create custom roles that assign these privilege levels independently for each system resource, enabling precise allocation of capabilities to specific personnel without granting broader access than required. Roles are combined with tenant assignments to define the complete authorization profile for each user, making it possible for a team member responsible for virtual service operations to hold write access to load balancing resources while holding no access to certificate management or WAF policy configuration. Permission categories cover two main areas: Operations (including alerts, actions, and traffic capture) and Administration (including controller, tenant, user, role, and system configuration management).
-The Extended Granular RBAC system provides additional access scoping through label-based permissions for cloud objects. When no filters are configured, a user can access all objects according to the privileges in the assigned role. Granular RBAC per field allows administrators to restrict write access to specific sub-resources within objects, enabling fine-grained separation of configuration responsibilities. Virtual services also support RBAC configuration during creation, allowing granular access control for managing and monitoring individual applications independently.
-In VCF organization-managed mode, a Provider or Load Balancer Administrator manages resource assignments to organizations to enforce quotas and resource boundaries. At the data plane level, Service Engine groups are an inherent method of providing data plane isolation, and Service Engine Group allocation at the project level keeps each project within its designated boundaries. A service provider can allocate isolated Service Engines to each tenant or place multiple tenants in the same group depending on resource sharing requirements.
-For Global Server Load Balancing (GSLB), both predefined and custom-defined roles are available. Function-specific roles such as Gslb_Group_Enabled and Gslb_Health_Monitor can be assigned to user accounts with tenant-level scope, allowing separate personnel to manage GSLB group membership configuration independently from health monitoring configuration.
-The License Hub implements three distinct roles: Enterprise Admin (performs all operations), Auditor (views information and tracks activity without making changes), and Support Bundle Collector (collects system logs and diagnostics). This structure provides built-in separation of duties between operational and read-only audit functions for licensing management.
-For Kubernetes environments, the Avi Kubernetes Operator (AKO) implements RBAC by assigning tenants and roles to user accounts. HealthMonitor resources in AKO are scoped to a specific tenant, and the AKO CRD Operator manages namespace-scoped resources with tenant isolation for multi-tenancy support.
-Organizations should identify which duties require separation based on their operational and compliance requirements, then configure Avi roles, tenant assignments, Service Engine group boundaries, and organization-managed mode settings to enforce those separations.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -15315,95 +15094,57 @@
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
         <is>
-          <t>VCF provides secure baseline configurations for all major platform components, consistent with industry-accepted hardening standards. The VCF Security Baseline is a purpose-built document that builds on VCF security fundamentals to address frequently requested compliance standards, regulations, and frameworks. It is designed and validated to tailor security configurations without affecting VCF's ability to meet its design objectives. Organizations can use the VCF Security Baseline to evaluate both default and non-default configurations and to secure their environments in a compliance context.
-VCF Operations includes a consolidated out-of-the-box benchmark called the VCF 9 Security Baseline, which provides a ready-to-use compliance profile for evaluating the security posture of a VCF environment. This benchmark enables automated assessment of configurations against the documented baseline, helping maintain a consistent configuration across VCF components. ISO Security Standards compliance benchmarks are also available from the VCF Operations repository as a native pack, giving organizations the ability to measure their environment against internationally recognized hardening standards. Broadcom also provides DISA Security Technical Implementation Guides (STIGs) for VCF components, including vSphere 7.0 and vSphere 8.0 STIGs, which provide detailed instructions for securing and configuring systems to meet specific security requirements.
-Individual VCF components have their own security configuration guides that document hardening recommendations. The vSphere Security Configuration Guide provides best practices for securing VMware vCenter, including securing the installation, configuring access and authentication, defining roles and permissions, and enabling auditing and logging. VMware ESX host hardening covers authentication and authorization settings, disabling unnecessary services, enabling security features such as Secure Boot and Trusted Platform Module (TPM), and implementing network security measures. The vSphere Security Configuration Guide documents specific STIG-aligned values for the Security.PasswordQualityControlPwquality setting on ESX hosts, including parameters such as minlen=15, maxrepeat=3, maxclassrepeat=4, difok=4, and enforce_for_root. The NSX Security Configuration Guide provides recommendations for securing NSX components, including NSX nodes, NSX Controllers, and NSX Edge nodes, by configuring strong authentication, implementing role-based access control, and securing administrative access.
-VCF Operations also provides a Configure Host Security Config Data workflow that allows selective enforcement of host security hardening rules. Beyond security settings, vSphere Lifecycle Manager maintains a desired-state cluster image that defines the ESX base build, vendor add-ons, and firmware for every host in a cluster, so the software baseline stays consistent across hosts, and VCF Operations runs scheduled drift detection that flags configuration deviations from the desired state for remediation. Administrators can configure individual configuration elements under Enforce Options, enabling granular control over which baseline settings are applied and enforced across the environment. This supports reducing organizational and business risk by maintaining configuration consistency. vSphere Host Profiles provide an additional mechanism for automated and centrally managed host configuration baseline enforcement, capturing a reference host's configuration and applying it consistently across ESX hosts, covering memory, storage, networking, and other configuration aspects.
-For containerized workloads, VMware Kubernetes Service (VKS) includes preconfigured security policy templates. The Baseline security template provides a set of constraints that restrict known privilege escalations while maintaining compatibility with common containerized workloads.
-DISA STIGs for Supervisor and VKrs are available to guide hardening of the Supervisor control plane and individual VKS cluster releases, providing baseline security guidance at the same standard as the DISA STIGs applied to VCF infrastructure components. The VKS cluster management interface provides out-of-the-box security policy templates that mirror industry-standard Pod Security Standards profiles, including both Baseline and Restricted configurations. Custom VKS Cluster Management Security Policy templates are also available to fine-tune individual security context parameters and support governance controls tailored to specific organizational requirements.
-Pod Security Admission (PSA), enabled in VKr 1.25 and later, enforces pod security standards at the namespace level. Three policy profiles are defined: Privileged (unrestricted, for system-level workloads), Baseline (helps prevent known privilege escalations while allowing the default minimally specified pod configuration), and Restricted (heavily restricted, following pod hardening best practices). Three enforcement modes are available: enforce, warn, and audit. The podSecurityStandard field in the ClusterClass API encodes the intended security posture in cluster definitions, accepting these modes with specific policy versions and namespace exemptions so that baseline security configurations are applied consistently across VKS deployments. System namespaces including kube-system, tkg-system, and vmware-system-cloudprovider are excluded from pod security enforcement. The PSA admission controller can also be statically configured with default enforce, audit, and warn levels for unlabeled namespaces, so namespaces created without explicit labels still receive a defined security baseline. To support gradual policy adoption, audit and warn modes can be set to a stricter level such as restricted while enforce remains at baseline, giving administrators visibility into policy violations before full enforcement is applied. VCF Automation IaaS Resource Policies provide an additional enforcement point at the management layer, supporting requirements that Kubernetes clusters operate at a minimum baseline pod security level.
-Kubernetes-native kernel security mechanisms provide workload-level baseline hardening options. seccomp restricts the Linux kernel system call surface available inside containers using BPF-based profiles, and the RuntimeDefault seccomp profile provides a strong set of security defaults while preserving workload functionality. AppArmor and SELinux provide further kernel-level restrictions through default configurations that offer foundational protections. Kubernetes default RBAC role bindings should be reviewed as part of establishing a security baseline, as defaults may grant broader access than a hardened configuration requires. Isolating each workload in its own Kubernetes namespace allows tailored security policies to be applied per workload and restricts access to namespace-scoped resources such as ConfigMaps and Secrets.
-Harbor Registry, available as a standard package for VKS clusters, supports a controlled baseline for container artifacts entering the environment. Harbor provides vulnerability scanning, content trust, and policy-based replication, along with role-based access control and artifact security policies, supporting controlled management of the container image supply chain. For stand-alone virtual machines deployed in vSphere Supervisor environments, Content Libraries can distribute VM images created with current patches and required security settings that follow corporate security policies.
-VMware Private AI Services (PAIS) provides PAIS-specific declarative configuration mechanisms that organizations can use to define and apply baseline settings across the AI infrastructure stack on VCF.
-The primary mechanism is the PAISConfiguration custom resource. Private AI Services settings are declared in a YAML file compliant with the PAISConfiguration schema and applied with kubectl, giving administrators a single resource that captures observability, identity, and trust configuration for an organization namespace. Observability includes the spec.observability.prometheusRuntime section for Prometheus metrics collection with a configurable storage class and metrics retention period, and an llmTraces section for routing large language model traces to an OpenTelemetry Collector. The PAISConfiguration custom resource can be patched with kubectl patch and verified with kubectl get paisconfiguration, supporting baseline change control and drift detection at the AI service layer.
-Certificate trust is handled through the spec.clientTls.caBundleRefs section, which references ConfigMaps containing CA trust bundles. Private AI Services requires HTTPS trust bundles for the OIDC provider, the Harbor registry, content management systems hosting knowledge database data, and MCP servers that provide tools to models. Trust bundles can be organized per application, with periodic updates required before certificate expiration. Access scope is restricted through the authorizedGroups setting, which limits Private AI Services access to specified OIDC groups.
-Harbor registry distribution carries baseline controls for model and image artifacts. Replication rules support configurable filters, target namespace, and trigger mode, including a manual trigger mode, so administrators can align artifact replication with organizational policy for connected and disconnected sites. The Model Gallery uses Harbor project access capabilities to restrict access to sensitive training and tuning data. Air-gapped deployments capture the self-hosted registry URL and registry login credentials as part of the activation flow.
-Workload resource baselines are defined through SupervisorNamespaceClassConfig, which specifies per-zone CPU limits, CPU reservations, memory limits, and memory reservations for resource allocation across zones. GPU-capable VM classes can carry GPU reservations and be confined to a single zone or supervisor namespace, supporting isolation of GPU consumption to a specific tenant. A default storage policy selection in the Private AI Services quickstart defines storage placement and resources for the service database.
-Deep Learning VM (DL VM) baselines are captured through VCF Automation self-service catalog items that parameterize VM class, data disk size, user password, and optional SSH public key authentication for remote access. The DL VM OVF property config-json accepts a base64-encoded configuration file that controls DCGM Exporter metrics visibility through export_dcgm_to_public and JupyterLab authentication through enable_jupyter_auth, giving operators a consistent surface to define DL VM hardening parameters.
-Credentials supplied during Private AI Services activation, including the private container registry password and proxy password, are stored as secrets in VCF Automation rather than as plaintext configuration values, supporting credential hygiene as part of the deployment baseline.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G197" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to secure baseline configurations within its network security domain by providing structured configuration management capabilities, predefined security profiles and strategies, and configuration integrity controls that align with industry-accepted hardening practices.
-vDefend supports draft configuration management with configuration locking to prevent multiple users from simultaneously opening and editing a manual draft, helping maintain configuration integrity and reducing the risk of conflicting changes to firewall policy. Role-Based Access Control (RBAC) in vDefend governs who can create or modify firewall policies, providing control over which administrators can alter the security baseline.
-In vDefend, five system-defined VPC Security Strategies are available for establishing security baselines across Virtual Private Clouds (VPCs): VPC Isolation, VPC Isolation with Essential Services, VPC External Connectivity, VPC Secure Connection, and NONE. These strategies are consumed through Security Profiles in VCF Automation, which are predefined configuration templates that define the default security posture for VPCs. VPC Security Strategies provide a declarative, consistent way to apply DFW security baselines across multiple VPCs within a project, and Project Admins are guided to select a pre-defined high-level security posture that enforces Secure by Default principles rather than manually configuring individual firewall rules. Security profiles can be applied to one or more VPCs simultaneously and updated as requirements evolve.
-vDefend provides predefined TLS Decryption Action Profiles with four settings: Balanced (default), High Fidelity, High Security, and Custom. These profiles are vendor-defined baseline configurations for TLS inspection behavior, giving organizations a documented starting point aligned with different security postures. TLS Inspection policies also support an Advanced Configuration option to lock policies, preventing multiple users from making concurrent changes to TLS inspection policy baseline settings.
-Security Services Platform validates configuration changes before implementation through a deployment wizard that conducts thorough validations to confirm configurations are correct and compatible. The platform enforces initial security policies that cannot be modified through the user interface after they have been published, providing an immutability mechanism for foundational policy baseline elements. Security Services Platform supports backup and restore of configuration data, and certificate consistency between backup and restored environments should be verified to maintain NDR sensor integrity.
-Security Services Platform's Bare Metal Security feature extends vDefend policy enforcement to physical servers, applying L3/4 security policies to bare metal infrastructure using the same policy model and management plane as virtualized workloads. Two default DFW rules are created when Bare Metal servers are onboarded to Security Services Platform, providing an immediate baseline posture for physical infrastructure. Security policies are defined, propagated, and enforced across Bare Metal servers with consistent application and monitoring.
-vDefend's configuration management capabilities operate within the network security layer. The broader secure baseline configuration program for VCF, including the VCF Security Baseline document, component hardening guides, DISA STIGs, and compliance scanning through VCF Operations, is managed at the platform level. vDefend contributes by maintaining its own secure defaults and configuration controls within the network security domain.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="J197" s="10" t="inlineStr">
         <is>
-          <t>VCF Protection and Recovery (PNR) provides configurable security baseline mechanisms for its replication and recovery infrastructure. The PNR appliance includes a security reference section that identifies configuration files containing settings that affect environment security, and PNR documentation establishes that secure operation depends on proper configuration and maintenance of the PNR server. The security reference also documents network port requirements, providing the technical specifications needed to develop and maintain secure baseline configurations for disaster recovery infrastructure.
-PNR includes a Configuration Import/Export Tool that captures the complete set of protection and recovery configuration settings, including server version, build number, local and remote site names, inventory mappings, placeholder datastores, advanced settings, and array managers. The tool supports both UI-based and scripted exports and can transfer configuration data without requiring credential entry when using the bundled generated script. This gives organizations a mechanism to document, back up, and restore known-good baseline configurations for their disaster recovery infrastructure. The underlying system configuration is stored in the va-configurator.xml file and is accessible through Advanced Settings on the Site Pair tab in the management interface, providing a defined location for baseline review and modification.
-The PNR appliance management interface allows administrators to configure appliance security settings after deployment. The Advanced Settings system provides privileged users with the ability to adjust default values governing protection and recovery features. When modifying the minimum protocol version for TLS, PNR requires that the change be applied consistently across all configuration occurrences in the system, supporting systematic baseline management for transport security settings.
-For cyber recovery deployments, PNR documentation recommends using standard VCF topology with separate workload and management domains to achieve better isolation and align with security best practices at the recovery site.
-Full compliance with this control requires an organizational baseline configuration management program, documentation practices, version control, and hardening tooling extending beyond what PNR provides directly.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="K197" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="L197" s="10" t="inlineStr">
         <is>
-          <t>VMware Data Services Manager (DSM) contributes to secure baseline configuration management through its infrastructure policy framework, data service policy enforcement, and built-in secure defaults for authentication and certificate management.
-Infrastructure policies in DSM define the compute, storage, and networking resources for each database deployment, including the list of allowed VM classes and compatible storage policies. These policies are configured by DSM administrators and act as standardized, repeatable deployment baselines that database users must follow. When administrators configure infrastructure policies, they constrain the quality and quantity of resources that users can consume from vSphere clusters, establishing guardrails that support consistent deployments across the environment. Database cluster creation applies both infrastructure policies and storage policies that enforce isolation and resource constraints, reducing the risk of misconfiguration by individual users.
-Data service policies extend this baseline enforcement across multi-tenant deployments. DSM administrators can define and configure data service policies for various database services and enforce them across different tenants to maintain a consistent security and compliance posture. Data service policies constrain which infrastructure options can be applied to database instances. When DSM is integrated with VCF Automation, data service policies can be applied consistently across organizational units.
-DSM also ships with predefined secure defaults for database authentication. PostgreSQL databases on DSM use scram-sha-256 as the default password-based authentication method, as configured in the default pg_hba.conf entries stored at /pgsql/data/pg_hba.conf. Custom pg_hba.conf entries support scram-sha-256, reject, and cert authentication methods. TLS is enforced by default for database client connections, with an administrator-controlled option to relax enforcement via the postgrescluster-allow-non-ssl-system-users setting in the advanced-system-config ConfigMap within the dsm-system namespace.
-Certificate management is integrated into the database creation workflow and validates certificate chains for connections to external systems, including VMware vCenter. DSM introduces a stricter default certificate validation mode, the "latest" mode, that enforces cryptographic and KeyUsage validations for all DSM endpoints, including the Provider VM and data service clusters. Certificates uploaded to DSM are validated against FIPS 140-3 cryptographic standards, and uploads containing unsupported algorithms or parameters are rejected. Custom trusted root certificates must comply with FIPS requirements. DSM also verifies the SHA256 thumbprint of vCenter during initial configuration to confirm the management connection targets the expected endpoint. Custom certificate support allows organizations to replace the default DSM certificate with organization-issued certificates for both the Provider VM and database clusters. For self-service deployments using the DSM Consumption Operator, signature verification confirms package integrity before installation.
-DSM validates certificate chains using configured root CA certificates stored in ConfigMaps and supports private container registry configuration with CA certificate validation for air-gapped environments.
-Addressing this control fully requires organizational processes beyond what DSM provides directly. DSM does not include tooling to document baseline configurations in a compliance-ready format, map configurations to specific industry hardening standards, or audit deviations from defined baselines over time. Organizations should supplement DSM's policy and defaults framework with configuration management documentation, change tracking processes, and integration with compliance scanning tools to satisfy the full requirements of this control.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="M197" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N197" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) provides several built-in mechanisms that support the development and application of secure baseline configurations for the application delivery layer.
-The SSL/TLS Profile system gives administrators a documented starting point for cryptographic configuration. Profile Templates define accepted SSL and TLS versions and ciphers in prioritized order, and can be associated with virtual services or the Controller itself. The Standard SSL/TLS Profile is suitable for typical deployments, while the System-Standard profile provides modern cipher suites for backend server re-encryption in Kubernetes environments managed through the Avi Kubernetes Operator (AKO). Avi includes a curated list of cipher suites considered reasonably strong for SSL/TLS configuration, and the documentation notes the trade-offs between security, compatibility, and computational expense when selecting profiles. The Service Engine disables unsafe legacy renegotiation by default, providing a built-in protocol hardening baseline that reduces the risk of protocol downgrade attacks.
-The System-Secure-HTTP application profile is a pre-configured baseline for securing HTTP virtual services. It enforces HTTPS, protects cookies, manages client IP handling, and controls protocol behavior, giving administrators a hardened starting point for web application delivery. Administrators can supplement these defaults with more granular settings through policies or DataScripts.
-For deployments requiring validated cryptographic modules, Avi Load Balancer implements FIPS 140-3 compliance, providing a cryptographic baseline aligned with the U.S. and Canadian government standard for cryptographic modules.
-The Avi Web Application Firewall (WAF) Positive Security model supports application-layer baseline configuration through rules that define allowed application behavior. Each rule supports Enable/Disable control, mode selection between Detection and Enforcement, and configurable Paranoia levels, allowing organizations to tune an application security baseline to their risk posture. The Positive Security Rule Updates feature can be enabled to activate additional configuration options for application security policies. The Cloud Console Application Rules service extends this with rules specifically designed to address known application vulnerabilities, including those with CVEs, and updates them automatically.
-For Kubernetes deployments, AKO uses Custom Resource Definitions (CRDs) to enable syntactical validation of configuration objects at creation time, which helps prevent invalid configurations from being deployed. The AKO L4 CRD Rule supports SSL profiles and PKI profiles for securing pool connections, allowing Kubernetes-native expression of Avi's cryptographic baseline settings.
-Certificate lifecycle management supports maintaining cryptographic baselines over time. Certificate Management Profiles support automated certificate renewal workflows, and the Trust Protection Platform integration can automatically handle certificate and chain certificate renewals by learning the mapping of virtual service names to their certificates.
-The organizational process of developing, documenting, and maintaining baseline configurations across all in-scope technology assets, including selecting appropriate profile settings, applying them consistently, and updating them as software versions and security guidance evolve, remains outside what Avi performs on the organization's behalf.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -16301,19 +16042,17 @@
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E210" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F210" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides several infrastructure capabilities that support the development and implementation of fact-checking techniques for AI-generated content. The most direct mechanism is the Retrieval-Augmented Generation (RAG) architecture available through PAIS. RAG workloads combine a large language model with an external knowledge base, grounding model responses in organizational data rather than relying solely on the model's training data. Data scientists can build knowledge bases that link to data sources hosted in external content management systems, including Microsoft SharePoint sites and Amazon S3 compatible stores, with a maximum of 10 data sources per knowledge base and each data source bound to a fixed type at creation. PAIS Data Indexing and Retrieval enables automatic collection and indexing of data updates from linked sources over time, which helps keep the grounding data current. This architecture provides a structural approach to improving the accuracy of AI-generated information by anchoring responses to authoritative source material rather than unconstrained generation.
-The validate-then-publish workflow for ML models supports pre-deployment testing that can include accuracy verification. MLOps engineers validate ML models against the security, privacy, and technical requirements of their organization before storing them in PAIS. PAIS uses a Harbor registry service in the Supervisor to store validated ML models, with authentication and certificate-based trust required for model retrieval, and OCI-compliant registries from other vendors are also supported. Storing models in a controlled registry provides traceability for which model version was validated and deployed.
-Agent Builder in PAIS integrates with Data Indexing and Retrieval to add business data from knowledge bases to agents, allowing teams to build generative AI applications where agent output is informed by curated, access-controlled knowledge bases. Agent Builder also maintains a list of approved tools for use in AI agents when connecting to MCP servers, and available tools are displayed in the tool gallery for namespace-level examination and approval before an agent can call them. MLOps engineers and application developers can monitor the health, quality, and behavior of models used in agents through observability platforms such as Grafana, and PAIS observability can be activated by updating the PAISConfiguration custom resource with metrics and OpenTelemetry trace parameters. The combination of RAG grounding, model validation, approved-tool gating, and observability provides the technical mechanisms organizations need to implement fact-checking techniques, while the specific fact-checking methodologies and acceptance criteria remain the responsibility of the deploying organization.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G210" s="10" t="inlineStr">
@@ -16519,38 +16258,27 @@
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E213" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F213" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several built-in capabilities that support routine vulnerability scanning and configuration error detection across the infrastructure stack, though a complete vulnerability management program requires integration with dedicated scanning tools for guest operating systems and applications.
-VCF Operations includes a diagnostics engine that automatically detects known issues and critical vulnerabilities within the VCF software stack. The engine scans the platform against VMware best practices, logs, and properties to identify diagnostic findings that match known issues, providing detailed descriptions, root cause insights, and actionable remediation steps. The Diagnostic Findings feature provides a consolidated view of known product issues, VMware Security Advisory (VMSA)-based security exposures, and best-practice recommendations across the environment. The Findings Catalog displays the complete list of diagnostic signatures checked at any given time, allowing administrators to see exactly what conditions are being evaluated. Administrators can manage diagnostics parameters through a JSON solution configuration file to customize which rules are active, adjust defaults, and control how findings are handled. These diagnostics build on the capabilities of several legacy tools and operational data to provide integrated issue detection and remediation.
-VCF Operations also supports advanced query capabilities that can identify virtual machines running vulnerable operating systems, including specific detection for end-of-life platforms such as Microsoft Windows Server 2003, Microsoft Windows Server 2008, Red Hat Enterprise Linux 5 and 6, and SUSE Linux Enterprise 10. These queries can group results by VLAN for security assessment and compliance monitoring purposes.
-The Security Operations dashboard consolidates user and infrastructure security elements into a single view, helping administrators identify areas that require attention. This dashboard highlights security-relevant findings across the VCF environment, providing a centralized starting point for security posture review.
-For configuration error detection, VCF Operations monitors configuration errors generated from infrastructure components such as NSX networking, grouping findings by hostname. Alert definitions can be created to monitor virtual machines and hosts with custom symptom parameters, enabling identification of configuration problems before users encounter them. The Configuration Drifts feature in VCF Operations provides proactive monitoring of configuration changes across vCenter instances and vSphere clusters, comparing current values against configuration templates to identify drift. vSphere Configuration Profiles must be enabled on clusters to view drift status. Configuration drift detection compares each vCenter instance's current configuration against the defined template values, and the Configuration Drift dashboard allows administrators to view and monitor drift statuses across the environment.
-For patch compliance scanning, vSphere Lifecycle Manager manages all hosts in a cluster collectively with a single image and tracks the current state of each host against the desired cluster image specification, reporting compliance status. The compliance check capability compares the current image on a host against the desired image and reports compatibility status. PowerCLI provides cmdlets for scanning virtual machines and hosts against defined baselines, including the Test-Compliance command to scan entities against downloaded patches and identify which hosts or components are missing security updates. Dynamic baselines update automatically based on specified criteria each time new patches are downloaded, allowing ongoing comparison of system state against current patch levels. The vCenter appliance can also be configured to perform automatic checks for available patches from a configured repository URL, enabling timely awareness of patch availability for the management plane itself. This automatic checking is configured through the vCenter Management Interface (the Check-for-updates-automatically setting) and supports proxy server configuration for environments without direct repository access.
-VMware releases security advisories (VMSAs) for critical known vulnerabilities with step-by-step remediation instructions. VCF Operations Diagnostic Findings provides a consolidated view of VMSA-based security exposures alongside best-practice recommendations, connecting advisory information directly to the operational environment.
-The DISA STIG Viewer tool provides automated checking of system configurations against STIG requirements, helping identify security vulnerabilities and configuration deviations for environments that follow DISA hardening guidance. This offers a structured approach to configuration compliance scanning against industry-standard best practices.
-While VCF provides vulnerability detection and compliance scanning for its own infrastructure stack, scanning of guest operating systems and applications running on VCF requires integration with third-party vulnerability scanning tools. VCF's REST APIs and PowerCLI support enable integration with external scanners and security information and event management platforms to extend scanning coverage beyond the infrastructure layer.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G213" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to vulnerability awareness through Security Services Platform analytics and IDS/IPS threat detection, though it does not perform host-based or authenticated application-layer vulnerability scanning.
-The Security Services Platform generates Security Segmentation Reports and Blast Radius Reports as part of the vDefend Security Assessment workflow. The Security Segmentation Report assesses security posture by analyzing network traffic over a configurable time range, identifying workloads running obsolete operating systems and using risky protocols, and providing specific improvement recommendations. Blast Radius Reports break down at-risk workloads, communication chains, and network flows to support protection planning. The Security Services Platform also provides an application monitoring view that displays information about running applications and identifies potential security risks, enabling assessment and remediation planning.
-The IDS/IPS subsystem contributes vulnerability-specific context by detecting exploitation attempts against known vulnerabilities. IDS/IPS event monitoring records Common Vulnerability Scoring System (CVSS) scores and CVE reference information for vulnerabilities targeted by active exploits. Administrators can search the signature library by specific CVE IDs to assess whether detection coverage is in place for known vulnerabilities. The Security Services Platform provides IDS/IPS performance metrics to monitor detection readiness across the environment.
-Because vDefend operates at the network layer, dedicated host-based and authenticated application-layer scanning tools are required to fully satisfy this control. Coverage remains at Contributes.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr">
@@ -16575,17 +16303,12 @@
       </c>
       <c r="M213" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="N213" s="10" t="inlineStr">
         <is>
-          <t>VMware Avi Load Balancer (Avi) supports vulnerability detection for web applications through its Web Application Firewall (WAF) Dynamic Application Security Testing (DAST) integration. The Avi SDK includes a DAST vulnerability scanner script, delivered in the DAST directory on the Avi Controller, which integrates with OWASP ZAP Attack Proxy and Qualys Web App Scanning to assess web application vulnerabilities and drive virtual patching. When a DAST scan identifies vulnerabilities, the avi-iwaf-vpatch.py tool automates virtual patch creation by generating Positive Security location rules for each vulnerable URL and Positive Security rules for each supported issue type. This allows the WAF to block requests targeting known vulnerable application paths while underlying code remediation proceeds.
-In 9.1, the Avi Cloud Console adds an Application Rules service that provides rules specifically designed to block attacks on known application vulnerabilities, many correlated with CVE identifiers, and automatically updates those rules on the Avi Controller. This complements DAST-driven virtual patching with a continuously refreshed, CVE-mapped rule set covering known application vulnerability classes.
-The DAST integration has acknowledged limitations: it does not detect all cookie-related security issues, and some flagged vulnerabilities may require manual remediation rather than automated virtual patching. Organizations should validate scan results and supplement Avi's application-layer DAST capability with platform-level scanning of the Avi Controller infrastructure through VCF platform vulnerability management tooling.
-Avi also supports configuration error detection through its inventory fault monitoring system. The Controller's inventoryfaultconfig setting allows independent tracking of license faults, migration faults, backup scheduler faults, SSL profile faults, and deprecated API version faults, with alert generation on configured conditions. This supports detection of misconfigured components before they affect application delivery.
-The Avi Application Security Report consolidates security findings for a selected virtual service. The report includes ranked lists of top attack types such as SQL injection and cross-site scripting, lists of top attacking IP addresses, and trend summaries showing total and flagged requests. Reports can be generated through the Avi UI or the Avi Controller CLI and downloaded in PDF format, supporting auditor review and periodic vulnerability assessment documentation workflows.
-Organizations running Avi on VCF should also lock the Avi Controller Linux OS to a specific version to reduce false-positive CVE scanner findings that arise from inactive OS package versions present on the system but no longer in active use.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
     </row>
@@ -16691,20 +16414,17 @@
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E215" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F215" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) provides provenance tracking mechanisms for model artifacts and data sources used by AI workloads. Models are stored in Harbor registries integrated with PAIS as a model storage backend, with authentication and certificate-based trust required for model retrieval. PAIS is also compatible with OCI-compliant registries from other vendors, allowing organizations to use existing model storage infrastructure while preserving artifact lineage. Each model artifact stored as an OCI object carries an immutable manifest and a unique content digest, which provides verifiable lineage from a deployed model back to its specific revision and the registry of origin.
-In disconnected (air-gapped) environments, a Harbor registry acts as a controlled intermediary between external model sources and the internal deployment environment. The artifact mirroring tool (AMT), distributed as part of the pais CLI plug-in, helps administrators populate the Harbor registry from external sources before catalog publication. PAIS requires HTTPS trust bundles configured for the OIDC provider, the Harbor registry, content management systems hosting knowledge base data, and Model Context Protocol servers providing tools to models, which establishes verified channels for the artifact and data sources entering the platform.
-For knowledge base data used in retrieval-augmented generation, PAIS Data Indexing and Retrieval connects to enterprise content management systems such as Microsoft SharePoint sites and Amazon S3 compatible stores as data sources. Data sources are created with a specific type that cannot be changed after creation, and a knowledge base can be linked to a maximum of ten data sources, with one data source linkable to multiple knowledge bases. PAIS tracks document-level changes during indexing operations, capturing counts of crawled documents, new documents found, deleted documents, existing unmodified documents, modified documents requiring embeddings update, and skipped documents. Indexing operations also record megabytes downloaded, number of new chunks indexed, final index size after removal of deleted documents, and timing metrics for download, embedding generation, and the index operation. PAIS supports OpenTelemetry collector integration for metrics collection and large language model traces, including knowledge base indexing traces, which records observable evidence of content provenance at the data layer.
-PAIS gives a foundation for content provenance through OCI-based artifact immutability and digest-based integrity verification, combined with knowledge base indexing telemetry. The platform does not implement a formal content provenance benchmarking standard such as SLSA (Supply Chain Levels for Software Artifacts) or SPDX (Software Package Data Exchange). Organizations requiring benchmarking against industry-recognized provenance standards layer those frameworks on top of PAIS-native artifact and data source management.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G215" s="10" t="inlineStr">
@@ -16910,40 +16630,27 @@
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E218" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F218" s="10" t="inlineStr">
         <is>
-          <t>VCF contributes to protecting the integrity of data sources used by AI workloads through storage-level encryption and access controls. vSAN encryption at rest and VM encryption protect AI training data stored on VCF infrastructure from unauthorized access at the storage layer. VMware vCenter RBAC restricts who can access or modify VMs containing AI data. Storage policies control datastore placement and encryption properties for AI workload VMs.
-At the Consumption layer, VMware Kubernetes Service (VKS) on vSphere Supervisor extends these protections to containerized AI workloads. Harbor, available both as a Supervisor Service and as a standard package on VKS clusters, is the private container image registry, with images organized by vSphere Namespace. Harbor scans images for known vulnerabilities, enforces content trust so that only signed and verified artifacts are trusted, applies role-based access control to restrict which principals can push or overwrite model artifacts and pipeline images, and uses policy-based replication to control how artifacts move between registries. After Harbor is integrated with the Supervisor, all VKS clusters on the same Supervisor automatically trust it as a source of verified images.
-Kubernetes admission controllers, including ValidatingAdmissionPolicy and validating webhook controllers, can be configured on VKS clusters to enforce requirements before workloads are admitted. Relevant policies include restricting image pulls to the trusted Harbor registry, requiring that images carry a valid signature, and blocking workloads that reference unscanned or unapproved artifacts. These controls reduce the risk that a workload carrying corrupted or tampered data processing logic reaches AI training data.
-GitOps workflows, supported through the Argo CD Supervisor Service, store all workload and infrastructure configuration declaratively in a Git repository as the single source of truth. Every change to the deployed state flows through Git, creating a durable record of every authorized modification. Immutable infrastructure patterns complement this approach by making unauthorized changes identifiable through drift detection between actual cluster state and the declared configuration.
-Kubernetes RBAC restricts which users and service accounts can read from or write to data volumes, ConfigMaps, and Secrets within VKS clusters. Supervisor namespace isolation with resource quotas contains workloads within defined boundaries, reducing the risk that one tenant can access or alter another tenant's data. Antrea-based network policies define namespace-level ingress and egress rules, scoping the network access surface for storage components that hold AI training data or inference inputs.
-CSI Volume Snapshots for VKS clusters support crash-consistent backups with deduplication, compression, and encryption. The ability to restore from a known-good snapshot provides a recovery path when data corruption is detected. The VCF CLI binary, used to interact with VCF Services consumption, publishes a sha256sum.txt checksum file alongside each download so that administrators can verify the binary's integrity before use.
-Validating the provenance and accuracy of AI training data at the application level is outside VCF's scope. Data poisoning detection, training data lineage, and AI-specific data provenance tracking require application-layer tooling or AI platform components built on top of the VCF platform.
-VMware Private AI Services (PAIS) provides integrity controls for both model artifacts and data sources used by AI workloads. Model revisions in the Model Gallery use Harbor as a storage backend, and each push of the same model receives a unique digest so that successive revisions are content-addressed and distinguishable. Before upload, model files should be validated for integrity by checking hash codes, scanned for malware and serialization attacks, and tested for correct inference behavior using Triton Inference Server as part of the sandbox validation process in a Deep Learning VM. This pre-upload validation provides cryptographic verification and behavioral testing that helps prevent contaminated or tampered model data from entering production.
-The Model Gallery uses Harbor project access capabilities to restrict access to sensitive data used to train and tune models. Harbor integration requires authentication and certificate-based trust for model retrieval, and PAIS requires CA trust bundles to be imported for the Private Harbor registry, content management systems used as data sources in Data Indexing and Retrieval, and MCP servers providing tools for agents. These access controls and verified chains of trust restrict unauthorized modification of model and data artifacts. The documentation recommends using the Model Gallery to reduce redundant copies of models and maintain model integrity in a controlled environment.
-For knowledge base data sources used by retrieval-augmented generation, PAIS Data Indexing and Retrieval enables automatic collection and indexing of data updates from linked data sources over time, supporting external content management systems such as Microsoft SharePoint and Amazon S3 compatible stores. Each knowledge base data source is created with a specific type that cannot be changed after creation, which helps prevent silent reconfiguration of the underlying source provider. The content management system used as a data source must be supported, and valid credentials are required for access to the content location. SharePoint data sources require user name and password authentication, and service account key file data sources require the information from the service account key file during data source creation. PAIS uses a CA trust bundle for secure communication with external services and databases, establishing verified transport between PAIS and its data sources.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G218" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend contributes to protecting the integrity of source data used by AI workloads on VCF through network-level security controls that restrict access to data stores and pipelines and detect malicious activity targeting data repositories.
-Distributed Firewall microsegmentation enforces least-privilege network access at the vNIC level, limiting which workloads and users can reach databases, object stores, and data pipelines used for AI training and operation. Attacks that attempt to contaminate or corrupt AI source data require network access to the stores where training data resides; microsegmentation restricts that access to authorized workloads and identities. Security Intelligence provides visibility into traffic flows between workloads, generates firewall rule recommendations, and validates that security policies are enforced. Security Intelligence administrators can monitor for traffic leakage between environments, establish exceptions for authorized communication paths, and implement lockdown protection rules to control unauthorized inter-environment traffic. Gateway Firewall provides an additional enforcement point at the perimeter of network segments containing sensitive data repositories.
-vDefend IDS/IPS inspects traffic to and from data repositories for known exploit patterns, command-and-control traffic, lateral movement, and data exfiltration signatures. The IDS/IPS filestore capability stores matched files to disk when a signature rule fires, supporting forensic analysis and post-incident review of suspected data integrity compromises. IDS/IPS signature-based detection also uses file magic inspection, identifying file types by their binary structure via libmagic, to detect misrepresented or malformed files in transit to data repositories.
-Malware Prevention intercepts and analyzes files transferred over the network to data repositories. Profiles can be configured to send files to the cloud for detailed analysis or to process them locally without cloud connectivity. Verdict decisions classify files as Benign, Trusted, Highly Trusted, or Malicious. Security Services Platform Malware Prevention collects file analysis data including file hash submissions, assigns an Analyst UUID to each cloud submission for tracking, and records in-memory script buffer inspection details with associated analysis reports. The Security Services Platform also provides backup and restore mechanisms covering hardware malfunctions, software malfunctions, data corruption, and malware incidents, providing a recovery path if SSP itself is compromised.
-vDefend contributes to this control because its microsegmentation, threat detection, and file inspection capabilities reduce the attack surface and detection gap for data poisoning attacks targeting AI workloads. Protecting data integrity at the application layer, including content validation, provenance tracking, and checksums within data stores, is outside vDefend's domain and requires organizational processes and additional tooling.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr">
@@ -17665,1325 +17372,1321 @@
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E228" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F228" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G228" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H228" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I228" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J228" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K228" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L228" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M228" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N228" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.10-001</t>
+        </is>
+      </c>
+      <c r="B229" s="10" t="inlineStr">
+        <is>
+          <t>AAT-19, AAT-19.8, VPM-10</t>
+        </is>
+      </c>
+      <c r="C229" s="10" t="inlineStr">
+        <is>
+          <t>Conduct AI red-teaming to assess issues such as: Outputting of training data samples, and subsequent reverse engineering, model extraction, and membership inference risks; Revealing biometric, conﬁdential, copyrighted, licensed, patented, personal, proprietary, sensitive, or trade-marked information; Tracking or revealing location information of users or members of training datasets.</t>
+        </is>
+      </c>
+      <c r="D229" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E229" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F229" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G229" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H229" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I229" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J229" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K229" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L229" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M229" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N229" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.10-002</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
+        <is>
+          <t>AAT-11.1, AAT-11.3</t>
+        </is>
+      </c>
+      <c r="C230" s="10" t="inlineStr">
+        <is>
+          <t>Engage directly with end-users and other stakeholders to understand their expectations and concerns regarding content provenance. Use this feedback to guide the design of provenance data-tracking techniques.</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E230" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F230" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G230" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H230" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I230" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J230" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K230" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L230" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M230" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N230" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.10-003</t>
+        </is>
+      </c>
+      <c r="B231" s="10" t="inlineStr">
+        <is>
+          <t>AAT-10.18, AAT-12.1</t>
+        </is>
+      </c>
+      <c r="C231" s="10" t="inlineStr">
+        <is>
+          <t>Verify deduplication of GAI training data samples, particularly regarding synthetic data.</t>
+        </is>
+      </c>
+      <c r="D231" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E231" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F231" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G231" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H231" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I231" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J231" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K231" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L231" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M231" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N231" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.11-001</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>AAT-06, AAT-10.8, AAT-26</t>
+        </is>
+      </c>
+      <c r="C232" s="10" t="inlineStr">
+        <is>
+          <t>Apply use-case appropriate benchmarks (e.g., Bias Benchmark Questions, Real Hateful or Harmful Prompts, Winogender Schemas15) to quantify systemic bias, stereotyping, denigration, and hateful content in GAI system outputs; Document assumptions and limitations of benchmarks, including any actual or possible training/test data cross contamination, relative to in-context deployment environment.</t>
+        </is>
+      </c>
+      <c r="D232" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E232" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F232" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G232" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H232" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I232" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J232" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K232" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L232" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M232" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N232" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.11-002</t>
+        </is>
+      </c>
+      <c r="B233" s="10" t="inlineStr">
+        <is>
+          <t>AAT-10.8</t>
+        </is>
+      </c>
+      <c r="C233" s="10" t="inlineStr">
+        <is>
+          <t>Conduct fairness assessments to measure systemic bias. Measure GAI system performance across demographic groups and subgroups, addressing both quality of service and any allocation of services and resources. Quantify harms using: ﬁeld testing with sub-group populations to determine likelihood of exposure to generated content exhibiting harmful bias, AI red-teaming with counterfactual and low-context (e.g., “leader,” “bad guys”) prompts. For ML pipelines or business processes with categorical or numeric outcomes that rely on GAI, apply general fairness metrics (e.g., demographic parity, equalized odds, equal opportunity, statistical hypothesis tests), to the pipeline or business outcome where appropriate; Custom, context-speciﬁc metrics developed in collaboration with domain experts and aﬀected communities; Measurements of the prevalence of denigration in generated content in deployment (e.g., sub- sampling a fraction of traﬃc and manually annotating denigrating content).</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E233" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F233" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G233" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H233" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I233" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J233" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K233" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L233" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M233" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N233" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.11-003</t>
+        </is>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
+        <is>
+          <t>AAT-07</t>
+        </is>
+      </c>
+      <c r="C234" s="10" t="inlineStr">
+        <is>
+          <t>Identify the classes of individuals, groups, or environmental ecosystems which might be impacted by GAI systems through direct engagement with potentially impacted communities.</t>
+        </is>
+      </c>
+      <c r="D234" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E234" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F234" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G234" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H234" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I234" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J234" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K234" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L234" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M234" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N234" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.11-004</t>
+        </is>
+      </c>
+      <c r="B235" s="10" t="inlineStr">
+        <is>
+          <t>AAT-10.8</t>
+        </is>
+      </c>
+      <c r="C235" s="10" t="inlineStr">
+        <is>
+          <t>Review, document, and measure sources of bias in GAI training and TEVV data: Diﬀerences in distributions of outcomes across and within groups, including intersecting groups; Completeness, representativeness, and balance of data sources; demographic group and subgroup coverage in GAI system training data; Forms of latent systemic bias in images, text, audio, embeddings, or other complex or unstructured data; Input data features that may serve as proxies for demographic group membership (i.e., image metadata, language dialect) or otherwise give rise to emergent bias within GAI systems; The extent to which the digital divide may negatively impact representativeness in GAI system training and TEVV data; Filtering of hate speech or content in GAI system training data; Prevalence of GAI-generated data in GAI system training data.</t>
+        </is>
+      </c>
+      <c r="D235" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E235" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F235" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G235" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H235" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I235" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J235" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K235" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L235" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M235" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N235" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.11-005</t>
+        </is>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
+        <is>
+          <t>AAT-10.18</t>
+        </is>
+      </c>
+      <c r="C236" s="10" t="inlineStr">
+        <is>
+          <t>Assess the proportion of synthetic to non-synthetic training data and verify training data is not overly homogenous or GAI-produced to mitigate concerns of model collapse.</t>
+        </is>
+      </c>
+      <c r="D236" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E236" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F236" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G236" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H236" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I236" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J236" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K236" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L236" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M236" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N236" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.12-001</t>
+        </is>
+      </c>
+      <c r="B237" s="10" t="inlineStr">
+        <is>
+          <t>AAT-17, AAT-17.1, EMB-15</t>
+        </is>
+      </c>
+      <c r="C237" s="10" t="inlineStr">
+        <is>
+          <t>Assess safety to physical environments when deploying GAI systems.</t>
+        </is>
+      </c>
+      <c r="D237" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E237" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F237" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G237" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H237" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I237" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J237" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K237" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L237" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M237" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N237" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.12-002</t>
+        </is>
+      </c>
+      <c r="B238" s="10" t="inlineStr">
+        <is>
+          <t>AAT-17.2</t>
+        </is>
+      </c>
+      <c r="C238" s="10" t="inlineStr">
+        <is>
+          <t>Document anticipated environmental impacts of model development, maintenance, and deployment in product design decisions.</t>
+        </is>
+      </c>
+      <c r="D238" s="10" t="inlineStr">
+        <is>
           <t>Contributes</t>
         </is>
       </c>
-      <c r="E228" s="10" t="inlineStr">
+      <c r="E238" s="10" t="inlineStr">
         <is>
           <t>Contributes</t>
         </is>
       </c>
-      <c r="F228" s="10" t="inlineStr">
+      <c r="F238" s="10" t="inlineStr">
+        <is>
+          <t>VMware Private AI Services (PAIS) provides PAIS-native mechanisms that help organizations assess the environmental footprint of AI workloads. Metrics collection for PAIS is activated by uncommenting the spec.observability.prometheusRuntime section of the PAISConfiguration custom resource, after which DevOps and MLOps engineers can visualize PAIS health and performance metrics for components running in a VCF Automation namespace through observability platforms such as Grafana. The same observability pipeline lets MLOps engineers and application developers monitor models used in agents, giving operators visibility into the operational characteristics of individual AI workloads across deep learning VMs, VKS clusters, and RAG applications. This telemetry is the raw operational data that organizations use to quantify the energy and resource footprint of AI activity.
+PAIS also supports resource efficiency through deployment leases. A lease controls how long a PAIS deployment can exist, so that AI workloads provisioned from VCF Automation catalog items are reclaimed at the end of a defined period rather than continuing to consume GPU and compute resources indefinitely. Disconnected (air-gapped) and connected deployment modes both rely on the same observability and lease controls, so the same sustainability-relevant data and lifecycle controls apply regardless of connectivity model.
+Broader sustainability and green-metric monitoring at the cluster and host level is a VCF platform capability and is covered under VCF Coverage. The organizational activity of setting sustainability targets, analyzing collected metrics, and documenting environmental impact is a process obligation outside PAIS itself, which is why the rating is Contributes rather than Meets.</t>
+        </is>
+      </c>
+      <c r="G238" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H238" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I238" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J238" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K238" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L238" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M238" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N238" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.12-003</t>
+        </is>
+      </c>
+      <c r="B239" s="10" t="inlineStr">
+        <is>
+          <t>AAT-17.2</t>
+        </is>
+      </c>
+      <c r="C239" s="10" t="inlineStr">
+        <is>
+          <t>Measure or estimate environmental impacts (e.g., energy and water consumption) for training, ﬁne tuning, and deploying models: Verify tradeoﬀs between resources used at inference time versus additional resources required at training time.</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E239" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F239" s="10" t="inlineStr">
+        <is>
+          <t>VMware Private AI Services (PAIS) provides PAIS-native mechanisms that help organizations assess the environmental footprint of AI workloads. Metrics collection for PAIS is activated by uncommenting the spec.observability.prometheusRuntime section of the PAISConfiguration custom resource, after which DevOps and MLOps engineers can visualize PAIS health and performance metrics for components running in a VCF Automation namespace through observability platforms such as Grafana. The same observability pipeline lets MLOps engineers and application developers monitor models used in agents, giving operators visibility into the operational characteristics of individual AI workloads across deep learning VMs, VKS clusters, and RAG applications. This telemetry is the raw operational data that organizations use to quantify the energy and resource footprint of AI activity.
+PAIS also supports resource efficiency through deployment leases. A lease controls how long a PAIS deployment can exist, so that AI workloads provisioned from VCF Automation catalog items are reclaimed at the end of a defined period rather than continuing to consume GPU and compute resources indefinitely. Disconnected (air-gapped) and connected deployment modes both rely on the same observability and lease controls, so the same sustainability-relevant data and lifecycle controls apply regardless of connectivity model.
+Broader sustainability and green-metric monitoring at the cluster and host level is a VCF platform capability and is covered under VCF Coverage. The organizational activity of setting sustainability targets, analyzing collected metrics, and documenting environmental impact is a process obligation outside PAIS itself, which is why the rating is Contributes rather than Meets.</t>
+        </is>
+      </c>
+      <c r="G239" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H239" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I239" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J239" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K239" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L239" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M239" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N239" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
+        <is>
+          <t>MS-2.12-004</t>
+        </is>
+      </c>
+      <c r="B240" s="10" t="inlineStr">
+        <is>
+          <t>AAT-17.2</t>
+        </is>
+      </c>
+      <c r="C240" s="10" t="inlineStr">
+        <is>
+          <t>Verify eﬀectiveness of carbon capture or oﬀset programs for GAI training and applications, and address green-washing concerns.</t>
+        </is>
+      </c>
+      <c r="D240" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E240" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F240" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G240" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H240" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I240" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J240" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K240" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L240" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M240" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N240" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="inlineStr">
+        <is>
+          <t>MS-3.2-001</t>
+        </is>
+      </c>
+      <c r="B241" s="10" t="inlineStr">
+        <is>
+          <t>AAT-07</t>
+        </is>
+      </c>
+      <c r="C241" s="10" t="inlineStr">
+        <is>
+          <t>Establish processes for identifying emergent GAI system risks including consulting with external AI Actors.</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E241" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F241" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G241" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H241" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I241" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J241" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K241" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L241" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M241" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N241" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="inlineStr">
+        <is>
+          <t>MS-3.3-001</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
+        <is>
+          <t>AAT-07.1</t>
+        </is>
+      </c>
+      <c r="C242" s="10" t="inlineStr">
+        <is>
+          <t>Conduct impact assessments on how AI-generated content might aﬀect diﬀerent social, economic, and cultural groups.</t>
+        </is>
+      </c>
+      <c r="D242" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E242" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F242" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G242" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H242" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I242" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J242" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K242" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L242" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M242" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N242" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="inlineStr">
+        <is>
+          <t>MS-3.3-003</t>
+        </is>
+      </c>
+      <c r="B243" s="10" t="inlineStr">
+        <is>
+          <t>AAT-06</t>
+        </is>
+      </c>
+      <c r="C243" s="10" t="inlineStr">
+        <is>
+          <t>Evaluate potential biases and stereotypes that could emerge from the AI- generated content using appropriate methodologies including computational testing methods as well as evaluating structured feedback input.</t>
+        </is>
+      </c>
+      <c r="D243" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E243" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F243" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G243" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H243" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I243" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J243" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K243" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L243" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M243" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N243" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>MS-3.3-004</t>
+        </is>
+      </c>
+      <c r="B244" s="10" t="inlineStr">
+        <is>
+          <t>AAT-05</t>
+        </is>
+      </c>
+      <c r="C244" s="10" t="inlineStr">
+        <is>
+          <t>Provide input for training materials about the capabilities and limitations of GAI systems related to digital content transparency for AI Actors, other professionals, and the public about the societal impacts of AI and the role of diverse and inclusive content generation.</t>
+        </is>
+      </c>
+      <c r="D244" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E244" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F244" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G244" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H244" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I244" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J244" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K244" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L244" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M244" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N244" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>MS-3.3-005</t>
+        </is>
+      </c>
+      <c r="B245" s="10" t="inlineStr">
+        <is>
+          <t>AAT-10.8, AAT-11</t>
+        </is>
+      </c>
+      <c r="C245" s="10" t="inlineStr">
+        <is>
+          <t>Record and integrate structured feedback about content provenance from operators, users, and potentially impacted communities through the use of methods such as user research studies, focus groups, or community forums. Actively seek feedback on generated content quality and potential biases. Assess the general awareness among end users and impacted communities about the availability of these feedback channels.</t>
+        </is>
+      </c>
+      <c r="D245" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="E245" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F245" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="G245" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="H245" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="I245" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="J245" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="K245" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="L245" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+      <c r="M245" s="10" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="N245" s="10" t="inlineStr">
+        <is>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="inlineStr">
+        <is>
+          <t>MS-4.2-001</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
+        <is>
+          <t>AAT-10, AAT-26</t>
+        </is>
+      </c>
+      <c r="C246" s="10" t="inlineStr">
+        <is>
+          <t>Conduct adversarial testing at a regular cadence to map and measure GAI risks, including tests to address attempts to deceive or manipulate the application of provenance techniques or other misuses. Identify vulnerabilities and understand potential misuse scenarios and unintended outputs.</t>
+        </is>
+      </c>
+      <c r="D246" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="E246" s="10" t="inlineStr">
+        <is>
+          <t>Contributes</t>
+        </is>
+      </c>
+      <c r="F246" s="10" t="inlineStr">
         <is>
           <t>VMware Private AI Services (PAIS) provides infrastructure that supports AI Test, Evaluation, Validation and Verification (TEVV) activities throughout the model lifecycle. Deep learning VMs provisioned from PAIS images provide dedicated testing environments for AI prototyping, fine-tuning, validation, and inference workloads. These DL VMs run on the same GPU-accelerated workload domains, vGPU profiles, and VM classes used in production, so TEVV activities occur in conditions comparable to the deployment environment.
 The validate-then-publish workflow creates a formal gate for AI deployment. MLOps engineers validate models for inference functionality using the Triton Inference Server and evaluate performance and safety against business use cases, including examination of inference requests for malicious behavior and functional testing. Models must pass this validation before being uploaded to the Model Gallery for production use. Model integrity is verified through hash code validation, and each revision is assigned a unique digest stored as an OCI artifact with an immutable manifest, giving cryptographic verification that the tested model is the same artifact that gets deployed.
 The platform also supports TEVV through its monitoring stack. VCF Operations monitors GPU consumption at cluster, host system, and host properties levels. Each DL VM includes a pre-installed DCGM Exporter with Prometheus collection at 5-second scrape intervals and Grafana visualization, supplying performance telemetry during testing and evaluation. The software stack for running AI applications on top of NVIDIA GPUs is validated in advance, and NVIDIA NGC containers are pre-tested and ready to run, reducing variables during TEVV by providing a known-good baseline.</t>
         </is>
       </c>
-      <c r="G228" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H228" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I228" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J228" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K228" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L228" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M228" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N228" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.10-001</t>
-        </is>
-      </c>
-      <c r="B229" s="10" t="inlineStr">
-        <is>
-          <t>AAT-19, AAT-19.8, VPM-10</t>
-        </is>
-      </c>
-      <c r="C229" s="10" t="inlineStr">
-        <is>
-          <t>Conduct AI red-teaming to assess issues such as: Outputting of training data samples, and subsequent reverse engineering, model extraction, and membership inference risks; Revealing biometric, conﬁdential, copyrighted, licensed, patented, personal, proprietary, sensitive, or trade-marked information; Tracking or revealing location information of users or members of training datasets.</t>
-        </is>
-      </c>
-      <c r="D229" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E229" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F229" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G229" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H229" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I229" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J229" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K229" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L229" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M229" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N229" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.10-002</t>
-        </is>
-      </c>
-      <c r="B230" s="10" t="inlineStr">
-        <is>
-          <t>AAT-11.1, AAT-11.3</t>
-        </is>
-      </c>
-      <c r="C230" s="10" t="inlineStr">
-        <is>
-          <t>Engage directly with end-users and other stakeholders to understand their expectations and concerns regarding content provenance. Use this feedback to guide the design of provenance data-tracking techniques.</t>
-        </is>
-      </c>
-      <c r="D230" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E230" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F230" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G230" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H230" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I230" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J230" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K230" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L230" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M230" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N230" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.10-003</t>
-        </is>
-      </c>
-      <c r="B231" s="10" t="inlineStr">
-        <is>
-          <t>AAT-10.18, AAT-12.1</t>
-        </is>
-      </c>
-      <c r="C231" s="10" t="inlineStr">
-        <is>
-          <t>Verify deduplication of GAI training data samples, particularly regarding synthetic data.</t>
-        </is>
-      </c>
-      <c r="D231" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E231" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F231" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G231" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H231" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I231" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J231" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K231" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L231" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M231" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N231" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.11-001</t>
-        </is>
-      </c>
-      <c r="B232" s="10" t="inlineStr">
-        <is>
-          <t>AAT-06, AAT-10.8, AAT-26</t>
-        </is>
-      </c>
-      <c r="C232" s="10" t="inlineStr">
-        <is>
-          <t>Apply use-case appropriate benchmarks (e.g., Bias Benchmark Questions, Real Hateful or Harmful Prompts, Winogender Schemas15) to quantify systemic bias, stereotyping, denigration, and hateful content in GAI system outputs; Document assumptions and limitations of benchmarks, including any actual or possible training/test data cross contamination, relative to in-context deployment environment.</t>
-        </is>
-      </c>
-      <c r="D232" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E232" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F232" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G232" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H232" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I232" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J232" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K232" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L232" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M232" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N232" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.11-002</t>
-        </is>
-      </c>
-      <c r="B233" s="10" t="inlineStr">
-        <is>
-          <t>AAT-10.8</t>
-        </is>
-      </c>
-      <c r="C233" s="10" t="inlineStr">
-        <is>
-          <t>Conduct fairness assessments to measure systemic bias. Measure GAI system performance across demographic groups and subgroups, addressing both quality of service and any allocation of services and resources. Quantify harms using: ﬁeld testing with sub-group populations to determine likelihood of exposure to generated content exhibiting harmful bias, AI red-teaming with counterfactual and low-context (e.g., “leader,” “bad guys”) prompts. For ML pipelines or business processes with categorical or numeric outcomes that rely on GAI, apply general fairness metrics (e.g., demographic parity, equalized odds, equal opportunity, statistical hypothesis tests), to the pipeline or business outcome where appropriate; Custom, context-speciﬁc metrics developed in collaboration with domain experts and aﬀected communities; Measurements of the prevalence of denigration in generated content in deployment (e.g., sub- sampling a fraction of traﬃc and manually annotating denigrating content).</t>
-        </is>
-      </c>
-      <c r="D233" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E233" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F233" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G233" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H233" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I233" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J233" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K233" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L233" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M233" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N233" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.11-003</t>
-        </is>
-      </c>
-      <c r="B234" s="10" t="inlineStr">
-        <is>
-          <t>AAT-07</t>
-        </is>
-      </c>
-      <c r="C234" s="10" t="inlineStr">
-        <is>
-          <t>Identify the classes of individuals, groups, or environmental ecosystems which might be impacted by GAI systems through direct engagement with potentially impacted communities.</t>
-        </is>
-      </c>
-      <c r="D234" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E234" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F234" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G234" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H234" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I234" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J234" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K234" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L234" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M234" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N234" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.11-004</t>
-        </is>
-      </c>
-      <c r="B235" s="10" t="inlineStr">
-        <is>
-          <t>AAT-10.8</t>
-        </is>
-      </c>
-      <c r="C235" s="10" t="inlineStr">
-        <is>
-          <t>Review, document, and measure sources of bias in GAI training and TEVV data: Diﬀerences in distributions of outcomes across and within groups, including intersecting groups; Completeness, representativeness, and balance of data sources; demographic group and subgroup coverage in GAI system training data; Forms of latent systemic bias in images, text, audio, embeddings, or other complex or unstructured data; Input data features that may serve as proxies for demographic group membership (i.e., image metadata, language dialect) or otherwise give rise to emergent bias within GAI systems; The extent to which the digital divide may negatively impact representativeness in GAI system training and TEVV data; Filtering of hate speech or content in GAI system training data; Prevalence of GAI-generated data in GAI system training data.</t>
-        </is>
-      </c>
-      <c r="D235" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E235" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F235" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G235" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H235" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I235" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J235" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K235" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L235" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M235" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N235" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.11-005</t>
-        </is>
-      </c>
-      <c r="B236" s="10" t="inlineStr">
-        <is>
-          <t>AAT-10.18</t>
-        </is>
-      </c>
-      <c r="C236" s="10" t="inlineStr">
-        <is>
-          <t>Assess the proportion of synthetic to non-synthetic training data and verify training data is not overly homogenous or GAI-produced to mitigate concerns of model collapse.</t>
-        </is>
-      </c>
-      <c r="D236" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E236" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F236" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G236" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H236" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I236" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J236" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K236" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L236" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M236" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N236" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.12-001</t>
-        </is>
-      </c>
-      <c r="B237" s="10" t="inlineStr">
-        <is>
-          <t>AAT-17, AAT-17.1, EMB-15</t>
-        </is>
-      </c>
-      <c r="C237" s="10" t="inlineStr">
-        <is>
-          <t>Assess safety to physical environments when deploying GAI systems.</t>
-        </is>
-      </c>
-      <c r="D237" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E237" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F237" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G237" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H237" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I237" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J237" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K237" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L237" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M237" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N237" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.12-002</t>
-        </is>
-      </c>
-      <c r="B238" s="10" t="inlineStr">
-        <is>
-          <t>AAT-17.2</t>
-        </is>
-      </c>
-      <c r="C238" s="10" t="inlineStr">
-        <is>
-          <t>Document anticipated environmental impacts of model development, maintenance, and deployment in product design decisions.</t>
-        </is>
-      </c>
-      <c r="D238" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E238" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F238" s="10" t="inlineStr">
-        <is>
-          <t>VMware Private AI Services (PAIS) provides PAIS-native mechanisms that help organizations assess the environmental footprint of AI workloads. Metrics collection for PAIS is activated by uncommenting the spec.observability.prometheusRuntime section of the PAISConfiguration custom resource, after which DevOps and MLOps engineers can visualize PAIS health and performance metrics for components running in a VCF Automation namespace through observability platforms such as Grafana. The same observability pipeline lets MLOps engineers and application developers monitor models used in agents, giving operators visibility into the operational characteristics of individual AI workloads across deep learning VMs, VKS clusters, and RAG applications. This telemetry is the raw operational data that organizations use to quantify the energy and resource footprint of AI activity.
-PAIS also supports resource efficiency through deployment leases. A lease controls how long a PAIS deployment can exist, so that AI workloads provisioned from VCF Automation catalog items are reclaimed at the end of a defined period rather than continuing to consume GPU and compute resources indefinitely. Disconnected (air-gapped) and connected deployment modes both rely on the same observability and lease controls, so the same sustainability-relevant data and lifecycle controls apply regardless of connectivity model.
-Broader sustainability and green-metric monitoring at the cluster and host level is a VCF platform capability and is covered under VCF Coverage. The organizational activity of setting sustainability targets, analyzing collected metrics, and documenting environmental impact is a process obligation outside PAIS itself, which is why the rating is Contributes rather than Meets.</t>
-        </is>
-      </c>
-      <c r="G238" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H238" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I238" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J238" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K238" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L238" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M238" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N238" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.12-003</t>
-        </is>
-      </c>
-      <c r="B239" s="10" t="inlineStr">
-        <is>
-          <t>AAT-17.2</t>
-        </is>
-      </c>
-      <c r="C239" s="10" t="inlineStr">
-        <is>
-          <t>Measure or estimate environmental impacts (e.g., energy and water consumption) for training, ﬁne tuning, and deploying models: Verify tradeoﬀs between resources used at inference time versus additional resources required at training time.</t>
-        </is>
-      </c>
-      <c r="D239" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E239" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F239" s="10" t="inlineStr">
-        <is>
-          <t>VMware Private AI Services (PAIS) provides PAIS-native mechanisms that help organizations assess the environmental footprint of AI workloads. Metrics collection for PAIS is activated by uncommenting the spec.observability.prometheusRuntime section of the PAISConfiguration custom resource, after which DevOps and MLOps engineers can visualize PAIS health and performance metrics for components running in a VCF Automation namespace through observability platforms such as Grafana. The same observability pipeline lets MLOps engineers and application developers monitor models used in agents, giving operators visibility into the operational characteristics of individual AI workloads across deep learning VMs, VKS clusters, and RAG applications. This telemetry is the raw operational data that organizations use to quantify the energy and resource footprint of AI activity.
-PAIS also supports resource efficiency through deployment leases. A lease controls how long a PAIS deployment can exist, so that AI workloads provisioned from VCF Automation catalog items are reclaimed at the end of a defined period rather than continuing to consume GPU and compute resources indefinitely. Disconnected (air-gapped) and connected deployment modes both rely on the same observability and lease controls, so the same sustainability-relevant data and lifecycle controls apply regardless of connectivity model.
-Broader sustainability and green-metric monitoring at the cluster and host level is a VCF platform capability and is covered under VCF Coverage. The organizational activity of setting sustainability targets, analyzing collected metrics, and documenting environmental impact is a process obligation outside PAIS itself, which is why the rating is Contributes rather than Meets.</t>
-        </is>
-      </c>
-      <c r="G239" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H239" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I239" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J239" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K239" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L239" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M239" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N239" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="10" t="inlineStr">
-        <is>
-          <t>MS-2.12-004</t>
-        </is>
-      </c>
-      <c r="B240" s="10" t="inlineStr">
-        <is>
-          <t>AAT-17.2</t>
-        </is>
-      </c>
-      <c r="C240" s="10" t="inlineStr">
-        <is>
-          <t>Verify eﬀectiveness of carbon capture or oﬀset programs for GAI training and applications, and address green-washing concerns.</t>
-        </is>
-      </c>
-      <c r="D240" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E240" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F240" s="10" t="inlineStr">
-        <is>
-          <t>VMware Private AI Services (PAIS) provides PAIS-native mechanisms that help organizations assess the environmental footprint of AI workloads. Metrics collection for PAIS is activated by uncommenting the spec.observability.prometheusRuntime section of the PAISConfiguration custom resource, after which DevOps and MLOps engineers can visualize PAIS health and performance metrics for components running in a VCF Automation namespace through observability platforms such as Grafana. The same observability pipeline lets MLOps engineers and application developers monitor models used in agents, giving operators visibility into the operational characteristics of individual AI workloads across deep learning VMs, VKS clusters, and RAG applications. This telemetry is the raw operational data that organizations use to quantify the energy and resource footprint of AI activity.
-PAIS also supports resource efficiency through deployment leases. A lease controls how long a PAIS deployment can exist, so that AI workloads provisioned from VCF Automation catalog items are reclaimed at the end of a defined period rather than continuing to consume GPU and compute resources indefinitely. Disconnected (air-gapped) and connected deployment modes both rely on the same observability and lease controls, so the same sustainability-relevant data and lifecycle controls apply regardless of connectivity model.
-Broader sustainability and green-metric monitoring at the cluster and host level is a VCF platform capability and is covered under VCF Coverage. The organizational activity of setting sustainability targets, analyzing collected metrics, and documenting environmental impact is a process obligation outside PAIS itself, which is why the rating is Contributes rather than Meets.</t>
-        </is>
-      </c>
-      <c r="G240" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H240" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I240" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J240" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K240" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L240" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M240" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N240" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="10" t="inlineStr">
-        <is>
-          <t>MS-3.2-001</t>
-        </is>
-      </c>
-      <c r="B241" s="10" t="inlineStr">
-        <is>
-          <t>AAT-07</t>
-        </is>
-      </c>
-      <c r="C241" s="10" t="inlineStr">
-        <is>
-          <t>Establish processes for identifying emergent GAI system risks including consulting with external AI Actors.</t>
-        </is>
-      </c>
-      <c r="D241" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E241" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F241" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G241" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H241" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I241" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J241" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K241" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L241" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M241" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N241" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="10" t="inlineStr">
-        <is>
-          <t>MS-3.3-001</t>
-        </is>
-      </c>
-      <c r="B242" s="10" t="inlineStr">
-        <is>
-          <t>AAT-07.1</t>
-        </is>
-      </c>
-      <c r="C242" s="10" t="inlineStr">
-        <is>
-          <t>Conduct impact assessments on how AI-generated content might aﬀect diﬀerent social, economic, and cultural groups.</t>
-        </is>
-      </c>
-      <c r="D242" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E242" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F242" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G242" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H242" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I242" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J242" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K242" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L242" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M242" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N242" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="10" t="inlineStr">
-        <is>
-          <t>MS-3.3-003</t>
-        </is>
-      </c>
-      <c r="B243" s="10" t="inlineStr">
-        <is>
-          <t>AAT-06</t>
-        </is>
-      </c>
-      <c r="C243" s="10" t="inlineStr">
-        <is>
-          <t>Evaluate potential biases and stereotypes that could emerge from the AI- generated content using appropriate methodologies including computational testing methods as well as evaluating structured feedback input.</t>
-        </is>
-      </c>
-      <c r="D243" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E243" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F243" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G243" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H243" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I243" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J243" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K243" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L243" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M243" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N243" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>MS-3.3-004</t>
-        </is>
-      </c>
-      <c r="B244" s="10" t="inlineStr">
-        <is>
-          <t>AAT-05</t>
-        </is>
-      </c>
-      <c r="C244" s="10" t="inlineStr">
-        <is>
-          <t>Provide input for training materials about the capabilities and limitations of GAI systems related to digital content transparency for AI Actors, other professionals, and the public about the societal impacts of AI and the role of diverse and inclusive content generation.</t>
-        </is>
-      </c>
-      <c r="D244" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E244" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F244" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G244" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H244" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I244" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J244" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K244" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L244" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M244" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N244" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>MS-3.3-005</t>
-        </is>
-      </c>
-      <c r="B245" s="10" t="inlineStr">
-        <is>
-          <t>AAT-10.8, AAT-11</t>
-        </is>
-      </c>
-      <c r="C245" s="10" t="inlineStr">
-        <is>
-          <t>Record and integrate structured feedback about content provenance from operators, users, and potentially impacted communities through the use of methods such as user research studies, focus groups, or community forums. Actively seek feedback on generated content quality and potential biases. Assess the general awareness among end users and impacted communities about the availability of these feedback channels.</t>
-        </is>
-      </c>
-      <c r="D245" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="E245" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F245" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="G245" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="H245" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="I245" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="J245" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="K245" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="L245" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-      <c r="M245" s="10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="N245" s="10" t="inlineStr">
-        <is>
-          <t>End user activity or process, design decision, or activity out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="10" t="inlineStr">
-        <is>
-          <t>MS-4.2-001</t>
-        </is>
-      </c>
-      <c r="B246" s="10" t="inlineStr">
-        <is>
-          <t>AAT-10, AAT-26</t>
-        </is>
-      </c>
-      <c r="C246" s="10" t="inlineStr">
-        <is>
-          <t>Conduct adversarial testing at a regular cadence to map and measure GAI risks, including tests to address attempts to deceive or manipulate the application of provenance techniques or other misuses. Identify vulnerabilities and understand potential misuse scenarios and unintended outputs.</t>
-        </is>
-      </c>
-      <c r="D246" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="E246" s="10" t="inlineStr">
-        <is>
-          <t>Contributes</t>
-        </is>
-      </c>
-      <c r="F246" s="10" t="inlineStr">
-        <is>
-          <t>VMware Private AI Services (PAIS) provides infrastructure that supports AI Test, Evaluation, Validation and Verification (TEVV) activities throughout the model lifecycle. Deep learning VMs provisioned from PAIS images provide dedicated testing environments for AI prototyping, fine-tuning, validation, and inference workloads. These DL VMs run on the same GPU-accelerated workload domains, vGPU profiles, and VM classes used in production, so TEVV activities occur in conditions comparable to the deployment environment.
-The validate-then-publish workflow creates a formal gate for AI deployment. MLOps engineers validate models for inference functionality using the Triton Inference Server and evaluate performance and safety against business use cases, including examination of inference requests for malicious behavior and functional testing. Models must pass this validation before being uploaded to the Model Gallery for production use. Model integrity is verified through hash code validation, and each revision is assigned a unique digest stored as an OCI artifact with an immutable manifest, giving cryptographic verification that the tested model is the same artifact that gets deployed.
-The platform also supports TEVV through its monitoring stack. VCF Operations monitors GPU consumption at cluster, host system, and host properties levels. Each DL VM includes a pre-installed DCGM Exporter with Prometheus collection at 5-second scrape intervals and Grafana visualization, supplying performance telemetry during testing and evaluation. The software stack for running AI applications on top of NVIDIA GPUs is validated in advance, and NVIDIA NGC containers are pre-tested and ready to run, reducing variables during TEVV by providing a known-good baseline.</t>
-        </is>
-      </c>
       <c r="G246" s="10" t="inlineStr">
         <is>
           <t>Not Applicable</t>
@@ -19043,21 +18746,17 @@
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E247" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F247" s="10" t="inlineStr">
         <is>
-          <t>VMware Private AI Services (PAIS) defines a structured, multi-stage value chain for creating and deploying AI workloads, with distinct stakeholder roles at each stage. The platform separates responsibilities across VI administrators, organization administrators, MLOps engineers, DevOps engineers, and AI application developers, with each role scoped to a specific phase of the deployment lifecycle.
-Infrastructure provisioning begins with VI administrators configuring GPU-accelerated workload domains, namespaces, and VMware Kubernetes Service (VKS) Supervisors in VMware vCenter and VMware ESX. Organization administrators set up the VCF Automation organization. PAIS must be activated in organization namespaces by an organization administrator or MLOps engineer after namespace creation, establishing the foundation before any AI workloads can be deployed.
-Model acquisition is registry-driven. A Harbor administrator creates a dedicated Harbor project for PAIS in the private Harbor registry, into which PAIS artifacts are uploaded as part of the installation process. OCI-compliant registries from other vendors are also supported. The Harbor project's user access controls restrict who can push or pull artifacts, creating an auditable record of which images are available and how they arrived. PAIS deployments can run in connected environments with internet access or in disconnected (air-gapped) environments, with disconnected operation requiring the Harbor registry to be pre-populated with the AI catalog images in advance.
-Compute provisioning is driven by VCF Automation catalog items created through the Private AI Services Quickstart. The catalog items include AI Workstation, DSM Database, Triton Inferencing Server, and AI Kubernetes Cluster, and are provisioned by users in selected namespaces. Catalog item visibility is verified per project so that PAIS catalog items are available only to members of the selected project. A machine retrieving information about PAIS must have access to VCF Automation, the VCF Consumption CLI, and kubectl, which scopes the provisioning interfaces to the responsible stakeholder.
-PAIS provides a UI and API for AI application developers to interact with deployed models and services. Data scientists and MLOps engineers compose applications by using PAIS Knowledge Bases linked to external data sources such as Microsoft SharePoint sites and Amazon S3 compatible stores. A Knowledge Base data source is created with a specific type that cannot be changed after creation, and one data source can be linked to multiple Knowledge Bases. DevOps engineers visualize PAIS component health and performance metrics in observability platforms such as Grafana and VCF Operations, providing accountability for each stage of the value chain.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="G247" s="10" t="inlineStr">
